--- a/docs/ATIP_Master_Deployment_Tracker_Wave_1_to_20_UPDATED.xlsx
+++ b/docs/ATIP_Master_Deployment_Tracker_Wave_1_to_20_UPDATED.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'PERF-001 Detail'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Implementation Sequence'!$A$1:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Master Dev Prompt'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Owner CSV vs repo'!$A$1:$G$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Owner CSV vs repo'!$A$1:$G$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -142,8 +142,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -638,23 +638,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
       <c r="B13" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14">
@@ -670,21 +670,21 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>YET TO START</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -730,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -749,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -781,13 +781,13 @@
         <v>49</v>
       </c>
       <c r="C22" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -844,7 +844,7 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -857,13 +857,13 @@
         <v>36</v>
       </c>
       <c r="C26" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -882,7 +882,7 @@
         <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1318,7 +1318,7 @@
         <v>31</v>
       </c>
       <c r="C53" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D53" t="n">
         <v>2</v>
@@ -1517,9 +1517,9 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Completed (automated)</t>
         </is>
       </c>
     </row>
@@ -1555,9 +1555,9 @@
           <t>Historical/model tests</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1727,9 +1727,9 @@
           <t>UI/API regression</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -2205,7 +2205,7 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>Yet to Start</t>
         </is>
@@ -2506,7 +2506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2780,22 +2780,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DP-04</t>
+          <t>PF-06</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Tick data</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Rebalancing</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
+          <t>W6 developed 2026-09-25 — coding only; independent testing PENDING (ChatGPT); see docs/W6_ADVANCED_QUANT_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DP-05</t>
+          <t>DP-04</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Order book / depth</t>
+          <t>Tick data</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -2854,22 +2854,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AF-06</t>
+          <t>DP-05</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Derivatives factors</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>Order book / depth</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
@@ -2879,34 +2879,34 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EX-11</t>
+          <t>AF-06</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Execution algos</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Derivatives factors</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
@@ -2921,19 +2921,19 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>W34 developed 2026-10-01 on branch w34-execution-microstructure — independent validation PENDING (ChatGPT); see docs/W34_EXECUTION_MICROSTRUCTURE_HANDOFF.md | W</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EX-12</t>
+          <t>EX-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Market impact model</t>
+          <t>Execution algos</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -2965,12 +2965,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EX-15</t>
+          <t>EX-12</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Latency telemetry</t>
+          <t>Market impact model</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -3002,12 +3002,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EX-16</t>
+          <t>EX-15</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Event-driven OMS</t>
+          <t>Latency telemetry</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
@@ -3039,12 +3039,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BT-17</t>
+          <t>EX-16</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Event-driven backtester</t>
+          <t>Event-driven OMS</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E15" s="18" t="inlineStr">
@@ -3076,12 +3076,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>DP-14</t>
+          <t>BT-17</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Macroeconomic data</t>
+          <t>Event-driven backtester</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
+          <t>W34 developed 2026-10-01 on branch w34-execution-microstructure — independent validation PENDING (ChatGPT); see docs/W34_EXECUTION_MICROSTRUCTURE_HANDOFF.md | W</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AD-01</t>
+          <t>DP-14</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Alt-data framework</t>
+          <t>Macroeconomic data</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -3150,12 +3150,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AD-02</t>
+          <t>AD-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Alt-data sources</t>
+          <t>Alt-data framework</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>DP-22</t>
+          <t>AD-02</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Point-in-time data lake</t>
+          <t>Alt-data sources</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" s="18" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3224,12 +3224,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DP-21</t>
+          <t>DP-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Multi-asset data</t>
+          <t>Point-in-time data lake</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
@@ -3249,24 +3249,24 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check: AMFI mutual-</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>API-06</t>
+          <t>DP-21</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Widget JSON schemas</t>
+          <t>Multi-asset data</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check: AMFI mutual-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DBS-05</t>
+          <t>API-05</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Scalable database</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>API contracts/docs</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E22" s="18" t="inlineStr">
@@ -3323,24 +3323,24 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
+          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ENT-06</t>
+          <t>API-06</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Per-user broker credential vault</t>
+          <t>Widget JSON schemas</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
@@ -3365,19 +3365,19 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ENT-14</t>
+          <t>DBS-05</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Regulatory approvals</t>
+          <t>Scalable database</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
@@ -3390,14 +3390,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3409,12 +3409,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SEC-05</t>
+          <t>ENT-06</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Compliance monitoring</t>
+          <t>Per-user broker credential vault</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
@@ -3434,24 +3434,24 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
+          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ENT-17</t>
+          <t>ENT-14</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Data privacy</t>
+          <t>Regulatory approvals</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
@@ -3464,14 +3464,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3483,49 +3483,49 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ENT-04</t>
+          <t>SEC-05</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Subscriptions &amp; billing</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>Compliance monitoring</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>W7 developed 2026-09-25 (enterprise layer, off by default) — coding only; independent testing PENDING (ChatGPT); see docs/W7_ENTERPRISE_HANDOFF.md</t>
+          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ENT-09</t>
+          <t>ENT-17</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Mobile apps</t>
+          <t>Data privacy</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3557,49 +3557,49 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>PF-12</t>
+          <t>ENT-04</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Multi-broker import</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Subscriptions &amp; billing</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
+          <t>W7 developed 2026-09-25 (enterprise layer, off by default) — coding only; independent testing PENDING (ChatGPT); see docs/W7_ENTERPRISE_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BR-07</t>
+          <t>ENT-09</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Additional brokers</t>
+          <t>Mobile apps</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
@@ -3619,34 +3619,34 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
+          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ENT-15</t>
+          <t>API-03</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Multi-asset trading</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Versioned public API</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
@@ -3656,24 +3656,24 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
+          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SE-10</t>
+          <t>PF-12</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>No/low-code strategy builder</t>
+          <t>Multi-broker import</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
@@ -3698,19 +3698,19 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ML-16</t>
+          <t>BR-07</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>AI chat assistant</t>
+          <t>Additional brokers</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
@@ -3730,24 +3730,24 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>OPS-04</t>
+          <t>ENT-15</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Cloud deployment</t>
+          <t>Multi-asset trading</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
@@ -3767,128 +3767,276 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
+          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ENT-16</t>
+          <t>SE-10</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Scalability, HA &amp; observability</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>No/low-code strategy builder</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PERF-001</t>
+          <t>ML-16</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Investor performance attribution</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
+          <t>AI chat assistant</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
         <is>
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>branch w20-release; merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>OPS-04</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Cloud deployment</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ENT-16</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Scalability, HA &amp; observability</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>PERF-001</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Investor performance attribution</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>branch w20-release; merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>QA-001</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Wealth QA / security / performance</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>RC line = w33-wealth-qa (W11-W32); merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>UAT-001</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Beta / UAT</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E37" s="19" t="inlineStr">
+      <c r="E41" s="19" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>RC line = w33-wealth-qa; merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G37"/>
+  <autoFilter ref="A1:G41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4323,7 +4471,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>39% of 1059 lines in 2 key file(s) run by: test_corporate_actions, test_fii_dii_and_delivery_factor, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live</t>
+          <t>42% of 1080 lines in 2 key file(s) run by: test_corporate_actions, test_fii_dii_and_delivery_factor, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_risk_gateway, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4531,7 +4679,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>96% of 24 lines in 1 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_regressions, test_risk_controls (+4 more)</t>
+          <t>96% of 24 lines in 1 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_regressions, test_risk_controls (+10 more)</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
@@ -4587,9 +4735,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K5" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4635,7 +4783,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>45% of 346 lines in 1 key file(s) run by: test_regressions</t>
+          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr"/>
@@ -4691,9 +4839,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -4739,7 +4887,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>45% of 346 lines in 1 key file(s) run by: test_regressions</t>
+          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr"/>
@@ -4795,9 +4943,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K7" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -4808,22 +4956,22 @@
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52-week 23.6/38.2/50/61.8 levels</t>
+          <t>52-week 23.6/38.2/50/61.8 levels; W39: swing-anchored Fibonacci (last two 5-bar pivots in 120 sessions, 38.2 / 50 / 61.8 levels, nearest level and distance) in technical_ext, shown in the stock panel</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Optional: swing-anchored levels</t>
+          <t>Independent QA</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>data/technical.py</t>
+          <t>data/technical.py; data/technical_ext.py</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>technical.py:262-268</t>
+          <t>tests/test_w39_technical_rs_fib.py</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr"/>
@@ -4832,7 +4980,7 @@
       <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr"/>
@@ -4843,7 +4991,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>45% of 346 lines in 1 key file(s) run by: test_regressions</t>
+          <t>tests/test_w39_technical_rs_fib.py | 86% of 728 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr"/>
@@ -4899,9 +5047,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K8" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4947,7 +5095,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>45% of 346 lines in 1 key file(s) run by: test_regressions</t>
+          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr"/>
@@ -5003,9 +5151,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K9" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -5016,22 +5164,22 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20-day RS with date-matched benchmark</t>
+          <t>20-day RS with date-matched benchmark; W39 (TA-08b): 63 / 126-session RS vs the stock's sector index (NSE industry -&gt; NIFTYIT / PHARMA / AUTO / FMCG / METAL / REALTY / ENERGY / BANK / PSUBANK, NIFTY50 fallback flagged) and percentile within the industry; display only</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Sector-relative RS later (TA-08b in Phase 2 if wanted)</t>
+          <t>Independent QA; IC research before any score use</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>scores/engine.py</t>
+          <t>scores/engine.py; data/technical_ext.py</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>8dd04fb</t>
+          <t>tests/test_w39_technical_rs_fib.py</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr"/>
@@ -5040,7 +5188,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr"/>
@@ -5051,7 +5199,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>tests/test_w39_technical_rs_fib.py | 88% of 961 lines in 2 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr"/>
@@ -5107,9 +5255,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K10" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -5155,7 +5303,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>85% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr"/>
@@ -5211,9 +5359,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K11" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5259,7 +5407,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>85% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr"/>
@@ -5315,9 +5463,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -5363,7 +5511,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>85% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr"/>
@@ -5467,7 +5615,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>21% of 130 lines in 1 key file(s) run by: test_risk_controls, test_w39_exec_data_tests, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_planning</t>
+          <t>26% of 130 lines in 1 key file(s) run by: test_risk_controls, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr"/>
@@ -5571,7 +5719,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>21% of 130 lines in 1 key file(s) run by: test_risk_controls, test_w39_exec_data_tests, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_planning</t>
+          <t>26% of 130 lines in 1 key file(s) run by: test_risk_controls, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr"/>
@@ -5627,9 +5775,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -5675,7 +5823,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>85% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr"/>
@@ -5731,9 +5879,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -5779,7 +5927,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>85% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr"/>
@@ -5883,7 +6031,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>83% of 317 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_paper_broker (+19 more)</t>
+          <t>85% of 327 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr"/>
@@ -5987,7 +6135,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>35% of 1105 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline</t>
+          <t>36% of 1105 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr"/>
@@ -6043,9 +6191,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K19" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -6091,7 +6239,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>85% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr"/>
@@ -6147,9 +6295,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K20" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -6195,7 +6343,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>36% of 95 lines in 1 key file(s) run by: test_w39_untested_modules</t>
+          <t>67% of 95 lines in 1 key file(s) run by: test_w39_qa_suite, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr"/>
@@ -6251,9 +6399,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K21" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -6299,7 +6447,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>55% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_performance_detail, test_wealth_dna_holdings, test_wealth_performance (+1 more)</t>
+          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite (+4 more)</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr"/>
@@ -6355,9 +6503,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K22" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -6403,7 +6551,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>55% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_performance_detail, test_wealth_dna_holdings, test_wealth_performance (+1 more)</t>
+          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite (+4 more)</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr"/>
@@ -6715,7 +6863,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>63% of 301 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_risk_gateway</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -6819,7 +6967,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>63% of 301 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_risk_gateway</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr"/>
@@ -6923,7 +7071,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>63% of 301 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_risk_gateway</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr"/>
@@ -7027,7 +7175,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>63% of 301 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_risk_gateway</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr"/>
@@ -7083,9 +7231,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K29" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -7131,7 +7279,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>85% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr"/>
@@ -7755,7 +7903,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>tests/test_paper_broker.py | 54% of 321 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w37_brokers_multi_asset, test_w39_exec_data_tests, test_w39_performance_detail, test_wealth_dna_holdings, test_wealth_performance</t>
+          <t>tests/test_paper_broker.py | 55% of 321 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w37_brokers_multi_asset, test_w39_exec_data_tests, test_w39_performance_detail, test_w39_qa_suite, test_wealth_dna_holdings (+1 more)</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr"/>
@@ -7859,7 +8007,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>53% of 64 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_ops_tests, test_w39_retail, test_w39_risk_gateway</t>
+          <t>53% of 64 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_retail (+2 more)</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr"/>
@@ -7963,7 +8111,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>36% of 877 lines in 2 key file(s) run by: test_auto_recover, test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_risk_gateway</t>
+          <t>39% of 898 lines in 2 key file(s) run by: test_auto_recover, test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_qa_suite, test_w39_risk_gateway (+1 more)</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr"/>
@@ -8067,7 +8215,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>53% of 64 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_ops_tests, test_w39_retail, test_w39_risk_gateway</t>
+          <t>53% of 64 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_retail (+2 more)</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr"/>
@@ -8123,9 +8271,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K39" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K39" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -8171,7 +8319,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr"/>
@@ -8227,9 +8375,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K40" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -8275,7 +8423,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr"/>
@@ -8331,9 +8479,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K41" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -8379,7 +8527,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr"/>
@@ -8435,9 +8583,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K42" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -8483,7 +8631,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr"/>
@@ -8539,9 +8687,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K43" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K43" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -8587,7 +8735,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr"/>
@@ -8643,9 +8791,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K44" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K44" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -8691,7 +8839,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr"/>
@@ -8747,9 +8895,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K45" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K45" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -8795,7 +8943,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr"/>
@@ -8851,9 +8999,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K46" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K46" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -8899,7 +9047,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr"/>
@@ -8955,9 +9103,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K47" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -9003,7 +9151,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr"/>
@@ -9059,9 +9207,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K48" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K48" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -9107,7 +9255,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr"/>
@@ -9163,9 +9311,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K49" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K49" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -9211,7 +9359,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr"/>
@@ -9371,9 +9519,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K51" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K51" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -9419,7 +9567,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>58% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+6 more)</t>
+          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr"/>
@@ -9523,7 +9671,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>93% of 43 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w38_platform_compliance, test_w39_backtest, test_w39_exec_data_tests, test_w39_owner_notes, test_w39_performance_detail, test_w39_quant_portfolio (+2 more)</t>
+          <t>93% of 43 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w38_platform_compliance, test_w39_backtest, test_w39_exec_data_tests, test_w39_owner_notes, test_w39_perf_budget, test_w39_performance_detail (+5 more)</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr"/>
@@ -9627,7 +9775,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>83% of 317 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_paper_broker (+19 more)</t>
+          <t>85% of 327 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr"/>
@@ -9851,7 +9999,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>37% of 202 lines in 2 key file(s) run by: test_regressions, test_risk_controls, test_w37_brokers_multi_asset, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests</t>
+          <t>37% of 202 lines in 2 key file(s) run by: test_regressions, test_risk_controls, test_w37_brokers_multi_asset, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_perf_budget, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr"/>
@@ -10011,9 +10159,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K57" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K57" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -10075,7 +10223,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>22% of 360 lines in 2 key file(s) run by: test_auto_recover, test_w39_ops_tests</t>
+          <t>65% of 360 lines in 2 key file(s) run by: test_auto_recover, test_w39_ops_tests, test_w39_perf_budget</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr"/>
@@ -10399,7 +10547,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>36% of 3017 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+1 more)</t>
+          <t>45% of 3038 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+4 more)</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr"/>
@@ -10519,7 +10667,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>62% of 907 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_paper_broker (+19 more)</t>
+          <t>85% of 917 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr"/>
@@ -10639,7 +10787,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>36% of 3017 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+1 more)</t>
+          <t>45% of 3038 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+4 more)</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr"/>
@@ -10695,9 +10843,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K63" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K63" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -10759,7 +10907,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>52% of 1076 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_paper_broker (+19 more)</t>
+          <t>72% of 1086 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr"/>
@@ -10875,7 +11023,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>46% of 1422 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_paper_broker (+19 more)</t>
+          <t>47% of 1432 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr"/>
@@ -10995,7 +11143,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>40% of 1221 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests</t>
+          <t>40% of 1221 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+4 more)</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr"/>
@@ -11051,9 +11199,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K66" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K66" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11115,7 +11263,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>58% of 1045 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_backtest, test_w39_exec_data_tests (+7 more)</t>
+          <t>61% of 1045 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_api_contract, test_w39_backtest (+11 more)</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr"/>
@@ -11235,7 +11383,7 @@
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>58% of 262 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_ops_tests</t>
+          <t>59% of 262 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite (+1 more)</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr"/>
@@ -11355,7 +11503,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>65% of 465 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_risk_gateway</t>
+          <t>66% of 502 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr"/>
@@ -11411,9 +11559,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K69" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="K69" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -11471,7 +11619,7 @@
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>0% of 263 lines in 1 key file(s) run by: no test</t>
+          <t>6% of 263 lines in 1 key file(s) run by: test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr"/>
@@ -11587,7 +11735,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>54% of 486 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_paper_broker (+19 more)</t>
+          <t>56% of 496 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr"/>
@@ -11707,7 +11855,7 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>31% of 1274 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline</t>
+          <t>31% of 1274 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr"/>
@@ -11879,9 +12027,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K73" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K73" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -11897,17 +12045,17 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Unit tests for rules.py</t>
+          <t>Independent QA</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>orders/rules.py; tests/</t>
+          <t>orders/rules.py</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>Phase status Phase 11</t>
+          <t>tests/test_w39_qa_suite.py</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr"/>
@@ -11916,10 +12064,14 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="W73" s="2" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>W39: tests/test_w39_qa_suite.py -- validation, triggers, OCO / bracket lifecycle, trailing stops through the paper broker; fix: bracket legs now anchor on the real fill price</t>
+        </is>
+      </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -11927,7 +12079,7 @@
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>20% of 465 lines in 39 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_exec_data_tests, test_w39_performance_detail, test_w39_quant_portfolio</t>
+          <t>tests/test_w39_qa_suite.py | 73% of 469 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr"/>
@@ -11983,9 +12135,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K74" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="K74" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -12005,17 +12157,17 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Add E2E pipeline test</t>
+          <t>Independent QA; network download steps are exercised only live</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>.github/workflows/tests.yml; tests/</t>
+          <t>pipeline/scheduler.py; .github/workflows/tests.yml</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>test_postmarket_scores_a_seeded_session_end_to_end; test_postmarket_refuses_a_session_that_is_a_copy_of_the_previous_one</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
@@ -12024,10 +12176,14 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="W74" s="2" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>W39: end-to-end test of run_postmarket on 260 seeded sessions (offline steps run for real) in tests/test_w39_qa_suite.py</t>
+        </is>
+      </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -12035,7 +12191,7 @@
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>0% of 0 lines in 38 key file(s) run by: no test</t>
+          <t>test_postmarket_scores_a_seeded_session_end_to_end; test_postmarket_refuses_a_session_that_is_a_copy_of_the_previous_one | 36% of 1105 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr"/>
@@ -12147,7 +12303,7 @@
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>28% of 1559 lines in 4 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_fundamentals_screener, test_job_monitoring, test_signal_pipeline, test_w38_platform_compliance</t>
+          <t>29% of 1559 lines in 4 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_fundamentals_screener, test_job_monitoring, test_signal_pipeline, test_w38_platform_compliance, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr"/>
@@ -12203,9 +12359,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K76" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K76" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -12263,7 +12419,7 @@
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>43% of 692 lines in 2 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>72% of 692 lines in 2 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr"/>
@@ -12319,9 +12475,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K77" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K77" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12379,7 +12535,7 @@
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>43% of 692 lines in 2 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>72% of 692 lines in 2 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr"/>
@@ -12435,9 +12591,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K78" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K78" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -12487,7 +12643,7 @@
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>85% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr"/>
@@ -12543,9 +12699,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K79" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K79" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -12595,7 +12751,7 @@
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>85% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr"/>
@@ -12711,7 +12867,7 @@
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>24% of 849 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live</t>
+          <t>31% of 870 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_risk_gateway, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr"/>
@@ -12831,7 +12987,7 @@
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>40% of 1221 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests</t>
+          <t>40% of 1221 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+4 more)</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr"/>
@@ -12887,9 +13043,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K82" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K82" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -12951,7 +13107,7 @@
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>56% of 917 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+9 more)</t>
+          <t>61% of 917 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+13 more)</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr"/>
@@ -13071,7 +13227,7 @@
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>73% of 451 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_paper_broker (+19 more)</t>
+          <t>75% of 461 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr"/>
@@ -13127,9 +13283,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K84" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K84" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -13187,7 +13343,7 @@
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>37% of 766 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_exec_data_tests, test_w39_performance_detail (+2 more)</t>
+          <t>70% of 807 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_exec_data_tests (+6 more)</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr"/>
@@ -13307,7 +13463,7 @@
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>63% of 301 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_risk_gateway</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr"/>
@@ -13427,7 +13583,7 @@
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>63% of 301 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_risk_gateway</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr"/>
@@ -13547,7 +13703,7 @@
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>92% of 306 lines in 1 key file(s) run by: test_w39_ops_tests</t>
+          <t>92% of 306 lines in 1 key file(s) run by: test_w39_ops_tests, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr"/>
@@ -13759,7 +13915,7 @@
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>61% of 233 lines in 1 key file(s) run by: test_w39_untested_modules</t>
+          <t>92% of 371 lines in 1 key file(s) run by: test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr"/>
@@ -13879,7 +14035,7 @@
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>33% of 1228 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline</t>
+          <t>41% of 1228 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr"/>
@@ -13999,7 +14155,7 @@
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>81% of 430 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_paper_broker (+19 more)</t>
+          <t>83% of 440 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr"/>
@@ -14111,7 +14267,7 @@
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>23% of 529 lines in 2 key file(s) run by: test_w39_untested_modules</t>
+          <t>26% of 529 lines in 2 key file(s) run by: test_w39_qa_suite, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr"/>
@@ -14223,7 +14379,7 @@
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>47% of 1091 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_paper_broker (+19 more)</t>
+          <t>50% of 1122 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr"/>
@@ -14279,9 +14435,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K94" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K94" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -14335,7 +14491,7 @@
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>51% of 579 lines in 2 key file(s) run by: test_regressions, test_w39_untested_modules</t>
+          <t>86% of 728 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr"/>
@@ -14391,9 +14547,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K95" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K95" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -14443,7 +14599,7 @@
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>45% of 346 lines in 1 key file(s) run by: test_regressions</t>
+          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr"/>
@@ -14555,7 +14711,7 @@
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>61% of 233 lines in 1 key file(s) run by: test_w39_untested_modules</t>
+          <t>92% of 371 lines in 1 key file(s) run by: test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr"/>
@@ -14667,7 +14823,7 @@
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>61% of 233 lines in 1 key file(s) run by: test_w39_untested_modules</t>
+          <t>92% of 371 lines in 1 key file(s) run by: test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr"/>
@@ -14723,9 +14879,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K98" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K98" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -14775,7 +14931,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>45% of 346 lines in 1 key file(s) run by: test_regressions</t>
+          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr"/>
@@ -14831,9 +14987,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K99" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K99" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -14887,7 +15043,7 @@
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>48% of 641 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>83% of 641 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr"/>
@@ -14943,9 +15099,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K100" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K100" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -14999,7 +15155,7 @@
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>58% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_quant_portfolio</t>
+          <t>61% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr"/>
@@ -15111,7 +15267,7 @@
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>71% of 114 lines in 1 key file(s) run by: test_w39_quant_portfolio</t>
+          <t>75% of 114 lines in 1 key file(s) run by: test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr"/>
@@ -15167,9 +15323,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K102" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K102" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -15223,7 +15379,7 @@
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>58% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_quant_portfolio</t>
+          <t>61% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr"/>
@@ -15279,9 +15435,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K103" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K103" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -15335,7 +15491,7 @@
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>20% of 51 lines in 1 key file(s) run by: test_auto_recover</t>
+          <t>61% of 51 lines in 1 key file(s) run by: test_auto_recover, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr"/>
@@ -15931,7 +16087,7 @@
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>44% of 242 lines in 3 key file(s) run by: test_auto_recover, test_w39_quant_portfolio</t>
+          <t>46% of 242 lines in 3 key file(s) run by: test_auto_recover, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr"/>
@@ -16043,7 +16199,7 @@
       </c>
       <c r="Y109" s="2" t="inlineStr">
         <is>
-          <t>18% of 167 lines in 2 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling</t>
+          <t>45% of 167 lines in 2 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial, test_w39_exec_data_tests</t>
         </is>
       </c>
       <c r="Z109" s="2" t="inlineStr"/>
@@ -16159,7 +16315,7 @@
       </c>
       <c r="Y110" s="2" t="inlineStr">
         <is>
-          <t>83% of 394 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_paper_broker (+19 more)</t>
+          <t>87% of 404 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
         </is>
       </c>
       <c r="Z110" s="2" t="inlineStr"/>
@@ -16279,7 +16435,7 @@
       </c>
       <c r="Y111" s="2" t="inlineStr">
         <is>
-          <t>80% of 212 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest</t>
+          <t>92% of 363 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z111" s="2" t="inlineStr"/>
@@ -16399,7 +16555,7 @@
       </c>
       <c r="Y112" s="2" t="inlineStr">
         <is>
-          <t>95% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_performance_detail, test_w39_untested_modules, test_wealth_performance</t>
+          <t>95% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z112" s="2" t="inlineStr"/>
@@ -16519,7 +16675,7 @@
       </c>
       <c r="Y113" s="2" t="inlineStr">
         <is>
-          <t>95% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_performance_detail, test_w39_untested_modules, test_wealth_performance</t>
+          <t>95% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z113" s="2" t="inlineStr"/>
@@ -16631,7 +16787,7 @@
       </c>
       <c r="Y114" s="2" t="inlineStr">
         <is>
-          <t>95% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_performance_detail, test_w39_untested_modules, test_wealth_performance</t>
+          <t>95% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z114" s="2" t="inlineStr"/>
@@ -16747,7 +16903,7 @@
       </c>
       <c r="Y115" s="2" t="inlineStr">
         <is>
-          <t>87% of 84 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_performance_detail, test_wealth_performance, test_wealth_planning</t>
+          <t>87% of 84 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_contract_note_fees, test_w39_performance_detail, test_w39_qa_suite, test_wealth_performance, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z115" s="2" t="inlineStr"/>
@@ -16867,7 +17023,7 @@
       </c>
       <c r="Y116" s="2" t="inlineStr">
         <is>
-          <t>69% of 29 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest</t>
+          <t>69% of 29 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z116" s="2" t="inlineStr"/>
@@ -16983,7 +17139,7 @@
       </c>
       <c r="Y117" s="2" t="inlineStr">
         <is>
-          <t>56% of 36 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest</t>
+          <t>56% of 36 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z117" s="2" t="inlineStr"/>
@@ -17039,9 +17195,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K118" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K118" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -17087,7 +17243,7 @@
       </c>
       <c r="Y118" s="2" t="inlineStr">
         <is>
-          <t>46% of 82 lines in 1 key file(s) run by: test_index_feed, test_w39_performance_detail, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_performance, test_wealth_planning</t>
+          <t>84% of 105 lines in 1 key file(s) run by: test_index_feed, test_w39_index_constituents, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings (+2 more)</t>
         </is>
       </c>
       <c r="Z118" s="2" t="inlineStr"/>
@@ -17207,7 +17363,7 @@
       </c>
       <c r="Y119" s="2" t="inlineStr">
         <is>
-          <t>80% of 348 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest</t>
+          <t>91% of 499 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z119" s="2" t="inlineStr"/>
@@ -17327,7 +17483,7 @@
       </c>
       <c r="Y120" s="2" t="inlineStr">
         <is>
-          <t>67% of 172 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest</t>
+          <t>81% of 175 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z120" s="2" t="inlineStr"/>
@@ -17447,7 +17603,7 @@
       </c>
       <c r="Y121" s="2" t="inlineStr">
         <is>
-          <t>83% of 123 lines in 1 key file(s) run by: test_w39_backtest</t>
+          <t>82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial</t>
         </is>
       </c>
       <c r="Z121" s="2" t="inlineStr"/>
@@ -17567,7 +17723,7 @@
       </c>
       <c r="Y122" s="2" t="inlineStr">
         <is>
-          <t>94% of 53 lines in 1 key file(s) run by: test_w39_untested_modules</t>
+          <t>94% of 53 lines in 1 key file(s) run by: test_w39_backtest_partial, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z122" s="2" t="inlineStr"/>
@@ -17679,7 +17835,7 @@
       </c>
       <c r="Y123" s="2" t="inlineStr">
         <is>
-          <t>33% of 197 lines in 1 key file(s) run by: test_w39_backtest, test_w39_untested_modules</t>
+          <t>45% of 197 lines in 1 key file(s) run by: test_w39_backtest, test_w39_qa_suite, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z123" s="2" t="inlineStr"/>
@@ -17735,9 +17891,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K124" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="K124" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -17780,10 +17936,14 @@
       <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="W124" s="2" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>W39 QA finding (owner methodology call): a neighbouring parameter value with too few trades is ignored, so 'stops trading one step away' is not flagged as a knife edge (backtest/sensitivity.py)</t>
+        </is>
+      </c>
       <c r="X124" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -17791,7 +17951,7 @@
       </c>
       <c r="Y124" s="2" t="inlineStr">
         <is>
-          <t>0% of 70 lines in 1 key file(s) run by: no test</t>
+          <t>100% of 70 lines in 1 key file(s) run by: test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z124" s="2" t="inlineStr"/>
@@ -18135,7 +18295,7 @@
       </c>
       <c r="Y127" s="2" t="inlineStr">
         <is>
-          <t>28% of 257 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest</t>
+          <t>32% of 257 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z127" s="2" t="inlineStr"/>
@@ -18247,7 +18407,7 @@
       </c>
       <c r="Y128" s="2" t="inlineStr">
         <is>
-          <t>28% of 257 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest</t>
+          <t>32% of 257 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z128" s="2" t="inlineStr"/>
@@ -18303,9 +18463,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K129" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K129" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
@@ -18355,7 +18515,7 @@
       </c>
       <c r="Y129" s="2" t="inlineStr">
         <is>
-          <t>55% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_performance_detail, test_wealth_dna_holdings, test_wealth_performance (+1 more)</t>
+          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite (+4 more)</t>
         </is>
       </c>
       <c r="Z129" s="2" t="inlineStr"/>
@@ -18467,7 +18627,7 @@
       </c>
       <c r="Y130" s="2" t="inlineStr">
         <is>
-          <t>61% of 233 lines in 1 key file(s) run by: test_w39_untested_modules</t>
+          <t>92% of 371 lines in 1 key file(s) run by: test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z130" s="2" t="inlineStr"/>
@@ -18579,7 +18739,7 @@
       </c>
       <c r="Y131" s="2" t="inlineStr">
         <is>
-          <t>61% of 233 lines in 1 key file(s) run by: test_w39_untested_modules</t>
+          <t>92% of 371 lines in 1 key file(s) run by: test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z131" s="2" t="inlineStr"/>
@@ -18635,9 +18795,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K132" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K132" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -18691,7 +18851,7 @@
       </c>
       <c r="Y132" s="2" t="inlineStr">
         <is>
-          <t>51% of 579 lines in 2 key file(s) run by: test_regressions, test_w39_untested_modules</t>
+          <t>86% of 728 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z132" s="2" t="inlineStr"/>
@@ -18811,7 +18971,7 @@
       </c>
       <c r="Y133" s="2" t="inlineStr">
         <is>
-          <t>9% of 275 lines in 2 key file(s) run by: test_regressions</t>
+          <t>17% of 275 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z133" s="2" t="inlineStr"/>
@@ -18867,9 +19027,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K134" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K134" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -18927,7 +19087,7 @@
       </c>
       <c r="Y134" s="2" t="inlineStr">
         <is>
-          <t>43% of 743 lines in 2 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>71% of 743 lines in 2 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z134" s="2" t="inlineStr"/>
@@ -19255,7 +19415,7 @@
       </c>
       <c r="Y137" s="2" t="inlineStr">
         <is>
-          <t>19% of 159 lines in 2 key file(s) run by: test_auto_recover</t>
+          <t>23% of 159 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget</t>
         </is>
       </c>
       <c r="Z137" s="2" t="inlineStr"/>
@@ -19475,7 +19635,7 @@
       </c>
       <c r="Y139" s="2" t="inlineStr">
         <is>
-          <t>27% of 802 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live</t>
+          <t>31% of 823 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_risk_gateway, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z139" s="2" t="inlineStr"/>
@@ -19643,9 +19803,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K141" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K141" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
@@ -19703,7 +19863,7 @@
       </c>
       <c r="Y141" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>85% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z141" s="2" t="inlineStr"/>
@@ -19875,9 +20035,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K143" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K143" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
@@ -19939,7 +20099,7 @@
       </c>
       <c r="Y143" s="2" t="inlineStr">
         <is>
-          <t>56% of 126 lines in 1 key file(s) run by: test_auto_recover</t>
+          <t>72% of 126 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest_partial</t>
         </is>
       </c>
       <c r="Z143" s="2" t="inlineStr"/>
@@ -19995,9 +20155,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K144" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K144" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -20047,7 +20207,7 @@
       </c>
       <c r="Y144" s="2" t="inlineStr">
         <is>
-          <t>50% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions</t>
+          <t>85% of 590 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z144" s="2" t="inlineStr"/>
@@ -20103,9 +20263,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K145" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K145" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
@@ -20152,12 +20312,12 @@
       </c>
       <c r="V145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W145" s="2" t="inlineStr">
         <is>
-          <t>W3 developed 2026-09-24 — independent functional validation PENDING (ChatGPT); see docs/W3_STRATEGY_ENGINE_HANDOFF.md</t>
+          <t>W3 developed 2026-09-24 — independent functional validation PENDING (ChatGPT); see docs/W3_STRATEGY_ENGINE_HANDOFF.md | W39: KNOWN_DEFECTS W3-L4 resolved -- ADD / REDUCE decisions are simulated in backtests</t>
         </is>
       </c>
       <c r="X145" s="2" t="inlineStr">
@@ -20167,7 +20327,7 @@
       </c>
       <c r="Y145" s="2" t="inlineStr">
         <is>
-          <t>45% of 192 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling</t>
+          <t>78% of 195 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial</t>
         </is>
       </c>
       <c r="Z145" s="2" t="inlineStr"/>
@@ -20223,9 +20383,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K146" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K146" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -20287,7 +20447,7 @@
       </c>
       <c r="Y146" s="2" t="inlineStr">
         <is>
-          <t>57% of 98 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling</t>
+          <t>68% of 98 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial</t>
         </is>
       </c>
       <c r="Z146" s="2" t="inlineStr"/>
@@ -20407,7 +20567,7 @@
       </c>
       <c r="Y147" s="2" t="inlineStr">
         <is>
-          <t>38% of 119 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling</t>
+          <t>38% of 119 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract</t>
         </is>
       </c>
       <c r="Z147" s="2" t="inlineStr"/>
@@ -20527,7 +20687,7 @@
       </c>
       <c r="Y148" s="2" t="inlineStr">
         <is>
-          <t>9% of 480 lines in 1 key file(s) run by: test_signal_pipeline</t>
+          <t>50% of 495 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z148" s="2" t="inlineStr"/>
@@ -20647,7 +20807,7 @@
       </c>
       <c r="Y149" s="2" t="inlineStr">
         <is>
-          <t>9% of 480 lines in 1 key file(s) run by: test_signal_pipeline</t>
+          <t>50% of 495 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z149" s="2" t="inlineStr"/>
@@ -20703,9 +20863,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K150" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K150" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -20767,7 +20927,7 @@
       </c>
       <c r="Y150" s="2" t="inlineStr">
         <is>
-          <t>25% of 64 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling</t>
+          <t>88% of 64 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial, test_w39_exec_data_tests</t>
         </is>
       </c>
       <c r="Z150" s="2" t="inlineStr"/>
@@ -21007,7 +21167,7 @@
       </c>
       <c r="Y152" s="2" t="inlineStr">
         <is>
-          <t>14% of 124 lines in 1 key file(s) run by: test_auto_recover</t>
+          <t>44% of 124 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract</t>
         </is>
       </c>
       <c r="Z152" s="2" t="inlineStr"/>
@@ -21127,7 +21287,7 @@
       </c>
       <c r="Y153" s="2" t="inlineStr">
         <is>
-          <t>14% of 124 lines in 1 key file(s) run by: test_auto_recover</t>
+          <t>44% of 124 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract</t>
         </is>
       </c>
       <c r="Z153" s="2" t="inlineStr"/>
@@ -21243,7 +21403,7 @@
       </c>
       <c r="Y154" s="2" t="inlineStr">
         <is>
-          <t>31% of 1241 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline</t>
+          <t>32% of 1241 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z154" s="2" t="inlineStr"/>
@@ -21299,9 +21459,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K155" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K155" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L155" s="2" t="inlineStr">
@@ -21355,7 +21515,7 @@
       </c>
       <c r="Y155" s="2" t="inlineStr">
         <is>
-          <t>48% of 622 lines in 3 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_risk_controls</t>
+          <t>81% of 622 lines in 3 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_risk_controls, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z155" s="2" t="inlineStr"/>
@@ -21475,7 +21635,7 @@
       </c>
       <c r="Y156" s="2" t="inlineStr">
         <is>
-          <t>85% of 68 lines in 2 key file(s) run by: test_w39_exec_data_tests</t>
+          <t>91% of 68 lines in 2 key file(s) run by: test_w39_exec_data_tests, test_w39_perf_budget</t>
         </is>
       </c>
       <c r="Z156" s="2" t="inlineStr"/>
@@ -21531,9 +21691,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K157" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K157" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
@@ -21599,7 +21759,7 @@
       </c>
       <c r="Y157" s="2" t="inlineStr">
         <is>
-          <t>56% of 104 lines in 1 key file(s) run by: test_auto_recover, test_w39_ml_regime_lineage_surface</t>
+          <t>76% of 104 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z157" s="2" t="inlineStr"/>
@@ -21775,9 +21935,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K159" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K159" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L159" s="2" t="inlineStr">
@@ -21839,7 +21999,7 @@
       </c>
       <c r="Y159" s="2" t="inlineStr">
         <is>
-          <t>12% of 159 lines in 1 key file(s) run by: test_auto_recover</t>
+          <t>85% of 159 lines in 1 key file(s) run by: test_auto_recover, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z159" s="2" t="inlineStr"/>
@@ -21895,9 +22055,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K160" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K160" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -21959,7 +22119,7 @@
       </c>
       <c r="Y160" s="2" t="inlineStr">
         <is>
-          <t>15% of 379 lines in 2 key file(s) run by: test_auto_recover</t>
+          <t>63% of 379 lines in 2 key file(s) run by: test_auto_recover, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z160" s="2" t="inlineStr"/>
@@ -22083,7 +22243,7 @@
       </c>
       <c r="Y161" s="2" t="inlineStr">
         <is>
-          <t>66% of 178 lines in 2 key file(s) run by: test_auto_recover, test_w39_ml_regime_lineage_surface</t>
+          <t>70% of 178 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z161" s="2" t="inlineStr"/>
@@ -22203,7 +22363,7 @@
       </c>
       <c r="Y162" s="2" t="inlineStr">
         <is>
-          <t>18% of 316 lines in 1 key file(s) run by: test_auto_recover</t>
+          <t>57% of 316 lines in 1 key file(s) run by: test_auto_recover, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z162" s="2" t="inlineStr"/>
@@ -22323,7 +22483,7 @@
       </c>
       <c r="Y163" s="2" t="inlineStr">
         <is>
-          <t>62% of 213 lines in 2 key file(s) run by: test_auto_recover, test_w39_ops_tests</t>
+          <t>63% of 213 lines in 2 key file(s) run by: test_auto_recover, test_w39_ops_tests</t>
         </is>
       </c>
       <c r="Z163" s="2" t="inlineStr"/>
@@ -22379,9 +22539,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K164" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K164" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -22443,7 +22603,7 @@
       </c>
       <c r="Y164" s="2" t="inlineStr">
         <is>
-          <t>16% of 475 lines in 2 key file(s) run by: test_auto_recover</t>
+          <t>67% of 475 lines in 2 key file(s) run by: test_auto_recover, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z164" s="2" t="inlineStr"/>
@@ -22499,9 +22659,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K165" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="K165" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L165" s="2" t="inlineStr">
@@ -22563,7 +22723,7 @@
       </c>
       <c r="Y165" s="2" t="inlineStr">
         <is>
-          <t>0% of 63 lines in 1 key file(s) run by: no test</t>
+          <t>90% of 63 lines in 1 key file(s) run by: test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z165" s="2" t="inlineStr"/>
@@ -23019,7 +23179,7 @@
       </c>
       <c r="Y169" s="2" t="inlineStr">
         <is>
-          <t>11% of 367 lines in 2 key file(s) run by: test_w36_ml_strategy_tooling</t>
+          <t>14% of 367 lines in 2 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z169" s="2" t="inlineStr"/>
@@ -23135,7 +23295,7 @@
       </c>
       <c r="Y170" s="2" t="inlineStr">
         <is>
-          <t>21% of 198 lines in 1 key file(s) run by: test_w36_ml_strategy_tooling</t>
+          <t>26% of 198 lines in 1 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z170" s="2" t="inlineStr"/>
@@ -23251,7 +23411,7 @@
       </c>
       <c r="Y171" s="2" t="inlineStr">
         <is>
-          <t>35% of 926 lines in 3 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_signal_pipeline</t>
+          <t>58% of 926 lines in 3 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_signal_pipeline, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z171" s="2" t="inlineStr"/>
@@ -23367,7 +23527,7 @@
       </c>
       <c r="Y172" s="2" t="inlineStr">
         <is>
-          <t>33% of 1303 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w36_ml_strategy_tooling</t>
+          <t>34% of 1303 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w36_ml_strategy_tooling, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z172" s="2" t="inlineStr"/>
@@ -23599,7 +23759,7 @@
       </c>
       <c r="Y174" s="2" t="inlineStr">
         <is>
-          <t>8% of 213 lines in 2 key file(s) run by: test_auto_recover</t>
+          <t>20% of 213 lines in 2 key file(s) run by: test_auto_recover, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z174" s="2" t="inlineStr"/>
@@ -23715,7 +23875,7 @@
       </c>
       <c r="Y175" s="2" t="inlineStr">
         <is>
-          <t>65% of 598 lines in 3 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_ml_regime_lineage_surface</t>
+          <t>68% of 598 lines in 3 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z175" s="2" t="inlineStr"/>
@@ -23951,7 +24111,7 @@
       </c>
       <c r="Y177" s="2" t="inlineStr">
         <is>
-          <t>31% of 103 lines in 2 key file(s) run by: test_auto_recover</t>
+          <t>47% of 103 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z177" s="2" t="inlineStr"/>
@@ -24067,7 +24227,7 @@
       </c>
       <c r="Y178" s="2" t="inlineStr">
         <is>
-          <t>29% of 484 lines in 2 key file(s) run by: test_auto_recover, test_w39_quant_portfolio</t>
+          <t>36% of 484 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z178" s="2" t="inlineStr"/>
@@ -24179,7 +24339,7 @@
       </c>
       <c r="Y179" s="2" t="inlineStr">
         <is>
-          <t>16% of 342 lines in 1 key file(s) run by: test_auto_recover, test_w39_quant_portfolio</t>
+          <t>23% of 342 lines in 1 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z179" s="2" t="inlineStr"/>
@@ -24299,7 +24459,7 @@
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>16% of 346 lines in 2 key file(s) run by: test_auto_recover, test_w39_quant_portfolio</t>
+          <t>24% of 346 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr"/>
@@ -24411,7 +24571,7 @@
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>43% of 581 lines in 2 key file(s) run by: test_auto_recover, test_w39_risk_gateway</t>
+          <t>45% of 595 lines in 2 key file(s) run by: test_auto_recover, test_w39_risk_gateway</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr"/>
@@ -24523,7 +24683,7 @@
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>33% of 923 lines in 3 key file(s) run by: test_auto_recover, test_w39_quant_portfolio, test_w39_risk_gateway</t>
+          <t>37% of 937 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_risk_gateway, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr"/>
@@ -24643,7 +24803,7 @@
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>47% of 590 lines in 2 key file(s) run by: test_auto_recover, test_w39_risk_gateway</t>
+          <t>51% of 604 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr"/>
@@ -24755,7 +24915,7 @@
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>45% of 678 lines in 3 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_risk_gateway</t>
+          <t>46% of 692 lines in 3 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z184" s="2" t="inlineStr"/>
@@ -24867,7 +25027,7 @@
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>50% of 882 lines in 3 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_risk_gateway</t>
+          <t>52% of 933 lines in 3 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr"/>
@@ -24987,7 +25147,7 @@
       </c>
       <c r="Y186" s="2" t="inlineStr">
         <is>
-          <t>47% of 590 lines in 2 key file(s) run by: test_auto_recover, test_w39_risk_gateway</t>
+          <t>51% of 604 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z186" s="2" t="inlineStr"/>
@@ -25095,7 +25255,7 @@
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>63% of 301 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_risk_gateway</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr"/>
@@ -25207,7 +25367,7 @@
       </c>
       <c r="Y188" s="2" t="inlineStr">
         <is>
-          <t>43% of 239 lines in 2 key file(s) run by: test_auto_recover, test_w39_quant_portfolio</t>
+          <t>51% of 239 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z188" s="2" t="inlineStr"/>
@@ -25312,12 +25472,12 @@
       <c r="U189" s="2" t="inlineStr"/>
       <c r="V189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W189" s="2" t="inlineStr">
         <is>
-          <t>W6 developed 2026-09-25 — coding only; independent testing PENDING (ChatGPT); see docs/W6_ADVANCED_QUANT_HANDOFF.md</t>
+          <t>W6 developed 2026-09-25 — coding only; independent testing PENDING (ChatGPT); see docs/W6_ADVANCED_QUANT_HANDOFF.md | W39 fix: the sector-cap projection (Dykstra, stopped early) could return weights over the sector cap (29 of 294 random cases, up to 48 points); replaced by the exact KKT projection (test_projection_never_breaks_a_sector_cap_and_is_the_nearest_feasible_point)</t>
         </is>
       </c>
       <c r="X189" s="2" t="inlineStr">
@@ -25327,7 +25487,7 @@
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>66% of 428 lines in 1 key file(s) run by: test_w39_quant_portfolio</t>
+          <t>65% of 417 lines in 1 key file(s) run by: test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr"/>
@@ -25383,14 +25543,14 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K190" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K190" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
@@ -25400,22 +25560,22 @@
       </c>
       <c r="N190" s="2" t="inlineStr">
         <is>
-          <t>W25: rebalance_plan (NEW/ADD/REDUCE/EXIT/HOLD, band, min trade, costs, turnover); portfolio strategy kind reweight_band_pct emits ADD/REDUCE with exact quantity</t>
+          <t>W25: rebalance_plan (NEW/ADD/REDUCE/EXIT/HOLD, band, min trade, costs, turnover); portfolio kind reweight_band_pct emits ADD/REDUCE with exact quantity. W39: the W2 backtest simulates ADD / REDUCE (partial rows, averaged entries, max_position_pct cap, P&amp;L conserved; BUY/SELL-only runs byte-identical); reweight_band_pct accepted by definition validation (was refused); saved runs, walk-forward and Monte Carlo count positions</t>
         </is>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
-          <t>Independent QA; backtest engine still trades whole positions</t>
+          <t>Independent QA; the event-driven engine (BT-17) still trades whole positions (it says so)</t>
         </is>
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>portfolio/optimize.py; strategy_engine/kinds.py; strategy_engine/engine.py</t>
+          <t>portfolio/optimize.py; strategy_engine/kinds.py; backtest/engine.py; strategy_engine/adapter.py</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
         <is>
-          <t>docs/W25_PORTFOLIO_RISK_HANDOFF.md</t>
+          <t>tests/test_w39_backtest_partial.py</t>
         </is>
       </c>
       <c r="R190" s="2" t="inlineStr">
@@ -25432,7 +25592,7 @@
       <c r="U190" s="2" t="inlineStr"/>
       <c r="V190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W190" s="2" t="inlineStr">
@@ -25447,7 +25607,7 @@
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>33% of 1057 lines in 3 key file(s) run by: test_signal_pipeline, test_w39_quant_portfolio</t>
+          <t>tests/test_w39_backtest_partial.py | 68% of 1355 lines in 4 key file(s) run by: test_auto_recover, test_signal_pipeline, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr"/>
@@ -25559,7 +25719,7 @@
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>16% of 342 lines in 1 key file(s) run by: test_auto_recover, test_w39_quant_portfolio</t>
+          <t>23% of 342 lines in 1 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr"/>
@@ -25637,7 +25797,7 @@
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>Independent QA; trade-based attribution needs a LIVE trade ledger</t>
+          <t>Independent QA. Trade-based attribution of the LIVE book now exists in the wealth performance report (PERF-001-07 / -09 / -10 on portfolio LIVE: broker_sync + PF-12 imports)</t>
         </is>
       </c>
       <c r="P192" s="2" t="inlineStr">
@@ -25660,7 +25820,7 @@
       <c r="U192" s="2" t="inlineStr"/>
       <c r="V192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W192" s="2" t="inlineStr"/>
@@ -25671,7 +25831,7 @@
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>16% of 342 lines in 1 key file(s) run by: test_auto_recover, test_w39_quant_portfolio</t>
+          <t>23% of 342 lines in 1 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr"/>
@@ -25749,7 +25909,7 @@
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
-          <t>Independent QA; LIVE XIRR needs a trade ledger</t>
+          <t>Independent QA. LIVE XIRR now comes from the wealth performance ledger (PERF-001-04, portfolio LIVE: Dhan broker_sync + PF-12 broker imports)</t>
         </is>
       </c>
       <c r="P193" s="2" t="inlineStr">
@@ -25772,7 +25932,7 @@
       <c r="U193" s="2" t="inlineStr"/>
       <c r="V193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W193" s="2" t="inlineStr"/>
@@ -25783,7 +25943,7 @@
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>34% of 437 lines in 2 key file(s) run by: test_auto_recover, test_w39_performance_detail, test_w39_quant_portfolio, test_wealth_math, test_wealth_performance</t>
+          <t>39% of 437 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_wealth_math, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr"/>
@@ -25839,9 +25999,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K194" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="K194" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
@@ -25899,7 +26059,7 @@
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>0% of 4 lines in 1 key file(s) run by: no test</t>
+          <t>100% of 4 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr"/>
@@ -26015,7 +26175,7 @@
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>41% of 684 lines in 4 key file(s) run by: test_auto_recover, test_paper_broker, test_risk_controls, test_strategy_live, test_w37_brokers_multi_asset, test_w39_exec_data_tests, test_w39_performance_detail, test_w39_risk_gateway (+2 more)</t>
+          <t>55% of 684 lines in 4 key file(s) run by: test_auto_recover, test_paper_broker, test_risk_controls, test_strategy_live, test_w37_brokers_multi_asset, test_w39_exec_data_tests, test_w39_performance_detail, test_w39_qa_suite (+3 more)</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr"/>
@@ -26131,7 +26291,7 @@
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>22% of 510 lines in 3 key file(s) run by: test_auto_recover</t>
+          <t>49% of 510 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr"/>
@@ -26243,7 +26403,7 @@
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>16% of 86 lines in 1 key file(s) run by: test_signal_pipeline</t>
+          <t>20% of 86 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr"/>
@@ -26359,7 +26519,7 @@
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>71% of 135 lines in 1 key file(s) run by: test_w39_exec_data_tests, test_w39_risk_gateway</t>
+          <t>73% of 135 lines in 1 key file(s) run by: test_w39_exec_data_tests, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr"/>
@@ -26479,7 +26639,7 @@
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>53% of 655 lines in 2 key file(s) run by: test_auto_recover, test_w39_exec_data_tests, test_w39_risk_gateway</t>
+          <t>55% of 669 lines in 2 key file(s) run by: test_auto_recover, test_w39_exec_data_tests, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr"/>
@@ -26711,7 +26871,7 @@
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>100% of 74 lines in 1 key file(s) run by: test_w39_exec_data_tests</t>
+          <t>100% of 74 lines in 1 key file(s) run by: test_w39_exec_data_tests, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr"/>
@@ -26831,7 +26991,7 @@
       </c>
       <c r="Y202" s="2" t="inlineStr">
         <is>
-          <t>95% of 78 lines in 2 key file(s) run by: test_w39_exec_data_tests</t>
+          <t>100% of 78 lines in 2 key file(s) run by: test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z202" s="2" t="inlineStr"/>
@@ -26943,7 +27103,7 @@
       </c>
       <c r="Y203" s="2" t="inlineStr">
         <is>
-          <t>17% of 244 lines in 2 key file(s) run by: test_auto_recover</t>
+          <t>37% of 244 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z203" s="2" t="inlineStr"/>
@@ -27059,7 +27219,7 @@
       </c>
       <c r="Y204" s="2" t="inlineStr">
         <is>
-          <t>70% of 89 lines in 2 key file(s) run by: test_w39_exec_data_tests</t>
+          <t>82% of 89 lines in 2 key file(s) run by: test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z204" s="2" t="inlineStr"/>
@@ -27583,9 +27743,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K209" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K209" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L209" s="2" t="inlineStr">
@@ -27647,7 +27807,7 @@
       </c>
       <c r="Y209" s="2" t="inlineStr">
         <is>
-          <t>42% of 406 lines in 2 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_quant_portfolio</t>
+          <t>61% of 419 lines in 2 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z209" s="2" t="inlineStr"/>
@@ -27767,7 +27927,7 @@
       </c>
       <c r="Y210" s="2" t="inlineStr">
         <is>
-          <t>12% of 208 lines in 2 key file(s) run by: test_regressions</t>
+          <t>12% of 208 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z210" s="2" t="inlineStr"/>
@@ -27887,7 +28047,7 @@
       </c>
       <c r="Y211" s="2" t="inlineStr">
         <is>
-          <t>29% of 1675 lines in 6 key file(s) run by: test_auto_recover, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_risk_gateway</t>
+          <t>50% of 1704 lines in 6 key file(s) run by: test_auto_recover, test_risk_controls, test_signal_pipeline, test_w39_backtest_partial, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio (+2 more)</t>
         </is>
       </c>
       <c r="Z211" s="2" t="inlineStr"/>
@@ -28007,7 +28167,7 @@
       </c>
       <c r="Y212" s="2" t="inlineStr">
         <is>
-          <t>9% of 480 lines in 1 key file(s) run by: test_signal_pipeline</t>
+          <t>50% of 495 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z212" s="2" t="inlineStr"/>
@@ -28183,9 +28343,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K214" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K214" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L214" s="2" t="inlineStr">
@@ -28247,7 +28407,7 @@
       </c>
       <c r="Y214" s="2" t="inlineStr">
         <is>
-          <t>58% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_quant_portfolio</t>
+          <t>61% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z214" s="2" t="inlineStr"/>
@@ -28419,9 +28579,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K216" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K216" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L216" s="2" t="inlineStr">
@@ -28479,7 +28639,7 @@
       </c>
       <c r="Y216" s="2" t="inlineStr">
         <is>
-          <t>45% of 101 lines in 1 key file(s) run by: test_w39_untested_modules</t>
+          <t>72% of 101 lines in 1 key file(s) run by: test_w39_backtest_partial, test_w39_performance_detail, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z216" s="2" t="inlineStr"/>
@@ -28591,7 +28751,7 @@
       </c>
       <c r="Y217" s="2" t="inlineStr">
         <is>
-          <t>34% of 1282 lines in 4 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live</t>
+          <t>44% of 1303 lines in 4 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live (+2 more)</t>
         </is>
       </c>
       <c r="Z217" s="2" t="inlineStr"/>
@@ -28707,7 +28867,7 @@
       </c>
       <c r="Y218" s="2" t="inlineStr">
         <is>
-          <t>8% of 407 lines in 3 key file(s) run by: test_auto_recover</t>
+          <t>34% of 407 lines in 3 key file(s) run by: test_auto_recover</t>
         </is>
       </c>
       <c r="Z218" s="2" t="inlineStr"/>
@@ -28763,9 +28923,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K219" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K219" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L219" s="2" t="inlineStr">
@@ -28823,7 +28983,7 @@
       </c>
       <c r="Y219" s="2" t="inlineStr">
         <is>
-          <t>10% of 402 lines in 2 key file(s) run by: test_auto_recover</t>
+          <t>65% of 407 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest_partial</t>
         </is>
       </c>
       <c r="Z219" s="2" t="inlineStr"/>
@@ -29047,7 +29207,7 @@
       </c>
       <c r="Y221" s="2" t="inlineStr">
         <is>
-          <t>79% of 132 lines in 1 key file(s) run by: test_w39_exec_data_tests</t>
+          <t>82% of 132 lines in 1 key file(s) run by: test_w39_exec_data_tests</t>
         </is>
       </c>
       <c r="Z221" s="2" t="inlineStr"/>
@@ -29275,7 +29435,7 @@
       </c>
       <c r="Y223" s="2" t="inlineStr">
         <is>
-          <t>55% of 177 lines in 1 key file(s) run by: test_w39_exec_data_tests, test_w39_untested_modules</t>
+          <t>58% of 177 lines in 1 key file(s) run by: test_w39_exec_data_tests, test_w39_ui_smoke, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z223" s="2" t="inlineStr"/>
@@ -29387,7 +29547,7 @@
       </c>
       <c r="Y224" s="2" t="inlineStr">
         <is>
-          <t>25% of 154 lines in 1 key file(s) run by: test_w39_untested_modules</t>
+          <t>27% of 154 lines in 1 key file(s) run by: test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z224" s="2" t="inlineStr"/>
@@ -29619,7 +29779,7 @@
       </c>
       <c r="Y226" s="2" t="inlineStr">
         <is>
-          <t>59% of 483 lines in 2 key file(s) run by: test_w39_ops_tests</t>
+          <t>59% of 483 lines in 2 key file(s) run by: test_w39_ops_tests, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z226" s="2" t="inlineStr"/>
@@ -29735,7 +29895,7 @@
       </c>
       <c r="Y227" s="2" t="inlineStr">
         <is>
-          <t>37% of 1437 lines in 6 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w37_brokers_multi_asset (+3 more)</t>
+          <t>41% of 1458 lines in 6 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w37_brokers_multi_asset (+7 more)</t>
         </is>
       </c>
       <c r="Z227" s="2" t="inlineStr"/>
@@ -29798,18 +29958,18 @@
       </c>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M228" s="2" t="inlineStr"/>
       <c r="N228" s="2" t="inlineStr">
         <is>
-          <t>W31: python -m ops api-docs generates docs/openapi.json (FastAPI schema) and docs/API_REFERENCE.md from the running app: 362 method+path pairs in 49 groups with the authz permission each needs, token requirement, parameters, summary (handler or route-module docstring)</t>
+          <t>W31: python -m ops api-docs (openapi.json + API_REFERENCE.md, 362 routes with permissions). W39: every public v1 resource has a typed response schema (openapi-v1.json) checked against the real handlers by a contract test; error bodies (incl. 422) use the envelope</t>
         </is>
       </c>
       <c r="O228" s="2" t="inlineStr">
         <is>
-          <t>Per-route response schemas (most handlers return untyped JSON)</t>
+          <t>Independent QA. Per-route schemas for the internal dashboard routes are not planned: /api/v1 is the published contract</t>
         </is>
       </c>
       <c r="P228" s="2" t="inlineStr">
@@ -29819,7 +29979,7 @@
       </c>
       <c r="Q228" s="2" t="inlineStr">
         <is>
-          <t>Generated; openapi.json 217 KB (after fixing the ops_routes forward-ref defect)</t>
+          <t>tests/test_w39_api_contract.py</t>
         </is>
       </c>
       <c r="R228" s="2" t="inlineStr">
@@ -29836,7 +29996,7 @@
       <c r="U228" s="2" t="inlineStr"/>
       <c r="V228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W228" s="2" t="inlineStr">
@@ -29851,7 +30011,7 @@
       </c>
       <c r="Y228" s="2" t="inlineStr">
         <is>
-          <t>91% of 99 lines in 1 key file(s) run by: test_w39_ops_tests</t>
+          <t>tests/test_w39_api_contract.py | 91% of 99 lines in 1 key file(s) run by: test_w39_ops_tests</t>
         </is>
       </c>
       <c r="Z228" s="2" t="inlineStr"/>
@@ -30199,7 +30359,7 @@
       </c>
       <c r="Y231" s="2" t="inlineStr">
         <is>
-          <t>18% of 373 lines in 3 key file(s) run by: test_auto_recover, test_w37_brokers_multi_asset, test_w39_risk_gateway</t>
+          <t>39% of 373 lines in 3 key file(s) run by: test_auto_recover, test_w37_brokers_multi_asset, test_w39_api_contract, test_w39_risk_gateway</t>
         </is>
       </c>
       <c r="Z231" s="2" t="inlineStr"/>
@@ -30315,7 +30475,7 @@
       </c>
       <c r="Y232" s="2" t="inlineStr">
         <is>
-          <t>61% of 486 lines in 4 key file(s) run by: test_postgres_backend, test_w38_platform_compliance</t>
+          <t>67% of 486 lines in 4 key file(s) run by: test_mysql_backend, test_postgres_backend, test_w38_platform_compliance, test_w39_perf_budget</t>
         </is>
       </c>
       <c r="Z232" s="2" t="inlineStr"/>
@@ -30555,7 +30715,7 @@
       </c>
       <c r="Y234" s="2" t="inlineStr">
         <is>
-          <t>21% of 513 lines in 3 key file(s) run by: test_auto_recover, test_w39_exec_data_tests, test_w39_risk_gateway</t>
+          <t>24% of 513 lines in 3 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_risk_gateway</t>
         </is>
       </c>
       <c r="Z234" s="2" t="inlineStr"/>
@@ -30679,7 +30839,7 @@
       </c>
       <c r="Y235" s="2" t="inlineStr">
         <is>
-          <t>28% of 673 lines in 2 key file(s) run by: test_auto_recover, test_w39_exec_data_tests</t>
+          <t>32% of 673 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_exec_data_tests</t>
         </is>
       </c>
       <c r="Z235" s="2" t="inlineStr"/>
@@ -30919,7 +31079,7 @@
       </c>
       <c r="Y237" s="2" t="inlineStr">
         <is>
-          <t>41% of 736 lines in 3 key file(s) run by: test_auto_recover, test_w39_risk_gateway</t>
+          <t>45% of 750 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_risk_gateway</t>
         </is>
       </c>
       <c r="Z237" s="2" t="inlineStr"/>
@@ -31267,7 +31427,7 @@
       </c>
       <c r="Y240" s="2" t="inlineStr">
         <is>
-          <t>67% of 359 lines in 3 key file(s) run by: test_auto_recover, test_w38_platform_compliance</t>
+          <t>77% of 359 lines in 3 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_perf_budget, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z240" s="2" t="inlineStr"/>
@@ -31383,7 +31543,7 @@
       </c>
       <c r="Y241" s="2" t="inlineStr">
         <is>
-          <t>48% of 231 lines in 2 key file(s) run by: test_auto_recover, test_w38_platform_compliance</t>
+          <t>48% of 231 lines in 2 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_perf_budget, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z241" s="2" t="inlineStr"/>
@@ -31743,7 +31903,7 @@
       </c>
       <c r="Y244" s="2" t="inlineStr">
         <is>
-          <t>28% of 577 lines in 2 key file(s) run by: test_auto_recover, test_w39_exec_data_tests</t>
+          <t>33% of 577 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_exec_data_tests</t>
         </is>
       </c>
       <c r="Z244" s="2" t="inlineStr"/>
@@ -31867,7 +32027,7 @@
       </c>
       <c r="Y245" s="2" t="inlineStr">
         <is>
-          <t>15% of 100 lines in 1 key file(s) run by: test_auto_recover</t>
+          <t>58% of 108 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_perf_budget</t>
         </is>
       </c>
       <c r="Z245" s="2" t="inlineStr"/>
@@ -31987,7 +32147,7 @@
       </c>
       <c r="Y246" s="2" t="inlineStr">
         <is>
-          <t>21% of 263 lines in 2 key file(s) run by: test_auto_recover, test_w39_risk_gateway</t>
+          <t>44% of 271 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_perf_budget, test_w39_risk_gateway</t>
         </is>
       </c>
       <c r="Z246" s="2" t="inlineStr"/>
@@ -32107,7 +32267,7 @@
       </c>
       <c r="Y247" s="2" t="inlineStr">
         <is>
-          <t>32% of 1313 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline</t>
+          <t>34% of 1313 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z247" s="2" t="inlineStr"/>
@@ -32163,9 +32323,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K248" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K248" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L248" s="2" t="inlineStr">
@@ -32223,7 +32383,7 @@
       </c>
       <c r="Y248" s="2" t="inlineStr">
         <is>
-          <t>51% of 138 lines in 2 key file(s) run by: test_auto_recover, test_w38_platform_compliance</t>
+          <t>77% of 138 lines in 2 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_perf_budget, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z248" s="2" t="inlineStr">
@@ -32283,14 +32443,14 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K249" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K249" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M249" s="2" t="inlineStr">
@@ -32300,22 +32460,22 @@
       </c>
       <c r="N249" s="2" t="inlineStr">
         <is>
-          <t>API keys with scopes + per-key limits; /api/v1 alias; v1 OpenAPI contract written by python -m ops api-docs</t>
+          <t>API keys with scopes + per-key limits; /api/v1 alias; v1 OpenAPI contract written by python -m ops api-docs; W39: deprecation policy (docs/API_VERSIONING_POLICY.md) enforced by a registry -- Deprecation / Sunset / Link headers, deprecated in OpenAPI, 410 GONE after sunset, &gt;= 180 days notice validated</t>
         </is>
       </c>
       <c r="O249" s="2" t="inlineStr">
         <is>
-          <t>Deprecation policy doc</t>
+          <t>Independent QA</t>
         </is>
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>enterprise/public_api.py; ops/__main__.py</t>
+          <t>enterprise/public_api.py; ops/http.py; ops/__main__.py; docs/API_VERSIONING_POLICY.md</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>test_a_deprecated_v1_resource_warns_then_answers_410_after_sunset</t>
         </is>
       </c>
       <c r="R249" s="2" t="inlineStr">
@@ -32332,7 +32492,7 @@
       <c r="U249" s="2" t="inlineStr"/>
       <c r="V249" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W249" s="2" t="inlineStr">
@@ -32347,7 +32507,7 @@
       </c>
       <c r="Y249" s="2" t="inlineStr">
         <is>
-          <t>18% of 227 lines in 2 key file(s) run by: test_w39_exec_data_tests</t>
+          <t>test_a_deprecated_v1_resource_warns_then_answers_410_after_sunset | 59% of 657 lines in 3 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface, test_w39_ops_tests, test_w39_owner_notes (+7 more)</t>
         </is>
       </c>
       <c r="Z249" s="2" t="inlineStr"/>
@@ -32467,7 +32627,7 @@
       </c>
       <c r="Y250" s="2" t="inlineStr">
         <is>
-          <t>20% of 447 lines in 3 key file(s) run by: test_auto_recover, test_w39_ops_tests, test_w39_risk_gateway</t>
+          <t>27% of 447 lines in 3 key file(s) run by: test_auto_recover, test_w39_ops_tests, test_w39_perf_budget, test_w39_risk_gateway</t>
         </is>
       </c>
       <c r="Z250" s="2" t="inlineStr"/>
@@ -32568,12 +32728,12 @@
       <c r="U251" s="2" t="inlineStr"/>
       <c r="V251" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W251" s="2" t="inlineStr">
         <is>
-          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKERS_MULTI_ASSET_HANDOFF.md | W39 check 2026-10-07: commit is an ancestor of master</t>
+          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKERS_MULTI_ASSET_HANDOFF.md | W39 check 2026-10-07: commit is an ancestor of master | W39 (PERF-001-06): contract-note charge columns stored per trade as fee_breakdown; a charges-only file becomes FEE rows (tests/test_w39_contract_note_fees.py)</t>
         </is>
       </c>
       <c r="X251" s="2" t="inlineStr">
@@ -32583,7 +32743,7 @@
       </c>
       <c r="Y251" s="2" t="inlineStr">
         <is>
-          <t>75% of 164 lines in 2 key file(s) run by: test_w37_brokers_multi_asset</t>
+          <t>80% of 220 lines in 2 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees</t>
         </is>
       </c>
       <c r="Z251" s="2" t="inlineStr"/>
@@ -32699,7 +32859,7 @@
       </c>
       <c r="Y252" s="2" t="inlineStr">
         <is>
-          <t>55% of 278 lines in 3 key file(s) run by: test_w37_brokers_multi_asset</t>
+          <t>55% of 278 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees</t>
         </is>
       </c>
       <c r="Z252" s="2" t="inlineStr"/>
@@ -32893,7 +33053,7 @@
       </c>
       <c r="O254" s="2" t="inlineStr">
         <is>
-          <t>Tax report content</t>
+          <t>Independent QA. Tax report content is NOT built: Tax is excluded by the owner (deployment tracker, Scope Exclusions sheet); revisit only if the owner re-scopes it</t>
         </is>
       </c>
       <c r="P254" s="2" t="inlineStr">
@@ -32920,12 +33080,12 @@
       <c r="U254" s="2" t="inlineStr"/>
       <c r="V254" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W254" s="2" t="inlineStr">
         <is>
-          <t>W7 developed 2026-09-25 (enterprise layer, off by default) — coding only; independent testing PENDING (ChatGPT); see docs/W7_ENTERPRISE_HANDOFF.md</t>
+          <t>W7 developed 2026-09-25 (enterprise layer, off by default) — coding only; independent testing PENDING (ChatGPT); see docs/W7_ENTERPRISE_HANDOFF.md | W39 check: the remaining gap (tax report) is owner-excluded scope, not open work; W39 adds the printable performance report (PERF-001-13)</t>
         </is>
       </c>
       <c r="X254" s="2" t="inlineStr">
@@ -32935,7 +33095,7 @@
       </c>
       <c r="Y254" s="2" t="inlineStr">
         <is>
-          <t>13% of 135 lines in 1 key file(s) run by: test_auto_recover</t>
+          <t>40% of 135 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract</t>
         </is>
       </c>
       <c r="Z254" s="2" t="inlineStr"/>
@@ -33055,7 +33215,7 @@
       </c>
       <c r="Y255" s="2" t="inlineStr">
         <is>
-          <t>29% of 321 lines in 2 key file(s) run by: test_auto_recover</t>
+          <t>38% of 321 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract</t>
         </is>
       </c>
       <c r="Z255" s="2" t="inlineStr"/>
@@ -33579,9 +33739,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K260" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K260" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L260" s="2" t="inlineStr">
@@ -33639,7 +33799,7 @@
       </c>
       <c r="Y260" s="2" t="inlineStr">
         <is>
-          <t>53% of 242 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface, test_w39_ops_tests, test_w39_owner_notes, test_w39_performance_detail (+3 more)</t>
+          <t>71% of 254 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface, test_w39_ops_tests, test_w39_owner_notes (+7 more)</t>
         </is>
       </c>
       <c r="Z260" s="2" t="inlineStr"/>
@@ -33755,7 +33915,7 @@
       </c>
       <c r="Y261" s="2" t="inlineStr">
         <is>
-          <t>22% of 206 lines in 2 key file(s) run by: test_auto_recover, test_regressions, test_risk_controls, test_w38_platform_compliance, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface, test_w39_ops_tests (+3 more)</t>
+          <t>44% of 206 lines in 2 key file(s) run by: test_auto_recover, test_regressions, test_risk_controls, test_w38_platform_compliance, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+7 more)</t>
         </is>
       </c>
       <c r="Z261" s="2" t="inlineStr"/>
@@ -33871,7 +34031,7 @@
       </c>
       <c r="Y262" s="2" t="inlineStr">
         <is>
-          <t>36% of 1233 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_ops_tests</t>
+          <t>36% of 1233 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z262" s="2" t="inlineStr"/>
@@ -33987,7 +34147,7 @@
       </c>
       <c r="Y263" s="2" t="inlineStr">
         <is>
-          <t>21% of 1100 lines in 4 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live</t>
+          <t>24% of 1121 lines in 4 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_risk_gateway, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z263" s="2" t="inlineStr"/>
@@ -34103,7 +34263,7 @@
       </c>
       <c r="Y264" s="2" t="inlineStr">
         <is>
-          <t>93% of 132 lines in 1 key file(s) run by: test_w39_ops_tests</t>
+          <t>94% of 132 lines in 1 key file(s) run by: test_w39_ops_tests</t>
         </is>
       </c>
       <c r="Z264" s="2" t="inlineStr"/>
@@ -34219,7 +34379,7 @@
       </c>
       <c r="Y265" s="2" t="inlineStr">
         <is>
-          <t>38% of 866 lines in 3 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_risk_gateway</t>
+          <t>50% of 880 lines in 3 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z265" s="2" t="inlineStr"/>
@@ -34275,9 +34435,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K266" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+      <c r="K266" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="L266" s="2" t="inlineStr">
@@ -34335,7 +34495,7 @@
       </c>
       <c r="Y266" s="2" t="inlineStr">
         <is>
-          <t>0% of 390 lines in 2 key file(s) run by: no test</t>
+          <t>18% of 390 lines in 2 key file(s) run by: test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z266" s="2" t="inlineStr"/>
@@ -34451,7 +34611,7 @@
       </c>
       <c r="Y267" s="2" t="inlineStr">
         <is>
-          <t>65% of 221 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_ops_tests, test_w39_risk_gateway</t>
+          <t>65% of 221 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway</t>
         </is>
       </c>
       <c r="Z267" s="2" t="inlineStr"/>
@@ -34563,7 +34723,7 @@
       </c>
       <c r="Y268" s="2" t="inlineStr">
         <is>
-          <t>75% of 207 lines in 1 key file(s) run by: test_wealth_api_security, test_wealth_dna_holdings, test_wealth_planning</t>
+          <t>75% of 207 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z268" s="2" t="inlineStr"/>
@@ -34679,7 +34839,7 @@
       </c>
       <c r="Y269" s="2" t="inlineStr">
         <is>
-          <t>75% of 373 lines in 2 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_performance, test_wealth_planning</t>
+          <t>76% of 373 lines in 2 key file(s) run by: test_w39_perf_budget, test_w39_performance_detail, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_performance, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z269" s="2" t="inlineStr"/>
@@ -34795,7 +34955,7 @@
       </c>
       <c r="Y270" s="2" t="inlineStr">
         <is>
-          <t>77% of 324 lines in 1 key file(s) run by: test_wealth_api_security, test_wealth_dna_holdings, test_wealth_math, test_wealth_planning</t>
+          <t>77% of 324 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_math, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z270" s="2" t="inlineStr"/>
@@ -34911,7 +35071,7 @@
       </c>
       <c r="Y271" s="2" t="inlineStr">
         <is>
-          <t>81% of 347 lines in 1 key file(s) run by: test_wealth_api_security, test_wealth_math, test_wealth_planning</t>
+          <t>83% of 347 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_math, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z271" s="2" t="inlineStr"/>
@@ -35027,7 +35187,7 @@
       </c>
       <c r="Y272" s="2" t="inlineStr">
         <is>
-          <t>86% of 239 lines in 1 key file(s) run by: test_wealth_api_security, test_wealth_planning</t>
+          <t>87% of 239 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z272" s="2" t="inlineStr"/>
@@ -35143,7 +35303,7 @@
       </c>
       <c r="Y273" s="2" t="inlineStr">
         <is>
-          <t>89% of 1124 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
+          <t>89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z273" s="2" t="inlineStr"/>
@@ -35259,7 +35419,7 @@
       </c>
       <c r="Y274" s="2" t="inlineStr">
         <is>
-          <t>68% of 313 lines in 1 key file(s) run by: test_wealth_api_security, test_wealth_planning</t>
+          <t>68% of 313 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z274" s="2" t="inlineStr"/>
@@ -35375,7 +35535,7 @@
       </c>
       <c r="Y275" s="2" t="inlineStr">
         <is>
-          <t>70% of 244 lines in 1 key file(s) run by: test_wealth_api_security, test_wealth_planning</t>
+          <t>77% of 244 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z275" s="2" t="inlineStr"/>
@@ -35438,7 +35598,7 @@
       </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="M276" s="2" t="inlineStr">
@@ -35448,12 +35608,12 @@
       </c>
       <c r="N276" s="2" t="inlineStr">
         <is>
-          <t>W18: 70-test wealth suite, security review (S1/S2 fixed), performance. W33: static security review of W25-W32 surfaces (open redirect, verify-link query loss, unescaped NSE fields, API-reference labels fixed), route-permission audit over the generated reference, performance targets, per-wave QA matrix</t>
+          <t>W18: 70-test wealth suite, security review, performance. W33: static security review. W39: load / latency tool (tools/load_test.py, in-process or against a running dashboard, targets from W18 / W33), Playwright browser smoke tests of every page and tab, QA suite for untested modules; measured p95 145-184 ms over HTTP at 4-8 threads, 0 errors (docs/W39_QA_PERFORMANCE.md)</t>
         </is>
       </c>
       <c r="O276" s="2" t="inlineStr">
         <is>
-          <t>Independent testing (ChatGPT) per W33 handoff; the development suite now runs 600+ tests green (W39)</t>
+          <t>Independent testing (ChatGPT) per W33 handoff; the development suite now runs 820+ tests green (W39); run tools/load_test.py against the production machine</t>
         </is>
       </c>
       <c r="P276" s="2" t="inlineStr">
@@ -35491,7 +35651,7 @@
       </c>
       <c r="Y276" s="2" t="inlineStr">
         <is>
-          <t>68% of 203 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface, test_w39_ops_tests, test_w39_owner_notes, test_w39_performance_detail (+3 more)</t>
+          <t>75% of 204 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface, test_w39_ops_tests, test_w39_owner_notes (+7 more)</t>
         </is>
       </c>
       <c r="Z276" s="2" t="inlineStr"/>
@@ -35723,7 +35883,7 @@
       </c>
       <c r="Y278" s="2" t="inlineStr">
         <is>
-          <t>83% of 174 lines in 2 key file(s) run by: test_w39_ops_tests, test_w39_performance_detail</t>
+          <t>83% of 174 lines in 2 key file(s) run by: test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail</t>
         </is>
       </c>
       <c r="Z278" s="2" t="inlineStr"/>
@@ -35839,7 +35999,7 @@
       </c>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 75% of 299 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_ops_tests, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance, test_wealth_planning</t>
+          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 75% of 299 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr"/>
@@ -35955,7 +36115,7 @@
       </c>
       <c r="Y280" s="2" t="inlineStr">
         <is>
-          <t>test_model_return_is_reproducible_and_matches_a_hand_calculation; test_model_and_executable_are_reported_separately | 87% of 207 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_model_return_is_reproducible_and_matches_a_hand_calculation; test_model_and_executable_are_reported_separately | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z280" s="2" t="inlineStr"/>
@@ -36024,22 +36184,22 @@
       <c r="M281" s="2" t="inlineStr"/>
       <c r="N281" s="2" t="inlineStr">
         <is>
-          <t>next-session open x (1 + slippage bps), NSE cost model both sides, ADV cap (NOT_EXECUTABLE); W39: liquidity UNKNOWN flag when volume is missing, exit liquidity check</t>
+          <t>next-session open x (1 + slippage bps), NSE cost model both sides, ADV cap (NOT_EXECUTABLE); W39: liquidity UNKNOWN flag when volume is missing, exit liquidity check, optional square-root market-impact slippage (slippage_model=impact: half spread + Y x sigma x sqrt(Q/ADV), inputs up to the signal date)</t>
         </is>
       </c>
       <c r="O281" s="2" t="inlineStr">
         <is>
-          <t>Parity with the OMS paper fill model is not automated (different fill rule by design); optional impact-based slippage (execution/impact.py)</t>
+          <t>Parity with the OMS paper fill model is not automated (different fill rule by design)</t>
         </is>
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>wealth/perf/model.py</t>
+          <t>wealth/perf/model.py; execution/impact.py</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
         <is>
-          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap</t>
+          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap; test_impact_slippage_uses_the_square_root_estimate_known_at_the_signal</t>
         </is>
       </c>
       <c r="R281" s="2" t="inlineStr">
@@ -36071,7 +36231,7 @@
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap | 87% of 207 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap; test_impact_slippage_uses_the_square_root_estimate_known_at_the_signal | 83% of 331 lines in 2 key file(s) run by: test_w39_backtest_partial, test_w39_contract_note_fees, test_w39_performance_detail, test_w39_untested_modules, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr"/>
@@ -36187,7 +36347,7 @@
       </c>
       <c r="Y282" s="2" t="inlineStr">
         <is>
-          <t>test_period_scope_is_separate_from_lifetime; test_xirr_and_pme_match_hand_computed_flows; test_average_cost_realized_pnl_and_fees | 94% of 370 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_period_scope_is_separate_from_lifetime; test_xirr_and_pme_match_hand_computed_flows; test_average_cost_realized_pnl_and_fees | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z282" s="2" t="inlineStr"/>
@@ -36303,7 +36463,7 @@
       </c>
       <c r="Y283" s="2" t="inlineStr">
         <is>
-          <t>test_benchmark_return_is_the_price_return_over_the_sessions | 91% of 268 lines in 2 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_benchmark_return_is_the_price_return_over_the_sessions | 93% of 299 lines in 2 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z283" s="2" t="inlineStr"/>
@@ -36372,22 +36532,22 @@
       <c r="M284" s="2" t="inlineStr"/>
       <c r="N284" s="2" t="inlineStr">
         <is>
-          <t>W39: fees per kind for the period (dividend TDS and capped-sell fees counted), independent SUM over perf_ledger reconciliation, recorded components (fee_breakdown), itemised NSE statutory estimate for trades without a breakdown, slippage vs reference price</t>
+          <t>W39: fees per kind for the period (dividend TDS and capped-sell fees counted), independent SUM over perf_ledger reconciliation, recorded components (fee_breakdown), itemised NSE statutory estimate for trades without a breakdown, slippage vs reference price; broker imports carry the contract-note split (brokerage / STT / exchange / SEBI / stamp / GST / DP) per trade, and a contract-note charges file becomes FEE rows (no double count)</t>
         </is>
       </c>
       <c r="O284" s="2" t="inlineStr">
         <is>
-          <t>Broker contract-note import with component split (PF-12 imports carry totals)</t>
+          <t>Independent QA with real broker contract notes</t>
         </is>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>wealth/perf/engine.py</t>
+          <t>wealth/perf/engine.py; portfolio/imports.py</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
         <is>
-          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades</t>
+          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades; tests/test_w39_contract_note_fees.py</t>
         </is>
       </c>
       <c r="R284" s="2" t="inlineStr">
@@ -36419,7 +36579,7 @@
       </c>
       <c r="Y284" s="2" t="inlineStr">
         <is>
-          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades | 94% of 370 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades; tests/test_w39_contract_note_fees.py | 89% of 587 lines in 2 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z284" s="2" t="inlineStr"/>
@@ -36535,7 +36695,7 @@
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win; test_position_attribution_identity | 87% of 207 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win; test_position_attribution_identity | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr"/>
@@ -36651,7 +36811,7 @@
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 95% of 216 lines in 2 key file(s) run by: test_w39_backtest, test_w39_performance_detail, test_w39_untested_modules, test_wealth_math, test_wealth_performance</t>
+          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 95% of 216 lines in 2 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_wealth_math, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr"/>
@@ -36767,7 +36927,7 @@
       </c>
       <c r="Y287" s="2" t="inlineStr">
         <is>
-          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win | 90% of 407 lines in 2 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win | 92% of 461 lines in 2 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z287" s="2" t="inlineStr"/>
@@ -36883,7 +37043,7 @@
       </c>
       <c r="Y288" s="2" t="inlineStr">
         <is>
-          <t>test_risk_contribution_reconciles_and_groups_sum_to_the_total; test_contributions_reconcile_to_the_total | 94% of 370 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_risk_contribution_reconciles_and_groups_sum_to_the_total; test_contributions_reconcile_to_the_total | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z288" s="2" t="inlineStr"/>
@@ -36999,7 +37159,7 @@
       </c>
       <c r="Y289" s="2" t="inlineStr">
         <is>
-          <t>test_routes_export_a_preview_and_verify_a_saved_report; test_happy_path_through_the_api | 100% of 6 lines in 2 key file(s) run by: test_w39_retail</t>
+          <t>test_routes_export_a_preview_and_verify_a_saved_report; test_happy_path_through_the_api | 100% of 6 lines in 2 key file(s) run by: test_w39_perf_budget</t>
         </is>
       </c>
       <c r="Z289" s="2" t="inlineStr"/>
@@ -37115,7 +37275,7 @@
       </c>
       <c r="Y290" s="2" t="inlineStr">
         <is>
-          <t>test_verify_reproduces_and_detects_changed_inputs | 94% of 200 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_verify_reproduces_and_detects_changed_inputs | 95% of 231 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z290" s="2" t="inlineStr"/>
@@ -37184,22 +37344,22 @@
       <c r="M291" s="2" t="inlineStr"/>
       <c r="N291" s="2" t="inlineStr">
         <is>
-          <t>CSV (every section, copied not recomputed) and JSON of a saved report; W39: preview export route, strategy filter (ACTUAL limited to one strategy's trades)</t>
+          <t>CSV (every section, copied not recomputed) and JSON of a saved report; W39: preview export route, strategy filter (ACTUAL limited to one strategy's trades), printable HTML report (A4, Print / Save as PDF) rendered from the same sections as the CSV</t>
         </is>
       </c>
       <c r="O291" s="2" t="inlineStr">
         <is>
-          <t>PDF export not built (CSV / JSON only)</t>
+          <t>Owner UAT of the printed layout</t>
         </is>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>wealth/perf/report.py; dashboard/wealth_routes.py</t>
+          <t>wealth/perf/report.py; dashboard/wealth_routes.py; dashboard/wealth_ui/performance_tab.py</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
         <is>
-          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio</t>
+          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio; test_printable_html_has_the_csv_sections_and_numbers_and_escapes_text</t>
         </is>
       </c>
       <c r="R291" s="2" t="inlineStr">
@@ -37231,7 +37391,7 @@
       </c>
       <c r="Y291" s="2" t="inlineStr">
         <is>
-          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio | 79% of 558 lines in 2 key file(s) run by: test_auto_recover, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio; test_printable_html_has_the_csv_sections_and_numbers_and_escapes_text | 87% of 594 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_performance_detail, test_w39_ui_smoke, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z291" s="2" t="inlineStr"/>
@@ -37347,7 +37507,7 @@
       </c>
       <c r="Y292" s="2" t="inlineStr">
         <is>
-          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1124 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
+          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z292" s="2" t="inlineStr"/>
@@ -37699,7 +37859,7 @@
       </c>
       <c r="Y295" s="2" t="inlineStr">
         <is>
-          <t>test_stock_history_reports_multi_year_returns | 69% of 74 lines in 1 key file(s) run by: test_auto_recover, test_w39_owner_notes</t>
+          <t>test_stock_history_reports_multi_year_returns | 80% of 74 lines in 1 key file(s) run by: test_auto_recover, test_w39_owner_notes, test_w39_perf_budget</t>
         </is>
       </c>
       <c r="Z295" s="2" t="inlineStr"/>
@@ -37768,17 +37928,17 @@
       <c r="M296" s="2" t="inlineStr"/>
       <c r="N296" s="2" t="inlineStr">
         <is>
-          <t>W39: price band vs LTP / last close in the W4 risk engine and the manual / rule path; paper futures notional in gross exposure; gross-exposure limit on the manual path</t>
+          <t>W39: price band vs LTP / last close in the W4 risk engine and the manual / rule path; NSE circuit limits (Dhan quote upper / lower circuit stored in live_quotes) refuse a price outside today's circuit; paper futures notional in gross exposure; gross-exposure limit on the manual path</t>
         </is>
       </c>
       <c r="O296" s="2" t="inlineStr">
         <is>
-          <t>NSE circuit limits are not stored by any feed yet</t>
+          <t>Independent QA; circuit fields confirmed against a live Dhan quote</t>
         </is>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>execution/risk_engine.py; orders/risk.py</t>
+          <t>execution/risk_engine.py; orders/risk.py; data/dhan.py</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37815,7 +37975,7 @@
       </c>
       <c r="Y296" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_risk_gateway.py | 54% of 821 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_risk_gateway</t>
+          <t>tests/test_w39_risk_gateway.py | 46% of 1606 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+6 more)</t>
         </is>
       </c>
       <c r="Z296" s="2" t="inlineStr"/>
@@ -37866,9 +38026,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J297" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="J297" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="K297" s="14" t="inlineStr">
@@ -37878,7 +38038,7 @@
       </c>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="M297" s="2" t="inlineStr"/>
@@ -37921,7 +38081,7 @@
       </c>
       <c r="W297" s="2" t="inlineStr">
         <is>
-          <t>W39 in development on branch claude/wizardly-curie-fbjeoa (PR #5); not merged yet</t>
+          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
         </is>
       </c>
       <c r="X297" s="2" t="inlineStr">
@@ -37931,7 +38091,7 @@
       </c>
       <c r="Y297" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_quant_portfolio.py | 58% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_quant_portfolio</t>
+          <t>tests/test_w39_quant_portfolio.py | 61% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z297" s="2" t="inlineStr"/>
@@ -37982,9 +38142,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J298" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="J298" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="K298" s="14" t="inlineStr">
@@ -37994,13 +38154,13 @@
       </c>
       <c r="L298" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="M298" s="2" t="inlineStr"/>
       <c r="N298" s="2" t="inlineStr">
         <is>
-          <t>W39: turnover_penalty + current_weights in portfolio/optimize (proximal step); kappa = 0 reproduces the old solver</t>
+          <t>W39: turnover_penalty + current_weights in portfolio/optimize (exact proximal step inside the budget / sector-cap shifts); kappa = 0 reproduces the old solver; route falls back to the book's weights</t>
         </is>
       </c>
       <c r="O298" s="2" t="inlineStr">
@@ -38037,7 +38197,7 @@
       </c>
       <c r="W298" s="2" t="inlineStr">
         <is>
-          <t>W39 in development on branch claude/wizardly-curie-fbjeoa (PR #5); not merged yet</t>
+          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
         </is>
       </c>
       <c r="X298" s="2" t="inlineStr">
@@ -38047,7 +38207,7 @@
       </c>
       <c r="Y298" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_quant_portfolio.py | 66% of 428 lines in 1 key file(s) run by: test_w39_quant_portfolio</t>
+          <t>tests/test_w39_quant_portfolio.py | 65% of 417 lines in 1 key file(s) run by: test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z298" s="2" t="inlineStr"/>
@@ -38098,9 +38258,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="J299" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="J299" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="K299" s="14" t="inlineStr">
@@ -38110,7 +38270,7 @@
       </c>
       <c r="L299" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="M299" s="2" t="inlineStr"/>
@@ -38153,7 +38313,7 @@
       </c>
       <c r="W299" s="2" t="inlineStr">
         <is>
-          <t>W39 in development on branch claude/wizardly-curie-fbjeoa (PR #5); not merged yet</t>
+          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
         </is>
       </c>
       <c r="X299" s="2" t="inlineStr">
@@ -38163,7 +38323,7 @@
       </c>
       <c r="Y299" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_quant_portfolio.py | 67% of 542 lines in 2 key file(s) run by: test_w39_quant_portfolio</t>
+          <t>tests/test_w39_quant_portfolio.py | 67% of 531 lines in 2 key file(s) run by: test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z299" s="2" t="inlineStr"/>
@@ -38511,7 +38671,7 @@
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_ml_regime_lineage_surface.py | 72% of 148 lines in 1 key file(s) run by: test_auto_recover, test_w39_ml_regime_lineage_surface</t>
+          <t>tests/test_w39_ml_regime_lineage_surface.py | 73% of 148 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr"/>
@@ -38627,7 +38787,7 @@
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_backtest.py | 83% of 123 lines in 1 key file(s) run by: test_w39_backtest</t>
+          <t>tests/test_w39_backtest.py | 82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr"/>
@@ -38975,7 +39135,7 @@
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py | 89% of 132 lines in 1 key file(s) run by: test_w39_retail</t>
+          <t>tests/test_w39_retail.py | 89% of 132 lines in 1 key file(s) run by: test_w39_retail, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr"/>
@@ -39203,7 +39363,7 @@
       </c>
       <c r="Y308" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py | 86% of 149 lines in 1 key file(s) run by: test_w39_retail</t>
+          <t>tests/test_w39_retail.py | 87% of 149 lines in 1 key file(s) run by: test_w39_retail, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z308" s="2" t="inlineStr"/>
@@ -39319,7 +39479,7 @@
       </c>
       <c r="Y309" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py | 100% of 20 lines in 1 key file(s) run by: test_w39_retail, test_wealth_api_security</t>
+          <t>tests/test_w39_retail.py | 100% of 20 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_retail, test_w39_ui_smoke, test_wealth_api_security</t>
         </is>
       </c>
       <c r="Z309" s="2" t="inlineStr"/>
@@ -39610,7 +39770,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 75% of 299 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_ops_tests, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance, test_wealth_planning</t>
+          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 75% of 299 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -39726,7 +39886,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>test_model_return_is_reproducible_and_matches_a_hand_calculation; test_model_and_executable_are_reported_separately | 87% of 207 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_model_return_is_reproducible_and_matches_a_hand_calculation; test_model_and_executable_are_reported_separately | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr"/>
@@ -39795,22 +39955,22 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>next-session open x (1 + slippage bps), NSE cost model both sides, ADV cap (NOT_EXECUTABLE); W39: liquidity UNKNOWN flag when volume is missing, exit liquidity check</t>
+          <t>next-session open x (1 + slippage bps), NSE cost model both sides, ADV cap (NOT_EXECUTABLE); W39: liquidity UNKNOWN flag when volume is missing, exit liquidity check, optional square-root market-impact slippage (slippage_model=impact: half spread + Y x sigma x sqrt(Q/ADV), inputs up to the signal date)</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Parity with the OMS paper fill model is not automated (different fill rule by design); optional impact-based slippage (execution/impact.py)</t>
+          <t>Parity with the OMS paper fill model is not automated (different fill rule by design)</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>wealth/perf/model.py</t>
+          <t>wealth/perf/model.py; execution/impact.py</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap</t>
+          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap; test_impact_slippage_uses_the_square_root_estimate_known_at_the_signal</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -39842,7 +40002,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap | 87% of 207 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap; test_impact_slippage_uses_the_square_root_estimate_known_at_the_signal | 83% of 331 lines in 2 key file(s) run by: test_w39_backtest_partial, test_w39_contract_note_fees, test_w39_performance_detail, test_w39_untested_modules, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
@@ -39958,7 +40118,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>test_period_scope_is_separate_from_lifetime; test_xirr_and_pme_match_hand_computed_flows; test_average_cost_realized_pnl_and_fees | 94% of 370 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_period_scope_is_separate_from_lifetime; test_xirr_and_pme_match_hand_computed_flows; test_average_cost_realized_pnl_and_fees | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr"/>
@@ -40074,7 +40234,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>test_benchmark_return_is_the_price_return_over_the_sessions | 91% of 268 lines in 2 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_benchmark_return_is_the_price_return_over_the_sessions | 93% of 299 lines in 2 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr"/>
@@ -40143,22 +40303,22 @@
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>W39: fees per kind for the period (dividend TDS and capped-sell fees counted), independent SUM over perf_ledger reconciliation, recorded components (fee_breakdown), itemised NSE statutory estimate for trades without a breakdown, slippage vs reference price</t>
+          <t>W39: fees per kind for the period (dividend TDS and capped-sell fees counted), independent SUM over perf_ledger reconciliation, recorded components (fee_breakdown), itemised NSE statutory estimate for trades without a breakdown, slippage vs reference price; broker imports carry the contract-note split (brokerage / STT / exchange / SEBI / stamp / GST / DP) per trade, and a contract-note charges file becomes FEE rows (no double count)</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Broker contract-note import with component split (PF-12 imports carry totals)</t>
+          <t>Independent QA with real broker contract notes</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>wealth/perf/engine.py</t>
+          <t>wealth/perf/engine.py; portfolio/imports.py</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades</t>
+          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades; tests/test_w39_contract_note_fees.py</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -40190,7 +40350,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades | 94% of 370 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades; tests/test_w39_contract_note_fees.py | 89% of 587 lines in 2 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr"/>
@@ -40306,7 +40466,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win; test_position_attribution_identity | 87% of 207 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win; test_position_attribution_identity | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr"/>
@@ -40422,7 +40582,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 95% of 216 lines in 2 key file(s) run by: test_w39_backtest, test_w39_performance_detail, test_w39_untested_modules, test_wealth_math, test_wealth_performance</t>
+          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 95% of 216 lines in 2 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_wealth_math, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr"/>
@@ -40538,7 +40698,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win | 90% of 407 lines in 2 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win | 92% of 461 lines in 2 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr"/>
@@ -40654,7 +40814,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>test_risk_contribution_reconciles_and_groups_sum_to_the_total; test_contributions_reconcile_to_the_total | 94% of 370 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_risk_contribution_reconciles_and_groups_sum_to_the_total; test_contributions_reconcile_to_the_total | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr"/>
@@ -40770,7 +40930,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>test_routes_export_a_preview_and_verify_a_saved_report; test_happy_path_through_the_api | 100% of 6 lines in 2 key file(s) run by: test_w39_retail</t>
+          <t>test_routes_export_a_preview_and_verify_a_saved_report; test_happy_path_through_the_api | 100% of 6 lines in 2 key file(s) run by: test_w39_perf_budget</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr"/>
@@ -40886,7 +41046,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>test_verify_reproduces_and_detects_changed_inputs | 94% of 200 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_verify_reproduces_and_detects_changed_inputs | 95% of 231 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr"/>
@@ -40955,22 +41115,22 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>CSV (every section, copied not recomputed) and JSON of a saved report; W39: preview export route, strategy filter (ACTUAL limited to one strategy's trades)</t>
+          <t>CSV (every section, copied not recomputed) and JSON of a saved report; W39: preview export route, strategy filter (ACTUAL limited to one strategy's trades), printable HTML report (A4, Print / Save as PDF) rendered from the same sections as the CSV</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>PDF export not built (CSV / JSON only)</t>
+          <t>Owner UAT of the printed layout</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>wealth/perf/report.py; dashboard/wealth_routes.py</t>
+          <t>wealth/perf/report.py; dashboard/wealth_routes.py; dashboard/wealth_ui/performance_tab.py</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio</t>
+          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio; test_printable_html_has_the_csv_sections_and_numbers_and_escapes_text</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -41002,7 +41162,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio | 79% of 558 lines in 2 key file(s) run by: test_auto_recover, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio; test_printable_html_has_the_csv_sections_and_numbers_and_escapes_text | 87% of 594 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_performance_detail, test_w39_ui_smoke, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr"/>
@@ -41118,7 +41278,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1124 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
+          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr"/>
@@ -41470,7 +41630,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>test_stock_history_reports_multi_year_returns | 69% of 74 lines in 1 key file(s) run by: test_auto_recover, test_w39_owner_notes</t>
+          <t>test_stock_history_reports_multi_year_returns | 80% of 74 lines in 1 key file(s) run by: test_auto_recover, test_w39_owner_notes, test_w39_perf_budget</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr"/>
@@ -41539,17 +41699,17 @@
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>W39: price band vs LTP / last close in the W4 risk engine and the manual / rule path; paper futures notional in gross exposure; gross-exposure limit on the manual path</t>
+          <t>W39: price band vs LTP / last close in the W4 risk engine and the manual / rule path; NSE circuit limits (Dhan quote upper / lower circuit stored in live_quotes) refuse a price outside today's circuit; paper futures notional in gross exposure; gross-exposure limit on the manual path</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>NSE circuit limits are not stored by any feed yet</t>
+          <t>Independent QA; circuit fields confirmed against a live Dhan quote</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>execution/risk_engine.py; orders/risk.py</t>
+          <t>execution/risk_engine.py; orders/risk.py; data/dhan.py</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -41586,7 +41746,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_risk_gateway.py | 54% of 821 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_risk_gateway</t>
+          <t>tests/test_w39_risk_gateway.py | 46% of 1606 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+6 more)</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr"/>
@@ -41637,9 +41797,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
@@ -41649,7 +41809,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
@@ -41692,7 +41852,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>W39 in development on branch claude/wizardly-curie-fbjeoa (PR #5); not merged yet</t>
+          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -41702,7 +41862,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_quant_portfolio.py | 58% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_quant_portfolio</t>
+          <t>tests/test_w39_quant_portfolio.py | 61% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr"/>
@@ -41753,9 +41913,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
@@ -41765,13 +41925,13 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>W39: turnover_penalty + current_weights in portfolio/optimize (proximal step); kappa = 0 reproduces the old solver</t>
+          <t>W39: turnover_penalty + current_weights in portfolio/optimize (exact proximal step inside the budget / sector-cap shifts); kappa = 0 reproduces the old solver; route falls back to the book's weights</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -41808,7 +41968,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>W39 in development on branch claude/wizardly-curie-fbjeoa (PR #5); not merged yet</t>
+          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
@@ -41818,7 +41978,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_quant_portfolio.py | 66% of 428 lines in 1 key file(s) run by: test_w39_quant_portfolio</t>
+          <t>tests/test_w39_quant_portfolio.py | 65% of 417 lines in 1 key file(s) run by: test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr"/>
@@ -41869,9 +42029,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
@@ -41881,7 +42041,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
@@ -41924,7 +42084,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>W39 in development on branch claude/wizardly-curie-fbjeoa (PR #5); not merged yet</t>
+          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -41934,7 +42094,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_quant_portfolio.py | 67% of 542 lines in 2 key file(s) run by: test_w39_quant_portfolio</t>
+          <t>tests/test_w39_quant_portfolio.py | 67% of 531 lines in 2 key file(s) run by: test_w39_quant_portfolio</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr"/>
@@ -42282,7 +42442,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_ml_regime_lineage_surface.py | 72% of 148 lines in 1 key file(s) run by: test_auto_recover, test_w39_ml_regime_lineage_surface</t>
+          <t>tests/test_w39_ml_regime_lineage_surface.py | 73% of 148 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -42398,7 +42558,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_backtest.py | 83% of 123 lines in 1 key file(s) run by: test_w39_backtest</t>
+          <t>tests/test_w39_backtest.py | 82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr"/>
@@ -42746,7 +42906,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py | 89% of 132 lines in 1 key file(s) run by: test_w39_retail</t>
+          <t>tests/test_w39_retail.py | 89% of 132 lines in 1 key file(s) run by: test_w39_retail, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr"/>
@@ -42974,7 +43134,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py | 86% of 149 lines in 1 key file(s) run by: test_w39_retail</t>
+          <t>tests/test_w39_retail.py | 87% of 149 lines in 1 key file(s) run by: test_w39_retail, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr"/>
@@ -43090,7 +43250,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py | 100% of 20 lines in 1 key file(s) run by: test_w39_retail, test_wealth_api_security</t>
+          <t>tests/test_w39_retail.py | 100% of 20 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_retail, test_w39_ui_smoke, test_wealth_api_security</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr"/>
@@ -43698,7 +43858,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 36/36 features developed (22 COMPLETED, 14 awaiting independent QA); automated tests: 13 covered, 16 partly, 4 none</t>
+          <t>[2026-10-07] 36/36 features developed (22 COMPLETED, 14 awaiting independent QA); automated tests: 18 covered, 14 partly, 1 none</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -43738,7 +43898,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 27/27 features developed (10 COMPLETED, 17 awaiting independent QA); automated tests: 10 covered, 17 partly, 0 none</t>
+          <t>[2026-10-07] 27/27 features developed (10 COMPLETED, 17 awaiting independent QA); automated tests: 11 covered, 16 partly, 0 none</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -43771,14 +43931,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Completed (automated)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 12/12 features developed (5 COMPLETED, 7 awaiting independent QA); automated tests: 4 covered, 8 partly, 0 none</t>
+          <t>[2026-10-07] 12/12 features developed (5 COMPLETED, 7 awaiting independent QA); automated tests: 12 covered, 0 partly, 0 none</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -43806,19 +43966,19 @@
           <t>Existing ATIP baseline</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 48/49 features developed (14 COMPLETED, 34 awaiting independent QA); automated tests: 11 covered, 37 partly, 1 none; open: AF-09</t>
+          <t>[2026-10-07] 49/49 features developed (14 COMPLETED, 35 awaiting independent QA); automated tests: 35 covered, 14 partly, 0 none</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -43858,7 +44018,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 18/19 features developed (16 COMPLETED, 2 awaiting independent QA); automated tests: 0 covered, 18 partly, 0 none; BLOCKED: SE-05</t>
+          <t>[2026-10-07] 18/19 features developed (16 COMPLETED, 2 awaiting independent QA); automated tests: 9 covered, 9 partly, 0 none; BLOCKED: SE-05</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -43898,7 +44058,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 32/32 features developed (15 COMPLETED, 17 awaiting independent QA); automated tests: 14 covered, 17 partly, 1 none</t>
+          <t>[2026-10-07] 32/32 features developed (15 COMPLETED, 17 awaiting independent QA); automated tests: 17 covered, 15 partly, 0 none</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -43938,7 +44098,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 46/49 features developed (25 COMPLETED, 21 awaiting independent QA); automated tests: 21 covered, 25 partly, 0 none; BLOCKED: BR-08, EX-17, EX-19</t>
+          <t>[2026-10-07] 46/49 features developed (25 COMPLETED, 21 awaiting independent QA); automated tests: 25 covered, 21 partly, 0 none; BLOCKED: BR-08, EX-17, EX-19</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -43966,19 +44126,19 @@
           <t>Existing ATIP baseline</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 34/36 features developed (17 COMPLETED, 17 awaiting independent QA); automated tests: 10 covered, 25 partly, 1 none; open: PF-14, PF-15</t>
+          <t>[2026-10-07] 36/36 features developed (17 COMPLETED, 19 awaiting independent QA); automated tests: 25 covered, 11 partly, 0 none</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -44018,7 +44178,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 18/23 features developed (2 COMPLETED, 16 awaiting independent QA); automated tests: 2 covered, 16 partly, 0 none; BLOCKED: ENT-07, ENT-14, ENT-08, ENT-04, ENT-16</t>
+          <t>[2026-10-07] 18/23 features developed (2 COMPLETED, 16 awaiting independent QA); automated tests: 4 covered, 14 partly, 0 none; BLOCKED: ENT-07, ENT-14, ENT-08, ENT-04, ENT-16</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -44500,7 +44660,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[2026-10-07] 11/11 features developed (0 COMPLETED, 11 awaiting independent QA); automated tests: 5 covered, 6 partly, 0 none</t>
+          <t>[2026-10-07] 11/11 features developed (0 COMPLETED, 11 awaiting independent QA); automated tests: 8 covered, 3 partly, 0 none</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -44542,7 +44702,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[2026-10-07] 10/10 features developed (0 COMPLETED, 10 awaiting independent QA); automated tests: 0 covered, 10 partly, 0 none</t>
+          <t>[2026-10-07] 10/10 features developed (0 COMPLETED, 10 awaiting independent QA); automated tests: 4 covered, 6 partly, 0 none</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -44584,7 +44744,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 1 covered, 4 partly, 1 none</t>
+          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 2 covered, 4 partly, 0 none</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -44626,7 +44786,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[2026-10-07] 10/10 features developed (0 COMPLETED, 10 awaiting independent QA); automated tests: 1 covered, 8 partly, 1 none</t>
+          <t>[2026-10-07] 10/10 features developed (0 COMPLETED, 10 awaiting independent QA); automated tests: 5 covered, 5 partly, 0 none</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -44668,7 +44828,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[2026-10-07] 14/14 features developed (0 COMPLETED, 14 awaiting independent QA); automated tests: 1 covered, 12 partly, 1 none</t>
+          <t>[2026-10-07] 14/14 features developed (0 COMPLETED, 14 awaiting independent QA); automated tests: 3 covered, 11 partly, 0 none</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -44752,7 +44912,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[2026-10-07] 10/10 features developed (0 COMPLETED, 10 awaiting independent QA); automated tests: 2 covered, 8 partly, 0 none</t>
+          <t>[2026-10-07] 10/10 features developed (0 COMPLETED, 10 awaiting independent QA); automated tests: 6 covered, 4 partly, 0 none</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -44794,7 +44954,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[2026-10-07] 10/11 features developed (0 COMPLETED, 10 awaiting independent QA); automated tests: 2 covered, 8 partly, 0 none; BLOCKED: SE-05</t>
+          <t>[2026-10-07] 10/11 features developed (0 COMPLETED, 10 awaiting independent QA); automated tests: 3 covered, 7 partly, 0 none; BLOCKED: SE-05</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -44920,7 +45080,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 0 covered, 6 partly, 0 none</t>
+          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 1 covered, 5 partly, 0 none</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -44962,7 +45122,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 1 covered, 3 partly, 1 none</t>
+          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 1 covered, 4 partly, 0 none</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -45088,7 +45248,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[2026-10-07] 5/5 features developed (0 COMPLETED, 5 awaiting independent QA); automated tests: 0 covered, 5 partly, 0 none</t>
+          <t>[2026-10-07] 5/5 features developed (0 COMPLETED, 5 awaiting independent QA); automated tests: 2 covered, 3 partly, 0 none</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -45172,7 +45332,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 2 covered, 4 partly, 0 none</t>
+          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 3 covered, 3 partly, 0 none</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -45256,7 +45416,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[2026-10-07] 5/6 features developed (0 COMPLETED, 5 awaiting independent QA); automated tests: 2 covered, 2 partly, 0 none; BLOCKED: ENT-14</t>
+          <t>[2026-10-07] 5/6 features developed (0 COMPLETED, 5 awaiting independent QA); automated tests: 3 covered, 1 partly, 0 none; BLOCKED: ENT-14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -45298,7 +45458,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[2026-10-07] 26/31 features developed (0 COMPLETED, 26 awaiting independent QA); automated tests: 29 covered, 0 partly, 0 none; BLOCKED: EX-17, EX-19; open: AF-09, PF-14, PF-15</t>
+          <t>[2026-10-07] 33/36 features developed (1 COMPLETED, 32 awaiting independent QA); automated tests: 34 covered, 0 partly, 0 none; BLOCKED: EX-17, EX-19; open: QA-001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -45456,7 +45616,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>41</v>
@@ -45584,7 +45744,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>79.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="G8" t="n">
         <v>18</v>
@@ -45680,7 +45840,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>71.2</v>
+        <v>83.8</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
@@ -45712,7 +45872,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -46040,9 +46200,9 @@
           <t>Completed / stabilization</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Completed (blocked items)</t>
         </is>
       </c>
     </row>
@@ -46555,17 +46715,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>next-session open x (1 + slippage bps), NSE cost model both sides, ADV cap (NOT_EXECUTABLE); W39: liquidity UNKNOWN flag when volume is missing, exit liquidity check</t>
+          <t>next-session open x (1 + slippage bps), NSE cost model both sides, ADV cap (NOT_EXECUTABLE); W39: liquidity UNKNOWN flag when volume is missing, exit liquidity check, optional square-root market-impact slippage (slippage_model=impact: half spread + Y x sigma x sqrt(Q/ADV), inputs up to the signal date)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap</t>
+          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap; test_impact_slippage_uses_the_square_root_estimate_known_at_the_signal</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Parity with the OMS paper fill model is not automated (different fill rule by design); optional impact-based slippage (execution/impact.py)</t>
+          <t>Parity with the OMS paper fill model is not automated (different fill rule by design)</t>
         </is>
       </c>
     </row>
@@ -46726,17 +46886,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>W39: fees per kind for the period (dividend TDS and capped-sell fees counted), independent SUM over perf_ledger reconciliation, recorded components (fee_breakdown), itemised NSE statutory estimate for trades without a breakdown, slippage vs reference price</t>
+          <t>W39: fees per kind for the period (dividend TDS and capped-sell fees counted), independent SUM over perf_ledger reconciliation, recorded components (fee_breakdown), itemised NSE statutory estimate for trades without a breakdown, slippage vs reference price; broker imports carry the contract-note split (brokerage / STT / exchange / SEBI / stamp / GST / DP) per trade, and a contract-note charges file becomes FEE rows (no double count)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades</t>
+          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades; tests/test_w39_contract_note_fees.py</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Broker contract-note import with component split (PF-12 imports carry totals)</t>
+          <t>Independent QA with real broker contract notes</t>
         </is>
       </c>
     </row>
@@ -47125,17 +47285,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CSV (every section, copied not recomputed) and JSON of a saved report; W39: preview export route, strategy filter (ACTUAL limited to one strategy's trades)</t>
+          <t>CSV (every section, copied not recomputed) and JSON of a saved report; W39: preview export route, strategy filter (ACTUAL limited to one strategy's trades), printable HTML report (A4, Print / Save as PDF) rendered from the same sections as the CSV</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio</t>
+          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio; test_printable_html_has_the_csv_sections_and_numbers_and_escapes_text</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>PDF export not built (CSV / JSON only)</t>
+          <t>Owner UAT of the printed layout</t>
         </is>
       </c>
     </row>

--- a/docs/ATIP_Master_Deployment_Tracker_Wave_1_to_20_UPDATED.xlsx
+++ b/docs/ATIP_Master_Deployment_Tracker_Wave_1_to_20_UPDATED.xlsx
@@ -11248,12 +11248,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>W1 developed 2026-09-24 — not yet independently validated (docs/W1_FOUNDATION_HANDOFF.md)</t>
+          <t>W1 developed 2026-09-24 — not yet independently validated (docs/W1_FOUNDATION_HANDOFF.md) | W39 audit of every notify path: an alert sent while the caller held an uncommitted write stalled 60 s and was lost -- fixed in SIP run_due, the wealth investor cycle, the Dhan live-quote refresh and portfolio sync; log_job and the Dhan tick / index flushes now close on failure (tests/test_w39_notify_transactions.py)</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
@@ -39331,7 +39331,7 @@
       </c>
       <c r="Q308" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py</t>
+          <t>tests/test_w39_retail.py; tests/test_w39_notify_transactions.py</t>
         </is>
       </c>
       <c r="R308" s="2" t="inlineStr">
@@ -39353,7 +39353,7 @@
       </c>
       <c r="W308" s="2" t="inlineStr">
         <is>
-          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+          <t>W39 developed 2026-10-07 (PR #5); fix: with two or more plans due, the second order waited on the first plan's uncommitted rows and failed -- the loop now commits before each placement</t>
         </is>
       </c>
       <c r="X308" s="2" t="inlineStr">
@@ -39363,7 +39363,7 @@
       </c>
       <c r="Y308" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py | 87% of 149 lines in 1 key file(s) run by: test_w39_retail, test_w39_ui_smoke</t>
+          <t>tests/test_w39_retail.py; tests/test_w39_notify_transactions.py | 87% of 149 lines in 1 key file(s) run by: test_w39_retail, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z308" s="2" t="inlineStr"/>
@@ -43102,7 +43102,7 @@
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py</t>
+          <t>tests/test_w39_retail.py; tests/test_w39_notify_transactions.py</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -43124,7 +43124,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+          <t>W39 developed 2026-10-07 (PR #5); fix: with two or more plans due, the second order waited on the first plan's uncommitted rows and failed -- the loop now commits before each placement</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
@@ -43134,7 +43134,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py | 87% of 149 lines in 1 key file(s) run by: test_w39_retail, test_w39_ui_smoke</t>
+          <t>tests/test_w39_retail.py; tests/test_w39_notify_transactions.py | 87% of 149 lines in 1 key file(s) run by: test_w39_retail, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr"/>

--- a/docs/ATIP_Master_Deployment_Tracker_Wave_1_to_20_UPDATED.xlsx
+++ b/docs/ATIP_Master_Deployment_Tracker_Wave_1_to_20_UPDATED.xlsx
@@ -22,8 +22,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Legend" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Features'!$A$1:$Z$309</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'New Items (W39)'!$A$1:$Z$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Features'!$A$1:$Z$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'New Items (W39)'!$A$1:$Z$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Blockers'!$A$1:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Master Tracker'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Gap Analysis'!$A$1:$E$15</definedName>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>308</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>180</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -1094,55 +1094,58 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>19</v>
+      </c>
+      <c r="C39" t="n">
+        <v>19</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>Developed</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>0 Delivered baseline (maintain)</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>58</v>
-      </c>
-      <c r="C41" t="n">
-        <v>58</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1 Foundation</t>
+          <t>0 Delivered baseline (maintain)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C42" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1151,14 +1154,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2 Quant Research (data, factors, backtesting)</t>
+          <t>1 Foundation</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C43" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1167,14 +1170,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3 Strategy Engine</t>
+          <t>2 Quant Research (data, factors, backtesting)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C44" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1183,78 +1186,78 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4 AI/ML</t>
+          <t>3 Strategy Engine</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C45" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5 Risk &amp; Portfolio</t>
+          <t>4 AI/ML</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C46" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6 Execution</t>
+          <t>5 Risk &amp; Portfolio</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7 Advanced Quant</t>
+          <t>6 Execution</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C48" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8 Production Hardening</t>
+          <t>7 Advanced Quant</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -1263,14 +1266,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8 Production hardening</t>
+          <t>8 Production Hardening</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -1279,48 +1282,64 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9 Enterprise SaaS (final objective)</t>
+          <t>8 Production hardening</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C51" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10 Wealth track (Waves 11-20)</t>
+          <t>9 Enterprise SaaS (final objective)</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>10 Wealth track (Waves 11-20)</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>11</v>
+      </c>
+      <c r="C53" t="n">
+        <v>9</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>11 W39 reconciliation (owner tracker 2026-10-07)</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>31</v>
-      </c>
-      <c r="C53" t="n">
-        <v>29</v>
-      </c>
-      <c r="D53" t="n">
+      <c r="B54" t="n">
+        <v>50</v>
+      </c>
+      <c r="C54" t="n">
+        <v>48</v>
+      </c>
+      <c r="D54" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4209,7 +4228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z309"/>
+  <dimension ref="A1:Z328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4471,7 +4490,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>42% of 1080 lines in 2 key file(s) run by: test_corporate_actions, test_fii_dii_and_delivery_factor, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_risk_gateway, test_w39_ui_smoke</t>
+          <t>49% of 1091 lines in 2 key file(s) run by: test_corporate_actions, test_fii_dii_and_delivery_factor, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions (+3 more)</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4679,7 +4698,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>96% of 24 lines in 1 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_regressions, test_risk_controls (+10 more)</t>
+          <t>92% of 24 lines in 1 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_regressions, test_risk_controls (+15 more)</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
@@ -5615,7 +5634,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>26% of 130 lines in 1 key file(s) run by: test_risk_controls, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_planning</t>
+          <t>26% of 130 lines in 1 key file(s) run by: test_risk_controls, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings (+1 more)</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr"/>
@@ -5719,7 +5738,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>26% of 130 lines in 1 key file(s) run by: test_risk_controls, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_planning</t>
+          <t>26% of 130 lines in 1 key file(s) run by: test_risk_controls, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings (+1 more)</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr"/>
@@ -6031,7 +6050,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>85% of 327 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
+          <t>86% of 335 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr"/>
@@ -6135,7 +6154,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>36% of 1105 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>35% of 1213 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr"/>
@@ -6447,7 +6466,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite (+4 more)</t>
+          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_perf_budget, test_w39_performance_detail (+5 more)</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr"/>
@@ -6551,7 +6570,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite (+4 more)</t>
+          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_perf_budget, test_w39_performance_detail (+5 more)</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr"/>
@@ -6863,7 +6882,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -6967,7 +6986,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr"/>
@@ -7071,7 +7090,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr"/>
@@ -7175,7 +7194,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr"/>
@@ -8007,7 +8026,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>53% of 64 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_retail (+2 more)</t>
+          <t>53% of 64 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite (+3 more)</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr"/>
@@ -8111,7 +8130,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>39% of 898 lines in 2 key file(s) run by: test_auto_recover, test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_qa_suite, test_w39_risk_gateway (+1 more)</t>
+          <t>48% of 909 lines in 2 key file(s) run by: test_auto_recover, test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions (+4 more)</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr"/>
@@ -8215,7 +8234,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>53% of 64 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_retail (+2 more)</t>
+          <t>53% of 64 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite (+3 more)</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr"/>
@@ -8319,7 +8338,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr"/>
@@ -8423,7 +8442,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr"/>
@@ -8527,7 +8546,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr"/>
@@ -8631,7 +8650,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr"/>
@@ -8735,7 +8754,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr"/>
@@ -8839,7 +8858,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr"/>
@@ -8943,7 +8962,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr"/>
@@ -9047,7 +9066,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr"/>
@@ -9151,7 +9170,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr"/>
@@ -9255,7 +9274,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr"/>
@@ -9359,7 +9378,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr"/>
@@ -9567,7 +9586,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>62% of 783 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+10 more)</t>
+          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr"/>
@@ -9671,7 +9690,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>93% of 43 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w38_platform_compliance, test_w39_backtest, test_w39_exec_data_tests, test_w39_owner_notes, test_w39_perf_budget, test_w39_performance_detail (+5 more)</t>
+          <t>93% of 43 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w38_platform_compliance, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+18 more)</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr"/>
@@ -9775,7 +9794,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>85% of 327 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
+          <t>86% of 335 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr"/>
@@ -9879,7 +9898,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>67% of 61 lines in 1 key file(s) run by: test_w39_ops_tests, test_w39_owner_notes</t>
+          <t>71% of 79 lines in 1 key file(s) run by: test_w39_history, test_w39_ops_tests</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr"/>
@@ -10103,7 +10122,7 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>76% of 232 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_index_feed</t>
+          <t>76% of 234 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_index_feed, test_w39_notify_transactions</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr"/>
@@ -10547,7 +10566,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>45% of 3038 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+4 more)</t>
+          <t>47% of 3154 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+7 more)</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr"/>
@@ -10667,7 +10686,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>85% of 917 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
+          <t>85% of 925 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr"/>
@@ -10787,7 +10806,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>45% of 3038 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+4 more)</t>
+          <t>47% of 3154 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+7 more)</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr"/>
@@ -10907,7 +10926,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>72% of 1086 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
+          <t>72% of 1094 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr"/>
@@ -11023,7 +11042,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>47% of 1432 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
+          <t>46% of 1548 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr"/>
@@ -11143,7 +11162,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>40% of 1221 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+4 more)</t>
+          <t>39% of 1329 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+6 more)</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr"/>
@@ -11263,7 +11282,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>61% of 1045 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_api_contract, test_w39_backtest (+11 more)</t>
+          <t>61% of 1047 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_api_contract, test_w39_backtest (+24 more)</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr"/>
@@ -11383,7 +11402,7 @@
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>59% of 262 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite (+1 more)</t>
+          <t>59% of 262 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget (+3 more)</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr"/>
@@ -11503,7 +11522,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>66% of 502 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
+          <t>66% of 502 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr"/>
@@ -11619,7 +11638,7 @@
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>6% of 263 lines in 1 key file(s) run by: test_w39_qa_suite</t>
+          <t>6% of 260 lines in 1 key file(s) run by: test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr"/>
@@ -11735,7 +11754,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>56% of 496 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
+          <t>57% of 504 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr"/>
@@ -11855,7 +11874,7 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>31% of 1274 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>31% of 1382 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr"/>
@@ -12191,7 +12210,7 @@
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>test_postmarket_scores_a_seeded_session_end_to_end; test_postmarket_refuses_a_session_that_is_a_copy_of_the_previous_one | 36% of 1105 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>test_postmarket_scores_a_seeded_session_end_to_end; test_postmarket_refuses_a_session_that_is_a_copy_of_the_previous_one | 35% of 1213 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr"/>
@@ -12303,7 +12322,7 @@
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>29% of 1559 lines in 4 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_fundamentals_screener, test_job_monitoring, test_signal_pipeline, test_w38_platform_compliance, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>28% of 1667 lines in 4 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_fundamentals_screener, test_job_monitoring, test_signal_pipeline, test_w38_platform_compliance, test_w39_history, test_w39_notify_transactions (+2 more)</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr"/>
@@ -12419,7 +12438,7 @@
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>72% of 692 lines in 2 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
+          <t>78% of 692 lines in 2 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_mcp, test_w39_qa_suite, test_w39_research</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr"/>
@@ -12535,7 +12554,7 @@
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>72% of 692 lines in 2 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_qa_suite</t>
+          <t>78% of 692 lines in 2 key file(s) run by: test_fii_dii_and_delivery_factor, test_market_health, test_regressions, test_w39_mcp, test_w39_qa_suite, test_w39_research</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr"/>
@@ -12867,7 +12886,7 @@
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>31% of 870 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_risk_gateway, test_w39_ui_smoke</t>
+          <t>40% of 881 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr"/>
@@ -12987,7 +13006,7 @@
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>40% of 1221 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+4 more)</t>
+          <t>39% of 1329 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+6 more)</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr"/>
@@ -13107,7 +13126,7 @@
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>61% of 917 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests (+13 more)</t>
+          <t>60% of 919 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+26 more)</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr"/>
@@ -13227,7 +13246,7 @@
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>75% of 461 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
+          <t>76% of 469 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr"/>
@@ -13343,7 +13362,7 @@
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>70% of 807 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_exec_data_tests (+6 more)</t>
+          <t>70% of 807 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_exec_data_tests (+7 more)</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr"/>
@@ -13463,7 +13482,7 @@
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr"/>
@@ -13583,7 +13602,7 @@
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr"/>
@@ -13807,7 +13826,7 @@
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>70% of 229 lines in 1 key file(s) run by: test_corporate_actions, test_w39_performance_detail, test_wealth_performance</t>
+          <t>70% of 229 lines in 1 key file(s) run by: test_corporate_actions, test_w39_history, test_w39_performance_detail, test_w39_research, test_w39b_merge, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr"/>
@@ -14035,7 +14054,7 @@
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>41% of 1228 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>40% of 1336 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr"/>
@@ -14155,7 +14174,7 @@
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>83% of 440 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
+          <t>83% of 448 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr"/>
@@ -14267,7 +14286,7 @@
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>26% of 529 lines in 2 key file(s) run by: test_w39_qa_suite, test_w39_untested_modules</t>
+          <t>27% of 526 lines in 2 key file(s) run by: test_w39_qa_suite, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr"/>
@@ -14379,7 +14398,7 @@
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>50% of 1122 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
+          <t>57% of 1159 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr"/>
@@ -16315,7 +16334,7 @@
       </c>
       <c r="Y110" s="2" t="inlineStr">
         <is>
-          <t>87% of 404 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+26 more)</t>
+          <t>87% of 412 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
         </is>
       </c>
       <c r="Z110" s="2" t="inlineStr"/>
@@ -17243,7 +17262,7 @@
       </c>
       <c r="Y118" s="2" t="inlineStr">
         <is>
-          <t>84% of 105 lines in 1 key file(s) run by: test_index_feed, test_w39_index_constituents, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings (+2 more)</t>
+          <t>85% of 105 lines in 1 key file(s) run by: test_index_feed, test_w39_index_constituents, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings (+2 more)</t>
         </is>
       </c>
       <c r="Z118" s="2" t="inlineStr"/>
@@ -18515,7 +18534,7 @@
       </c>
       <c r="Y129" s="2" t="inlineStr">
         <is>
-          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite (+4 more)</t>
+          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_perf_budget, test_w39_performance_detail (+5 more)</t>
         </is>
       </c>
       <c r="Z129" s="2" t="inlineStr"/>
@@ -19635,7 +19654,7 @@
       </c>
       <c r="Y139" s="2" t="inlineStr">
         <is>
-          <t>31% of 823 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_risk_gateway, test_w39_ui_smoke</t>
+          <t>40% of 834 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
         </is>
       </c>
       <c r="Z139" s="2" t="inlineStr"/>
@@ -21403,7 +21422,7 @@
       </c>
       <c r="Y154" s="2" t="inlineStr">
         <is>
-          <t>32% of 1241 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>33% of 1349 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_intraday, test_w39_notify_transactions, test_w39_qa_suite (+1 more)</t>
         </is>
       </c>
       <c r="Z154" s="2" t="inlineStr"/>
@@ -23179,7 +23198,7 @@
       </c>
       <c r="Y169" s="2" t="inlineStr">
         <is>
-          <t>14% of 367 lines in 2 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_ui_smoke</t>
+          <t>16% of 367 lines in 2 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_screener_nl, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z169" s="2" t="inlineStr"/>
@@ -23295,7 +23314,7 @@
       </c>
       <c r="Y170" s="2" t="inlineStr">
         <is>
-          <t>26% of 198 lines in 1 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_ui_smoke</t>
+          <t>29% of 198 lines in 1 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_screener_nl, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z170" s="2" t="inlineStr"/>
@@ -23527,7 +23546,7 @@
       </c>
       <c r="Y172" s="2" t="inlineStr">
         <is>
-          <t>34% of 1303 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w36_ml_strategy_tooling, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>34% of 1411 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w36_ml_strategy_tooling, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite (+2 more)</t>
         </is>
       </c>
       <c r="Z172" s="2" t="inlineStr"/>
@@ -25027,7 +25046,7 @@
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>52% of 933 lines in 3 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
+          <t>52% of 933 lines in 3 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr"/>
@@ -25255,7 +25274,7 @@
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_perf_budget (+3 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr"/>
@@ -27567,7 +27586,7 @@
       </c>
       <c r="Y207" s="2" t="inlineStr">
         <is>
-          <t>43% of 101 lines in 1 key file(s) run by: test_w39_untested_modules</t>
+          <t>43% of 101 lines in 1 key file(s) run by: test_w39_market_pulse, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z207" s="2" t="inlineStr"/>
@@ -28751,7 +28770,7 @@
       </c>
       <c r="Y217" s="2" t="inlineStr">
         <is>
-          <t>44% of 1303 lines in 4 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live (+2 more)</t>
+          <t>49% of 1316 lines in 4 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live (+5 more)</t>
         </is>
       </c>
       <c r="Z217" s="2" t="inlineStr"/>
@@ -29895,7 +29914,7 @@
       </c>
       <c r="Y227" s="2" t="inlineStr">
         <is>
-          <t>41% of 1458 lines in 6 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w37_brokers_multi_asset (+7 more)</t>
+          <t>47% of 1469 lines in 6 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w37_brokers_multi_asset (+11 more)</t>
         </is>
       </c>
       <c r="Z227" s="2" t="inlineStr"/>
@@ -30359,7 +30378,7 @@
       </c>
       <c r="Y231" s="2" t="inlineStr">
         <is>
-          <t>39% of 373 lines in 3 key file(s) run by: test_auto_recover, test_w37_brokers_multi_asset, test_w39_api_contract, test_w39_risk_gateway</t>
+          <t>49% of 375 lines in 3 key file(s) run by: test_auto_recover, test_w37_brokers_multi_asset, test_w39_api_contract, test_w39_depth20, test_w39_risk_gateway</t>
         </is>
       </c>
       <c r="Z231" s="2" t="inlineStr"/>
@@ -31543,7 +31562,7 @@
       </c>
       <c r="Y241" s="2" t="inlineStr">
         <is>
-          <t>48% of 231 lines in 2 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_perf_budget, test_w39_ui_smoke</t>
+          <t>48% of 231 lines in 2 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_depth20, test_w39_event_calendar, test_w39_global_sync, test_w39_intraday, test_w39_market_pulse, test_w39_perf_budget (+6 more)</t>
         </is>
       </c>
       <c r="Z241" s="2" t="inlineStr"/>
@@ -32267,7 +32286,7 @@
       </c>
       <c r="Y247" s="2" t="inlineStr">
         <is>
-          <t>34% of 1313 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>33% of 1421 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z247" s="2" t="inlineStr"/>
@@ -32507,7 +32526,7 @@
       </c>
       <c r="Y249" s="2" t="inlineStr">
         <is>
-          <t>test_a_deprecated_v1_resource_warns_then_answers_410_after_sunset | 59% of 657 lines in 3 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface, test_w39_ops_tests, test_w39_owner_notes (+7 more)</t>
+          <t>test_a_deprecated_v1_resource_warns_then_answers_410_after_sunset | 59% of 657 lines in 3 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+20 more)</t>
         </is>
       </c>
       <c r="Z249" s="2" t="inlineStr"/>
@@ -33799,7 +33818,7 @@
       </c>
       <c r="Y260" s="2" t="inlineStr">
         <is>
-          <t>71% of 254 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface, test_w39_ops_tests, test_w39_owner_notes (+7 more)</t>
+          <t>71% of 254 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+20 more)</t>
         </is>
       </c>
       <c r="Z260" s="2" t="inlineStr"/>
@@ -33915,7 +33934,7 @@
       </c>
       <c r="Y261" s="2" t="inlineStr">
         <is>
-          <t>44% of 206 lines in 2 key file(s) run by: test_auto_recover, test_regressions, test_risk_controls, test_w38_platform_compliance, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface (+7 more)</t>
+          <t>44% of 206 lines in 2 key file(s) run by: test_auto_recover, test_regressions, test_risk_controls, test_w38_platform_compliance, test_w39_api_contract, test_w39_backtest, test_w39_delivery, test_w39_depth20 (+22 more)</t>
         </is>
       </c>
       <c r="Z261" s="2" t="inlineStr"/>
@@ -34031,7 +34050,7 @@
       </c>
       <c r="Y262" s="2" t="inlineStr">
         <is>
-          <t>36% of 1233 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>35% of 1341 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget (+2 more)</t>
         </is>
       </c>
       <c r="Z262" s="2" t="inlineStr"/>
@@ -34147,7 +34166,7 @@
       </c>
       <c r="Y263" s="2" t="inlineStr">
         <is>
-          <t>24% of 1121 lines in 4 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_risk_gateway, test_w39_ui_smoke</t>
+          <t>31% of 1132 lines in 4 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
         </is>
       </c>
       <c r="Z263" s="2" t="inlineStr"/>
@@ -34495,7 +34514,7 @@
       </c>
       <c r="Y266" s="2" t="inlineStr">
         <is>
-          <t>18% of 390 lines in 2 key file(s) run by: test_w39_qa_suite</t>
+          <t>18% of 387 lines in 2 key file(s) run by: test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z266" s="2" t="inlineStr"/>
@@ -34611,7 +34630,7 @@
       </c>
       <c r="Y267" s="2" t="inlineStr">
         <is>
-          <t>65% of 221 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway</t>
+          <t>65% of 221 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite (+1 more)</t>
         </is>
       </c>
       <c r="Z267" s="2" t="inlineStr"/>
@@ -34723,7 +34742,7 @@
       </c>
       <c r="Y268" s="2" t="inlineStr">
         <is>
-          <t>75% of 207 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_planning</t>
+          <t>75% of 207 lines in 1 key file(s) run by: test_w39_notify_transactions, test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z268" s="2" t="inlineStr"/>
@@ -34839,7 +34858,7 @@
       </c>
       <c r="Y269" s="2" t="inlineStr">
         <is>
-          <t>76% of 373 lines in 2 key file(s) run by: test_w39_perf_budget, test_w39_performance_detail, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_performance, test_wealth_planning</t>
+          <t>77% of 373 lines in 2 key file(s) run by: test_w39_notify_transactions, test_w39_perf_budget, test_w39_performance_detail, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_performance, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z269" s="2" t="inlineStr"/>
@@ -34955,7 +34974,7 @@
       </c>
       <c r="Y270" s="2" t="inlineStr">
         <is>
-          <t>77% of 324 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_math, test_wealth_planning</t>
+          <t>77% of 324 lines in 1 key file(s) run by: test_w39_notify_transactions, test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings, test_wealth_math, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z270" s="2" t="inlineStr"/>
@@ -35071,7 +35090,7 @@
       </c>
       <c r="Y271" s="2" t="inlineStr">
         <is>
-          <t>83% of 347 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_math, test_wealth_planning</t>
+          <t>83% of 347 lines in 1 key file(s) run by: test_w39_notify_transactions, test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_math, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z271" s="2" t="inlineStr"/>
@@ -35187,7 +35206,7 @@
       </c>
       <c r="Y272" s="2" t="inlineStr">
         <is>
-          <t>87% of 239 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_planning</t>
+          <t>87% of 239 lines in 1 key file(s) run by: test_w39_notify_transactions, test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z272" s="2" t="inlineStr"/>
@@ -35303,7 +35322,7 @@
       </c>
       <c r="Y273" s="2" t="inlineStr">
         <is>
-          <t>89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
+          <t>89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z273" s="2" t="inlineStr"/>
@@ -35535,7 +35554,7 @@
       </c>
       <c r="Y275" s="2" t="inlineStr">
         <is>
-          <t>77% of 244 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_planning</t>
+          <t>81% of 245 lines in 1 key file(s) run by: test_w39_notify_transactions, test_w39_perf_budget, test_w39_ui_smoke, test_wealth_api_security, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z275" s="2" t="inlineStr"/>
@@ -35651,7 +35670,7 @@
       </c>
       <c r="Y276" s="2" t="inlineStr">
         <is>
-          <t>75% of 204 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_exec_data_tests, test_w39_ml_regime_lineage_surface, test_w39_ops_tests, test_w39_owner_notes (+7 more)</t>
+          <t>75% of 204 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+20 more)</t>
         </is>
       </c>
       <c r="Z276" s="2" t="inlineStr"/>
@@ -35999,7 +36018,7 @@
       </c>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 75% of 299 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance, test_wealth_planning</t>
+          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 76% of 314 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance (+1 more)</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr"/>
@@ -37507,7 +37526,7 @@
       </c>
       <c r="Y292" s="2" t="inlineStr">
         <is>
-          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
+          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z292" s="2" t="inlineStr"/>
@@ -37576,22 +37595,22 @@
       <c r="M293" s="2" t="inlineStr"/>
       <c r="N293" s="2" t="inlineStr">
         <is>
-          <t>tools/dhan_token_refresh.py (RenewToken, else TOTP + PIN generateAccessToken, writes config or vault); W39: scheduler job daily at dhan_token_refresh_time (06:45) + start-up renewal when the token is dead (it ran only from a Windows task, so on macOS the token expired daily); config template keys</t>
+          <t>tools/dhan_token_refresh.py (RenewToken with the documented dhanClientId header, else TOTP + PIN generateAccessToken; writes config or vault), run daily at 06:30 and at login by the macOS LaunchAgent com.atip.dhan-token-refresh (W39, PR #4) and at 08:00 by the Windows task. W39b's own scheduler job was dropped on merging #4 (two renewals a day)</t>
         </is>
       </c>
       <c r="O293" s="2" t="inlineStr">
         <is>
-          <t>Owner: add dhan_pin + dhan_totp_secret (or vault them) once</t>
+          <t>Owner: add dhan_pin + dhan_totp_secret (or vault them) once; run deploy/launchd/install.sh token</t>
         </is>
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>pipeline/w39_jobs.py; tools/dhan_token_refresh.py</t>
+          <t>tools/dhan_token_refresh.py; deploy/launchd/com.atip.dhan-token-refresh.plist</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
         <is>
-          <t>test_token_renewal_is_scheduled_and_runs_at_start_only_when_needed; test_refresher_only_if_invalid_keeps_a_working_token</t>
+          <t>tests/test_dhan_token_refresh.py</t>
         </is>
       </c>
       <c r="R293" s="2" t="inlineStr">
@@ -37613,7 +37632,7 @@
       </c>
       <c r="W293" s="2" t="inlineStr">
         <is>
-          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+          <t>Delivered by W39 (PR #4, merged to master 2026-10-08); independent validation PENDING</t>
         </is>
       </c>
       <c r="X293" s="2" t="inlineStr">
@@ -37623,7 +37642,7 @@
       </c>
       <c r="Y293" s="2" t="inlineStr">
         <is>
-          <t>test_token_renewal_is_scheduled_and_runs_at_start_only_when_needed; test_refresher_only_if_invalid_keeps_a_working_token | 60% of 178 lines in 2 key file(s) run by: test_w38_platform_compliance, test_w39_owner_notes</t>
+          <t>tests/test_dhan_token_refresh.py | 71% of 105 lines in 1 key file(s) run by: test_dhan_token_refresh, test_w38_platform_compliance</t>
         </is>
       </c>
       <c r="Z293" s="2" t="inlineStr">
@@ -37690,28 +37709,28 @@
       </c>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M294" s="2" t="inlineStr"/>
       <c r="N294" s="2" t="inlineStr">
         <is>
-          <t>W39: data/history_backfill.py year-window backfill of the tracked universe + indices (resumable, remembers listing dates, retries refused windows); weekly purge now keeps prices_daily for history_years (it deleted everything older than 600 days); main.py --backfill-history; weekly Sunday top-up; /api/data/history/status</t>
+          <t>W39 (PR #4, its DP-11): data/history_backfill.py walks each tracked symbol back to 7 years in 365-day windows, resumable (prices_daily_backfill), listing-aware, nightly 22:20 (40 symbols); db/purge.py HISTORY tier keeps prices_daily / ai_scores / predictions 7 years. W39b fix on merge: old windows are stored with today's corporate-action basis. W39b's own backfill was dropped</t>
         </is>
       </c>
       <c r="O294" s="2" t="inlineStr">
         <is>
-          <t>Owner: run python main.py --backfill-history once (Dhan API, ~30-40 min for 500 symbols)</t>
+          <t>Owner: Dhan Data API subscription; the Nifty 500 completes in ~2 weeks of nightly runs</t>
         </is>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>data/history_backfill.py; db/purge.py</t>
+          <t>data/history_backfill.py; db/purge.py; data/dhan.py</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
         <is>
-          <t>test_plan_asks_only_for_the_missing_years_in_shared_windows; test_backfill_stores_through_the_fetcher_and_remembers_listing_dates; test_the_purge_keeps_price_history_for_history_years</t>
+          <t>tests/test_w39_history.py; tests/test_w39b_merge.py</t>
         </is>
       </c>
       <c r="R294" s="2" t="inlineStr">
@@ -37733,7 +37752,7 @@
       </c>
       <c r="W294" s="2" t="inlineStr">
         <is>
-          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+          <t>Delivered by W39 (PR #4, merged to master 2026-10-08); independent validation PENDING</t>
         </is>
       </c>
       <c r="X294" s="2" t="inlineStr">
@@ -37743,7 +37762,7 @@
       </c>
       <c r="Y294" s="2" t="inlineStr">
         <is>
-          <t>test_plan_asks_only_for_the_missing_years_in_shared_windows; test_backfill_stores_through_the_fetcher_and_remembers_listing_dates; test_the_purge_keeps_price_history_for_history_years | 82% of 249 lines in 2 key file(s) run by: test_w39_ops_tests, test_w39_owner_notes</t>
+          <t>tests/test_w39_history.py; tests/test_w39b_merge.py | 50% of 1001 lines in 3 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests (+3 more)</t>
         </is>
       </c>
       <c r="Z294" s="2" t="inlineStr"/>
@@ -37975,7 +37994,7 @@
       </c>
       <c r="Y296" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_risk_gateway.py | 46% of 1606 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+6 more)</t>
+          <t>tests/test_w39_risk_gateway.py | 50% of 1617 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+9 more)</t>
         </is>
       </c>
       <c r="Z296" s="2" t="inlineStr"/>
@@ -38439,7 +38458,7 @@
       </c>
       <c r="Y300" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_ml_regime_lineage_surface.py | 76% of 140 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_ml_regime_lineage_surface</t>
+          <t>tests/test_w39_ml_regime_lineage_surface.py | 86% of 140 lines in 1 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_ml_regime_lineage_surface, test_w39_options</t>
         </is>
       </c>
       <c r="Z300" s="2" t="inlineStr"/>
@@ -39363,7 +39382,7 @@
       </c>
       <c r="Y308" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py; tests/test_w39_notify_transactions.py | 87% of 149 lines in 1 key file(s) run by: test_w39_retail, test_w39_ui_smoke</t>
+          <t>tests/test_w39_retail.py; tests/test_w39_notify_transactions.py | 89% of 150 lines in 1 key file(s) run by: test_w39_notify_transactions, test_w39_retail, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z308" s="2" t="inlineStr"/>
@@ -39484,8 +39503,2212 @@
       </c>
       <c r="Z309" s="2" t="inlineStr"/>
     </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>W39-RS</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>Equity research reports (RS-01..10)</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>Institutional-style valuation, targets, ratings, reports with disclosures and tracked calls</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J310" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K310" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L310" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="inlineStr"/>
+      <c r="N310" s="2" t="inlineStr">
+        <is>
+          <t>research/valuation.py (DCF + scenarios + sensitivity, justified P/B, peer / own-history multiples); research/report.py (12-month targets, ratings, SEBI-style disclosures, calls and hit rate); nightly 20:40</t>
+        </is>
+      </c>
+      <c r="O310" s="2" t="inlineStr">
+        <is>
+          <t>No consensus estimates feed; XBRL key lines only (no 3-statement model); hit rates start from the first report and need PaRRVA review before being shown to others</t>
+        </is>
+      </c>
+      <c r="P310" s="2" t="inlineStr">
+        <is>
+          <t>research/valuation.py; research/report.py</t>
+        </is>
+      </c>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_research.py</t>
+        </is>
+      </c>
+      <c r="R310" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S310" s="2" t="inlineStr"/>
+      <c r="T310" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U310" s="2" t="inlineStr"/>
+      <c r="V310" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W310" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X310" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y310" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_research.py | 90% of 554 lines in 2 key file(s) run by: test_w39_mcp, test_w39_research, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+        </is>
+      </c>
+      <c r="Z310" s="2" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>W39-SCREENER</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>Stock screener: fundamental + technical (SC-20)</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>Query screener with presets, saved screens and alerts</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J311" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K311" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L311" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="inlineStr"/>
+      <c r="N311" s="2" t="inlineStr">
+        <is>
+          <t>research/screener.py: query language (precedence, NOT, IN, aliases), presets, saved screens with new-match alerts, CSV; /screener</t>
+        </is>
+      </c>
+      <c r="O311" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA</t>
+        </is>
+      </c>
+      <c r="P311" s="2" t="inlineStr">
+        <is>
+          <t>research/screener.py</t>
+        </is>
+      </c>
+      <c r="Q311" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_screener.py</t>
+        </is>
+      </c>
+      <c r="R311" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S311" s="2" t="inlineStr"/>
+      <c r="T311" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U311" s="2" t="inlineStr"/>
+      <c r="V311" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W311" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X311" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y311" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_screener.py | 90% of 427 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_screener_nl, test_w39_technicals (+1 more)</t>
+        </is>
+      </c>
+      <c r="Z311" s="2" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>W39-OPTIONS</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>Derivatives</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>Options strategy builder (OP-01..05)</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>Payoff, breakevens, POP and Greeks for multi-leg strategies</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J312" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K312" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L312" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="inlineStr"/>
+      <c r="N312" s="2" t="inlineStr">
+        <is>
+          <t>quant/options_strategy.py: templates, payoff and breakevens, POP, Greeks, implied IV, chain pricing; POST /api/options/(build|analyse)</t>
+        </is>
+      </c>
+      <c r="O312" s="2" t="inlineStr">
+        <is>
+          <t>Analysis only: one-click execution needs the live OMS and the owner's explicit go-ahead</t>
+        </is>
+      </c>
+      <c r="P312" s="2" t="inlineStr">
+        <is>
+          <t>quant/options_strategy.py</t>
+        </is>
+      </c>
+      <c r="Q312" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_options.py</t>
+        </is>
+      </c>
+      <c r="R312" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S312" s="2" t="inlineStr"/>
+      <c r="T312" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U312" s="2" t="inlineStr"/>
+      <c r="V312" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W312" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X312" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y312" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_options.py | 88% of 209 lines in 1 key file(s) run by: test_w39_options</t>
+        </is>
+      </c>
+      <c r="Z312" s="2" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>W39-TECH</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Technical scans, ratings and signals (TA-01..04)</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>30 scans, 19 candle patterns, technical / RS ratings, signals with ATR levels and confluence</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J313" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K313" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L313" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="inlineStr"/>
+      <c r="N313" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py + research/tech_signals.py: scans, patterns, ratings, signals with entry / stop / target, confluence, outcomes (TARGET / STOPPED / EXPIRED); nightly 20:30</t>
+        </is>
+      </c>
+      <c r="O313" s="2" t="inlineStr">
+        <is>
+          <t>Trust a scan only after ~30 closed signals (records start on the first run)</t>
+        </is>
+      </c>
+      <c r="P313" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py; research/tech_signals.py</t>
+        </is>
+      </c>
+      <c r="Q313" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_technicals.py</t>
+        </is>
+      </c>
+      <c r="R313" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S313" s="2" t="inlineStr"/>
+      <c r="T313" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U313" s="2" t="inlineStr"/>
+      <c r="V313" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W313" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X313" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y313" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_technicals.py | 87% of 765 lines in 2 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener (+3 more)</t>
+        </is>
+      </c>
+      <c r="Z313" s="2" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>W39-PULSE</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Market Intelligence</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Market pulse (MP-01..05)</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>Global-cue model, GIFT gap, FII flow pressure, participant OI, OI walls</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J314" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K314" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="inlineStr"/>
+      <c r="N314" s="2" t="inlineStr">
+        <is>
+          <t>research/market_pulse.py + data/participant_oi.py: global-cue model, basis-free GIFT gap, FII streak / absorption, NSE participant OI positioning, OI walls; /market-pulse</t>
+        </is>
+      </c>
+      <c r="O314" s="2" t="inlineStr">
+        <is>
+          <t>Needs Nifty + global history loaded, Dhan index quotes for GIFT, NSE reachable for participant OI</t>
+        </is>
+      </c>
+      <c r="P314" s="2" t="inlineStr">
+        <is>
+          <t>research/market_pulse.py; data/participant_oi.py</t>
+        </is>
+      </c>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_market_pulse.py</t>
+        </is>
+      </c>
+      <c r="R314" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S314" s="2" t="inlineStr"/>
+      <c r="T314" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U314" s="2" t="inlineStr"/>
+      <c r="V314" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W314" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X314" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y314" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_market_pulse.py | 70% of 529 lines in 2 key file(s) run by: test_w39_event_calendar, test_w39_global_sync, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate</t>
+        </is>
+      </c>
+      <c r="Z314" s="2" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>W39-REGIME</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Market Intelligence</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>Market regime gate (RG-01..04)</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>Distribution / follow-through days, 200-DMA, signals tagged with or against the market</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J315" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K315" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L315" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="inlineStr"/>
+      <c r="N315" s="2" t="inlineStr">
+        <is>
+          <t>research/regime_gate.py: OPEN / CAUTION / CLOSED gate, signals tagged and never alerted against it, 'does the gate help' record</t>
+        </is>
+      </c>
+      <c r="O315" s="2" t="inlineStr">
+        <is>
+          <t>Thresholds are ATIP's choices (IBD tradition); evidence needs 30+ closed signals per side</t>
+        </is>
+      </c>
+      <c r="P315" s="2" t="inlineStr">
+        <is>
+          <t>research/regime_gate.py</t>
+        </is>
+      </c>
+      <c r="Q315" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_regime_gate.py</t>
+        </is>
+      </c>
+      <c r="R315" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S315" s="2" t="inlineStr"/>
+      <c r="T315" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U315" s="2" t="inlineStr"/>
+      <c r="V315" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W315" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X315" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y315" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_regime_gate.py | 83% of 248 lines in 1 key file(s) run by: test_w39_delivery, test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_technicals (+2 more)</t>
+        </is>
+      </c>
+      <c r="Z315" s="2" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>W39-TRACK</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>Signal track record by regime and horizon (TR-01..03)</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>5/20/60-session returns vs the Nifty per signal, by scan x gate and confluence</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J316" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K316" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L316" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="inlineStr"/>
+      <c r="N316" s="2" t="inlineStr">
+        <is>
+          <t>research/tech_signals.py forward returns and stats, shown next to today's signals</t>
+        </is>
+      </c>
+      <c r="O316" s="2" t="inlineStr">
+        <is>
+          <t>Useful after a few months of signals</t>
+        </is>
+      </c>
+      <c r="P316" s="2" t="inlineStr">
+        <is>
+          <t>research/tech_signals.py</t>
+        </is>
+      </c>
+      <c r="Q316" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_track_record.py</t>
+        </is>
+      </c>
+      <c r="R316" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S316" s="2" t="inlineStr"/>
+      <c r="T316" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U316" s="2" t="inlineStr"/>
+      <c r="V316" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W316" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X316" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y316" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_track_record.py | 84% of 506 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+2 more)</t>
+        </is>
+      </c>
+      <c r="Z316" s="2" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>W39-WEEKLY</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>Weekly technical rating (WK-01..02)</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>Weekly rating on completed weeks; daily / weekly agreement</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J317" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K317" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="inlineStr"/>
+      <c r="N317" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py weekly bars, rating, agreement as screener field and signal attribute</t>
+        </is>
+      </c>
+      <c r="O317" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA</t>
+        </is>
+      </c>
+      <c r="P317" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py</t>
+        </is>
+      </c>
+      <c r="Q317" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_weekly.py</t>
+        </is>
+      </c>
+      <c r="R317" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S317" s="2" t="inlineStr"/>
+      <c r="T317" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U317" s="2" t="inlineStr"/>
+      <c r="V317" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W317" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X317" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y317" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_weekly.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+        </is>
+      </c>
+      <c r="Z317" s="2" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>W39-PATTERNS</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>Chart patterns from swing pivots (CP-01..03)</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>Darvas box, VCP, double bottom, ascending triangle, head and shoulders</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J318" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K318" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L318" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M318" s="2" t="inlineStr"/>
+      <c r="N318" s="2" t="inlineStr">
+        <is>
+          <t>research/patterns.py: patterns as scans with levels, screener setups, alerts held until a positive 30-signal record</t>
+        </is>
+      </c>
+      <c r="O318" s="2" t="inlineStr">
+        <is>
+          <t>Rule-based approximations; no inverse H&amp;S, descending triangles, channels or wedges yet</t>
+        </is>
+      </c>
+      <c r="P318" s="2" t="inlineStr">
+        <is>
+          <t>research/patterns.py</t>
+        </is>
+      </c>
+      <c r="Q318" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_patterns.py</t>
+        </is>
+      </c>
+      <c r="R318" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S318" s="2" t="inlineStr"/>
+      <c r="T318" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U318" s="2" t="inlineStr"/>
+      <c r="V318" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W318" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X318" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y318" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_patterns.py | 92% of 216 lines in 1 key file(s) run by: test_w39_delivery, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+        </is>
+      </c>
+      <c r="Z318" s="2" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>W39-RSLINE</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>RS-line new highs and size-group RS ranks (RL-01..02)</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>RS line new highs (also before price); RS ranks within AMFI size groups</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J319" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K319" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L319" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M319" s="2" t="inlineStr"/>
+      <c r="N319" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py RS line; AMFI size groups from shares x price</t>
+        </is>
+      </c>
+      <c r="O319" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA</t>
+        </is>
+      </c>
+      <c r="P319" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py</t>
+        </is>
+      </c>
+      <c r="Q319" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_rs_line.py</t>
+        </is>
+      </c>
+      <c r="R319" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S319" s="2" t="inlineStr"/>
+      <c r="T319" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U319" s="2" t="inlineStr"/>
+      <c r="V319" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W319" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X319" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y319" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_rs_line.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+        </is>
+      </c>
+      <c r="Z319" s="2" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>W39-DELIVERY</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>Delivery-% spike scan (DL-01)</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>NSE delivery percentage spike as a scan and screener field</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J320" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K320" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L320" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="inlineStr"/>
+      <c r="N320" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py delivery spike scan, snapshot fields, preset</t>
+        </is>
+      </c>
+      <c r="O320" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py</t>
+        </is>
+      </c>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_delivery.py</t>
+        </is>
+      </c>
+      <c r="R320" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S320" s="2" t="inlineStr"/>
+      <c r="T320" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U320" s="2" t="inlineStr"/>
+      <c r="V320" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W320" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X320" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y320" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_delivery.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+        </is>
+      </c>
+      <c r="Z320" s="2" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>W39-SCORECARD</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>Explainable fundamental scorecard (FS-01..03)</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>5 axes x 6 pass / fail checks with their numbers, stored nightly with a record vs the Nifty</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J321" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K321" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L321" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="inlineStr"/>
+      <c r="N321" s="2" t="inlineStr">
+        <is>
+          <t>research/scorecard.py: value, earnings, growth, dividend, balance-sheet checks; screener fields and presets; nightly 20:50</t>
+        </is>
+      </c>
+      <c r="O321" s="2" t="inlineStr">
+        <is>
+          <t>Reported (not forecast) growth; banks / NBFCs miss six checks by design; record needs months</t>
+        </is>
+      </c>
+      <c r="P321" s="2" t="inlineStr">
+        <is>
+          <t>research/scorecard.py</t>
+        </is>
+      </c>
+      <c r="Q321" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_scorecard.py</t>
+        </is>
+      </c>
+      <c r="R321" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S321" s="2" t="inlineStr"/>
+      <c r="T321" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U321" s="2" t="inlineStr"/>
+      <c r="V321" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W321" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X321" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y321" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_scorecard.py | 89% of 413 lines in 1 key file(s) run by: test_w39_mcp, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+        </is>
+      </c>
+      <c r="Z321" s="2" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>W39-EVENTS</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>Market Intelligence</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>Macro event calendar (EV-01..03)</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>FOMC, US CPI, payrolls, RBI dates; the NSE session each hits; gap band widening</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J322" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K322" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L322" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="inlineStr"/>
+      <c r="N322" s="2" t="inlineStr">
+        <is>
+          <t>research/event_calendar.py: seeded dates, config / API additions, band widened after US releases</t>
+        </is>
+      </c>
+      <c r="O322" s="2" t="inlineStr">
+        <is>
+          <t>Seeded dates reach end-2026 (RBI Feb-2027): add next year's dates each December</t>
+        </is>
+      </c>
+      <c r="P322" s="2" t="inlineStr">
+        <is>
+          <t>research/event_calendar.py</t>
+        </is>
+      </c>
+      <c r="Q322" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_event_calendar.py</t>
+        </is>
+      </c>
+      <c r="R322" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S322" s="2" t="inlineStr"/>
+      <c r="T322" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U322" s="2" t="inlineStr"/>
+      <c r="V322" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W322" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X322" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y322" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_event_calendar.py | 85% of 159 lines in 1 key file(s) run by: test_w39_event_calendar, test_w39_global_sync, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate</t>
+        </is>
+      </c>
+      <c r="Z322" s="2" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>W39-INTRADAY</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>Intraday scans on 15-minute bars (IN-01..03)</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>Opening-range breakout, open = low / high, intraday squeeze with a record to the close</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J323" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K323" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L323" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="inlineStr"/>
+      <c r="N323" s="2" t="inlineStr">
+        <is>
+          <t>research/intraday_signals.py; every 15 minutes 09:45-15:50</t>
+        </is>
+      </c>
+      <c r="O323" s="2" t="inlineStr">
+        <is>
+          <t>Needs the Dhan Data API (15-minute bars) and 3 sessions of stored bars</t>
+        </is>
+      </c>
+      <c r="P323" s="2" t="inlineStr">
+        <is>
+          <t>research/intraday_signals.py</t>
+        </is>
+      </c>
+      <c r="Q323" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_intraday.py</t>
+        </is>
+      </c>
+      <c r="R323" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S323" s="2" t="inlineStr"/>
+      <c r="T323" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U323" s="2" t="inlineStr"/>
+      <c r="V323" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W323" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X323" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y323" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_intraday.py | 87% of 225 lines in 1 key file(s) run by: test_w39_intraday, test_w39_mcp</t>
+        </is>
+      </c>
+      <c r="Z323" s="2" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>W39-DEPTH20</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>Data Platform</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>20-level depth and depth-weighted imbalance (DP-01..03)</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>Dhan 20-level depth WebSocket, DWI, persistent flags, validation</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J324" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K324" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L324" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M324" s="2" t="inlineStr"/>
+      <c r="N324" s="2" t="inlineStr">
+        <is>
+          <t>data/depth20.py: depth feed (off by default), DWI, logistic validation vs the next 1 / 5 minutes</t>
+        </is>
+      </c>
+      <c r="O324" s="2" t="inlineStr">
+        <is>
+          <t>Owner: depth20.enabled and the Dhan Data API; no order-flow imbalance yet</t>
+        </is>
+      </c>
+      <c r="P324" s="2" t="inlineStr">
+        <is>
+          <t>data/depth20.py</t>
+        </is>
+      </c>
+      <c r="Q324" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_depth20.py</t>
+        </is>
+      </c>
+      <c r="R324" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S324" s="2" t="inlineStr"/>
+      <c r="T324" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U324" s="2" t="inlineStr"/>
+      <c r="V324" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W324" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X324" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y324" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_depth20.py | 76% of 282 lines in 1 key file(s) run by: test_w39_depth20</t>
+        </is>
+      </c>
+      <c r="Z324" s="2" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>W39-GLOBALSYNC</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>Market Intelligence</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>Synchronised global-cue model (GS-01..03)</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>15:30 / 08:45 snapshots of global futures, Asia and FX; the opening gap modelled on them</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J325" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K325" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L325" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M325" s="2" t="inlineStr"/>
+      <c r="N325" s="2" t="inlineStr">
+        <is>
+          <t>research/global_sync.py: snapshots, walk-forward record vs GIFT</t>
+        </is>
+      </c>
+      <c r="O325" s="2" t="inlineStr">
+        <is>
+          <t>Needs 40 mornings of snapshots (~2 months)</t>
+        </is>
+      </c>
+      <c r="P325" s="2" t="inlineStr">
+        <is>
+          <t>research/global_sync.py</t>
+        </is>
+      </c>
+      <c r="Q325" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_global_sync.py</t>
+        </is>
+      </c>
+      <c r="R325" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S325" s="2" t="inlineStr"/>
+      <c r="T325" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U325" s="2" t="inlineStr"/>
+      <c r="V325" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W325" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X325" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y325" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_global_sync.py | 84% of 128 lines in 1 key file(s) run by: test_w39_event_calendar, test_w39_global_sync, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate</t>
+        </is>
+      </c>
+      <c r="Z325" s="2" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>W39-NLSCREEN</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>English to screener query (NL-01..03)</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>Plain-English screener queries, validated and never run unseen</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J326" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K326" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L326" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="inlineStr"/>
+      <c r="N326" s="2" t="inlineStr">
+        <is>
+          <t>research/screener_nl.py: Claude path when enabled, rule translator otherwise; POST /api/screener/ask</t>
+        </is>
+      </c>
+      <c r="O326" s="2" t="inlineStr">
+        <is>
+          <t>Claude path needs a working Anthropic key (KD-001)</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="inlineStr">
+        <is>
+          <t>research/screener_nl.py</t>
+        </is>
+      </c>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_screener_nl.py</t>
+        </is>
+      </c>
+      <c r="R326" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S326" s="2" t="inlineStr"/>
+      <c r="T326" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U326" s="2" t="inlineStr"/>
+      <c r="V326" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W326" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X326" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y326" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_screener_nl.py | 95% of 199 lines in 1 key file(s) run by: test_w39_screener_nl</t>
+        </is>
+      </c>
+      <c r="Z326" s="2" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>W39-MCP</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>APIs</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>Read-only ATIP MCP server (MC-01..03)</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>12 read-only tools over stdio on a query-only database connection</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J327" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K327" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr"/>
+      <c r="N327" s="2" t="inlineStr">
+        <is>
+          <t>tools/atip_mcp.py</t>
+        </is>
+      </c>
+      <c r="O327" s="2" t="inlineStr">
+        <is>
+          <t>Local stdio only (no hosted transport)</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="inlineStr">
+        <is>
+          <t>tools/atip_mcp.py</t>
+        </is>
+      </c>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_mcp.py</t>
+        </is>
+      </c>
+      <c r="R327" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S327" s="2" t="inlineStr"/>
+      <c r="T327" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U327" s="2" t="inlineStr"/>
+      <c r="V327" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W327" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X327" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y327" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_mcp.py | 83% of 184 lines in 1 key file(s) run by: test_w39_mcp</t>
+        </is>
+      </c>
+      <c r="Z327" s="2" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>W39-ORDERBOOK</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>Market Intelligence</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Order-book pressure and open orders (OB-01..03)</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>Market-wide pending buy / sell pressure; a read-only view of your open orders</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J328" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K328" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr"/>
+      <c r="N328" s="2" t="inlineStr">
+        <is>
+          <t>data/order_pressure.py (every 15 minutes, market hours); portfolio/open_orders.py</t>
+        </is>
+      </c>
+      <c r="O328" s="2" t="inlineStr">
+        <is>
+          <t>Needs the Dhan Data API; context, not a signal</t>
+        </is>
+      </c>
+      <c r="P328" s="2" t="inlineStr">
+        <is>
+          <t>data/order_pressure.py; portfolio/open_orders.py</t>
+        </is>
+      </c>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_market_pulse.py</t>
+        </is>
+      </c>
+      <c r="R328" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S328" s="2" t="inlineStr"/>
+      <c r="T328" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U328" s="2" t="inlineStr"/>
+      <c r="V328" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W328" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X328" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y328" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_market_pulse.py | 56% of 190 lines in 2 key file(s) run by: test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+        </is>
+      </c>
+      <c r="Z328" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z309"/>
+  <autoFilter ref="A1:Z328"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39496,7 +41719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:Z51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39770,7 +41993,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 75% of 299 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance, test_wealth_planning</t>
+          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 76% of 314 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance (+1 more)</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -41278,7 +43501,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
+          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr"/>
@@ -41347,22 +43570,22 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>tools/dhan_token_refresh.py (RenewToken, else TOTP + PIN generateAccessToken, writes config or vault); W39: scheduler job daily at dhan_token_refresh_time (06:45) + start-up renewal when the token is dead (it ran only from a Windows task, so on macOS the token expired daily); config template keys</t>
+          <t>tools/dhan_token_refresh.py (RenewToken with the documented dhanClientId header, else TOTP + PIN generateAccessToken; writes config or vault), run daily at 06:30 and at login by the macOS LaunchAgent com.atip.dhan-token-refresh (W39, PR #4) and at 08:00 by the Windows task. W39b's own scheduler job was dropped on merging #4 (two renewals a day)</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Owner: add dhan_pin + dhan_totp_secret (or vault them) once</t>
+          <t>Owner: add dhan_pin + dhan_totp_secret (or vault them) once; run deploy/launchd/install.sh token</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>pipeline/w39_jobs.py; tools/dhan_token_refresh.py</t>
+          <t>tools/dhan_token_refresh.py; deploy/launchd/com.atip.dhan-token-refresh.plist</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>test_token_renewal_is_scheduled_and_runs_at_start_only_when_needed; test_refresher_only_if_invalid_keeps_a_working_token</t>
+          <t>tests/test_dhan_token_refresh.py</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -41384,7 +43607,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+          <t>Delivered by W39 (PR #4, merged to master 2026-10-08); independent validation PENDING</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -41394,7 +43617,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>test_token_renewal_is_scheduled_and_runs_at_start_only_when_needed; test_refresher_only_if_invalid_keeps_a_working_token | 60% of 178 lines in 2 key file(s) run by: test_w38_platform_compliance, test_w39_owner_notes</t>
+          <t>tests/test_dhan_token_refresh.py | 71% of 105 lines in 1 key file(s) run by: test_dhan_token_refresh, test_w38_platform_compliance</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -41461,28 +43684,28 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>W39: data/history_backfill.py year-window backfill of the tracked universe + indices (resumable, remembers listing dates, retries refused windows); weekly purge now keeps prices_daily for history_years (it deleted everything older than 600 days); main.py --backfill-history; weekly Sunday top-up; /api/data/history/status</t>
+          <t>W39 (PR #4, its DP-11): data/history_backfill.py walks each tracked symbol back to 7 years in 365-day windows, resumable (prices_daily_backfill), listing-aware, nightly 22:20 (40 symbols); db/purge.py HISTORY tier keeps prices_daily / ai_scores / predictions 7 years. W39b fix on merge: old windows are stored with today's corporate-action basis. W39b's own backfill was dropped</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Owner: run python main.py --backfill-history once (Dhan API, ~30-40 min for 500 symbols)</t>
+          <t>Owner: Dhan Data API subscription; the Nifty 500 completes in ~2 weeks of nightly runs</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>data/history_backfill.py; db/purge.py</t>
+          <t>data/history_backfill.py; db/purge.py; data/dhan.py</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>test_plan_asks_only_for_the_missing_years_in_shared_windows; test_backfill_stores_through_the_fetcher_and_remembers_listing_dates; test_the_purge_keeps_price_history_for_history_years</t>
+          <t>tests/test_w39_history.py; tests/test_w39b_merge.py</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -41504,7 +43727,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+          <t>Delivered by W39 (PR #4, merged to master 2026-10-08); independent validation PENDING</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
@@ -41514,7 +43737,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>test_plan_asks_only_for_the_missing_years_in_shared_windows; test_backfill_stores_through_the_fetcher_and_remembers_listing_dates; test_the_purge_keeps_price_history_for_history_years | 82% of 249 lines in 2 key file(s) run by: test_w39_ops_tests, test_w39_owner_notes</t>
+          <t>tests/test_w39_history.py; tests/test_w39b_merge.py | 50% of 1001 lines in 3 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests (+3 more)</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr"/>
@@ -41746,7 +43969,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_risk_gateway.py | 46% of 1606 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+6 more)</t>
+          <t>tests/test_w39_risk_gateway.py | 50% of 1617 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+9 more)</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr"/>
@@ -42210,7 +44433,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_ml_regime_lineage_surface.py | 76% of 140 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_ml_regime_lineage_surface</t>
+          <t>tests/test_w39_ml_regime_lineage_surface.py | 86% of 140 lines in 1 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_ml_regime_lineage_surface, test_w39_options</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr"/>
@@ -43134,7 +45357,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_retail.py; tests/test_w39_notify_transactions.py | 87% of 149 lines in 1 key file(s) run by: test_w39_retail, test_w39_ui_smoke</t>
+          <t>tests/test_w39_retail.py; tests/test_w39_notify_transactions.py | 89% of 150 lines in 1 key file(s) run by: test_w39_notify_transactions, test_w39_retail, test_w39_ui_smoke</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr"/>
@@ -43255,8 +45478,2212 @@
       </c>
       <c r="Z32" s="2" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>W39-RS</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Equity research reports (RS-01..10)</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Institutional-style valuation, targets, ratings, reports with disclosures and tracked calls</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J33" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>research/valuation.py (DCF + scenarios + sensitivity, justified P/B, peer / own-history multiples); research/report.py (12-month targets, ratings, SEBI-style disclosures, calls and hit rate); nightly 20:40</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>No consensus estimates feed; XBRL key lines only (no 3-statement model); hit rates start from the first report and need PaRRVA review before being shown to others</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>research/valuation.py; research/report.py</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_research.py</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_research.py | 90% of 554 lines in 2 key file(s) run by: test_w39_mcp, test_w39_research, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>W39-SCREENER</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Stock screener: fundamental + technical (SC-20)</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Query screener with presets, saved screens and alerts</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J34" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>research/screener.py: query language (precedence, NOT, IN, aliases), presets, saved screens with new-match alerts, CSV; /screener</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>research/screener.py</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_screener.py</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_screener.py | 90% of 427 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_screener_nl, test_w39_technicals (+1 more)</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>W39-OPTIONS</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Derivatives</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Options strategy builder (OP-01..05)</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Payoff, breakevens, POP and Greeks for multi-leg strategies</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J35" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>quant/options_strategy.py: templates, payoff and breakevens, POP, Greeks, implied IV, chain pricing; POST /api/options/(build|analyse)</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>Analysis only: one-click execution needs the live OMS and the owner's explicit go-ahead</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>quant/options_strategy.py</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_options.py</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_options.py | 88% of 209 lines in 1 key file(s) run by: test_w39_options</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>W39-TECH</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Technical scans, ratings and signals (TA-01..04)</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>30 scans, 19 candle patterns, technical / RS ratings, signals with ATR levels and confluence</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J36" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py + research/tech_signals.py: scans, patterns, ratings, signals with entry / stop / target, confluence, outcomes (TARGET / STOPPED / EXPIRED); nightly 20:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>Trust a scan only after ~30 closed signals (records start on the first run)</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py; research/tech_signals.py</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_technicals.py</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_technicals.py | 87% of 765 lines in 2 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener (+3 more)</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>W39-PULSE</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Market Intelligence</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Market pulse (MP-01..05)</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Global-cue model, GIFT gap, FII flow pressure, participant OI, OI walls</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J37" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>research/market_pulse.py + data/participant_oi.py: global-cue model, basis-free GIFT gap, FII streak / absorption, NSE participant OI positioning, OI walls; /market-pulse</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>Needs Nifty + global history loaded, Dhan index quotes for GIFT, NSE reachable for participant OI</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>research/market_pulse.py; data/participant_oi.py</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_market_pulse.py</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_market_pulse.py | 70% of 529 lines in 2 key file(s) run by: test_w39_event_calendar, test_w39_global_sync, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>W39-REGIME</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Market Intelligence</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Market regime gate (RG-01..04)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Distribution / follow-through days, 200-DMA, signals tagged with or against the market</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J38" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K38" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>research/regime_gate.py: OPEN / CAUTION / CLOSED gate, signals tagged and never alerted against it, 'does the gate help' record</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Thresholds are ATIP's choices (IBD tradition); evidence needs 30+ closed signals per side</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>research/regime_gate.py</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_regime_gate.py</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_regime_gate.py | 83% of 248 lines in 1 key file(s) run by: test_w39_delivery, test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_technicals (+2 more)</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>W39-TRACK</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Signal track record by regime and horizon (TR-01..03)</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>5/20/60-session returns vs the Nifty per signal, by scan x gate and confluence</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J39" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>research/tech_signals.py forward returns and stats, shown next to today's signals</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>Useful after a few months of signals</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>research/tech_signals.py</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_track_record.py</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_track_record.py | 84% of 506 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+2 more)</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>W39-WEEKLY</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Weekly technical rating (WK-01..02)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Weekly rating on completed weeks; daily / weekly agreement</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J40" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py weekly bars, rating, agreement as screener field and signal attribute</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_weekly.py</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_weekly.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>W39-PATTERNS</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Chart patterns from swing pivots (CP-01..03)</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Darvas box, VCP, double bottom, ascending triangle, head and shoulders</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J41" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>research/patterns.py: patterns as scans with levels, screener setups, alerts held until a positive 30-signal record</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Rule-based approximations; no inverse H&amp;S, descending triangles, channels or wedges yet</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>research/patterns.py</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_patterns.py</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_patterns.py | 92% of 216 lines in 1 key file(s) run by: test_w39_delivery, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>W39-RSLINE</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>RS-line new highs and size-group RS ranks (RL-01..02)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>RS line new highs (also before price); RS ranks within AMFI size groups</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J42" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py RS line; AMFI size groups from shares x price</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_rs_line.py</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_rs_line.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>W39-DELIVERY</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Delivery-% spike scan (DL-01)</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>NSE delivery percentage spike as a scan and screener field</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J43" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py delivery spike scan, snapshot fields, preset</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_delivery.py</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_delivery.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>W39-SCORECARD</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Explainable fundamental scorecard (FS-01..03)</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>5 axes x 6 pass / fail checks with their numbers, stored nightly with a record vs the Nifty</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J44" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K44" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>research/scorecard.py: value, earnings, growth, dividend, balance-sheet checks; screener fields and presets; nightly 20:50</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Reported (not forecast) growth; banks / NBFCs miss six checks by design; record needs months</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>research/scorecard.py</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_scorecard.py</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_scorecard.py | 89% of 413 lines in 1 key file(s) run by: test_w39_mcp, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>W39-EVENTS</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Market Intelligence</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Macro event calendar (EV-01..03)</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>FOMC, US CPI, payrolls, RBI dates; the NSE session each hits; gap band widening</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J45" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K45" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>research/event_calendar.py: seeded dates, config / API additions, band widened after US releases</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Seeded dates reach end-2026 (RBI Feb-2027): add next year's dates each December</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>research/event_calendar.py</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_event_calendar.py</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_event_calendar.py | 85% of 159 lines in 1 key file(s) run by: test_w39_event_calendar, test_w39_global_sync, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>W39-INTRADAY</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Intraday scans on 15-minute bars (IN-01..03)</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Opening-range breakout, open = low / high, intraday squeeze with a record to the close</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J46" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K46" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>research/intraday_signals.py; every 15 minutes 09:45-15:50</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Needs the Dhan Data API (15-minute bars) and 3 sessions of stored bars</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>research/intraday_signals.py</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_intraday.py</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_intraday.py | 87% of 225 lines in 1 key file(s) run by: test_w39_intraday, test_w39_mcp</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>W39-DEPTH20</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Data Platform</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>20-level depth and depth-weighted imbalance (DP-01..03)</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Dhan 20-level depth WebSocket, DWI, persistent flags, validation</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J47" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>data/depth20.py: depth feed (off by default), DWI, logistic validation vs the next 1 / 5 minutes</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Owner: depth20.enabled and the Dhan Data API; no order-flow imbalance yet</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>data/depth20.py</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_depth20.py</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_depth20.py | 76% of 282 lines in 1 key file(s) run by: test_w39_depth20</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>W39-GLOBALSYNC</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Market Intelligence</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Synchronised global-cue model (GS-01..03)</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>15:30 / 08:45 snapshots of global futures, Asia and FX; the opening gap modelled on them</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J48" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K48" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>research/global_sync.py: snapshots, walk-forward record vs GIFT</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Needs 40 mornings of snapshots (~2 months)</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>research/global_sync.py</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_global_sync.py</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_global_sync.py | 84% of 128 lines in 1 key file(s) run by: test_w39_event_calendar, test_w39_global_sync, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>W39-NLSCREEN</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>English to screener query (NL-01..03)</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Plain-English screener queries, validated and never run unseen</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J49" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K49" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>research/screener_nl.py: Claude path when enabled, rule translator otherwise; POST /api/screener/ask</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Claude path needs a working Anthropic key (KD-001)</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>research/screener_nl.py</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_screener_nl.py</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_screener_nl.py | 95% of 199 lines in 1 key file(s) run by: test_w39_screener_nl</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>W39-MCP</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>APIs</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Read-only ATIP MCP server (MC-01..03)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>12 read-only tools over stdio on a query-only database connection</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J50" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K50" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>tools/atip_mcp.py</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>Local stdio only (no hosted transport)</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>tools/atip_mcp.py</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_mcp.py</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_mcp.py | 83% of 184 lines in 1 key file(s) run by: test_w39_mcp</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>W39-ORDERBOOK</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Market Intelligence</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Order-book pressure and open orders (OB-01..03)</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Market-wide pending buy / sell pressure; a read-only view of your open orders</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4): docs/W39_RESEARCH_HISTORY_OPTIONS_HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J51" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K51" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>data/order_pressure.py (every 15 minutes, market hours); portfolio/open_orders.py</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>Needs the Dhan Data API; context, not a signal</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>data/order_pressure.py; portfolio/open_orders.py</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_market_pulse.py</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development), PR #4</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>W39 developed on branch ccr-643d84fc-yig8ts (PR #4), merged to master 2026-10-08; NOT DEPLOYED; independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>W39 (PR #4)</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39_market_pulse.py | 56% of 190 lines in 2 key file(s) run by: test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z32"/>
+  <autoFilter ref="A1:Z51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43677,12 +48104,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>tools/dhan_token_refresh.py (RenewToken, else TOTP + PIN generateAccessToken, writes config or vault); W39: scheduler job daily at dhan_token_refresh_time (06:45) + start-up renewal when the token is dead (it ran only from a Windows task, so on macOS the token expired daily); config template keys</t>
+          <t>tools/dhan_token_refresh.py (RenewToken with the documented dhanClientId header, else TOTP + PIN generateAccessToken; writes config or vault), run daily at 06:30 and at login by the macOS LaunchAgent com.atip.dhan-token-refresh (W39, PR #4) and at 08:00 by the Windows task. W39b's own scheduler job was dropped on merging #4 (two renewals a day)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Owner: add dhan_pin + dhan_totp_secret (or vault them) once</t>
+          <t>Owner: add dhan_pin + dhan_totp_secret (or vault them) once; run deploy/launchd/install.sh token</t>
         </is>
       </c>
     </row>
@@ -45458,7 +49885,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[2026-10-07] 33/36 features developed (1 COMPLETED, 32 awaiting independent QA); automated tests: 34 covered, 0 partly, 0 none; BLOCKED: EX-17, EX-19; open: QA-001</t>
+          <t>[2026-10-07] 52/55 features developed (1 COMPLETED, 51 awaiting independent QA); automated tests: 53 covered, 0 partly, 0 none; BLOCKED: EX-17, EX-19; open: QA-001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -45552,7 +49979,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>36</v>

--- a/docs/ATIP_Master_Deployment_Tracker_Wave_1_to_20_UPDATED.xlsx
+++ b/docs/ATIP_Master_Deployment_Tracker_Wave_1_to_20_UPDATED.xlsx
@@ -22,9 +22,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Legend" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Features'!$A$1:$Z$328</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'New Items (W39)'!$A$1:$Z$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Blockers'!$A$1:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Features'!$A$1:$Z$332</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'New Items (W39)'!$A$1:$Z$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Blockers'!$A$1:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Master Tracker'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Gap Analysis'!$A$1:$E$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Scope Exclusions'!$A$1:$C$6</definedName>
@@ -32,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'PERF-001 Detail'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Implementation Sequence'!$A$1:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Master Dev Prompt'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Owner CSV vs repo'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Owner CSV vs repo'!$A$1:$G$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -838,13 +838,13 @@
         <v>49</v>
       </c>
       <c r="C25" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
@@ -882,7 +882,7 @@
         <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1113,55 +1113,58 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>W39b (PR #5)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Developed</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>0 Delivered baseline (maintain)</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>58</v>
-      </c>
-      <c r="C42" t="n">
-        <v>58</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1 Foundation</t>
+          <t>0 Delivered baseline (maintain)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C43" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1170,14 +1173,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2 Quant Research (data, factors, backtesting)</t>
+          <t>1 Foundation</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C44" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1186,14 +1189,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3 Strategy Engine</t>
+          <t>2 Quant Research (data, factors, backtesting)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C45" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1202,78 +1205,78 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4 AI/ML</t>
+          <t>3 Strategy Engine</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C46" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5 Risk &amp; Portfolio</t>
+          <t>4 AI/ML</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C47" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6 Execution</t>
+          <t>5 Risk &amp; Portfolio</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7 Advanced Quant</t>
+          <t>6 Execution</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C49" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8 Production Hardening</t>
+          <t>7 Advanced Quant</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -1282,14 +1285,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8 Production hardening</t>
+          <t>8 Production Hardening</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -1298,49 +1301,65 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9 Enterprise SaaS (final objective)</t>
+          <t>8 Production hardening</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C52" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10 Wealth track (Waves 11-20)</t>
+          <t>9 Enterprise SaaS (final objective)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>10 Wealth track (Waves 11-20)</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>11</v>
+      </c>
+      <c r="C54" t="n">
+        <v>9</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>11 W39 reconciliation (owner tracker 2026-10-07)</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>50</v>
-      </c>
-      <c r="C54" t="n">
-        <v>48</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2</v>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="n">
+        <v>53</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2577,22 +2596,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DP-08</t>
+          <t>BT-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Derivatives data</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E2" s="18" t="inlineStr">
@@ -2602,24 +2621,24 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
+          <t>W23: robustness battery (costs x2, slippage x3, universe halves, period halves, regimes, Monte Carlo) with verdict. W39b: backtest/cpcv.py -- combinatorial purg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SE-05</t>
+          <t>DP-08</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>AI-driven strategies</t>
+          <t>Derivatives data</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -2629,71 +2648,71 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>W5 developed 2026-09-25 (incl. completion pass) — framework only, no model trained or validated; independent testing PENDING (ChatGPT); see docs/W5_AI_ML_HANDOF</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NS-05</t>
+          <t>SE-05</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Novelty/decay/source weighting</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>AI-driven strategies</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>W28b developed 2026-10-01 on branch w28b-news-weighting (on w33-wealth-qa) — independent validation PENDING (ChatGPT); see docs/W28B_NEWS_WEIGHTING_HANDOFF.md |</t>
+          <t>W5 developed 2026-09-25 (incl. completion pass) — framework only, no model trained or validated; independent testing PENDING (ChatGPT); see docs/W5_AI_ML_HANDOF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NS-06</t>
+          <t>NS-05</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Earnings call / announcement NLP</t>
+          <t>Novelty/decay/source weighting</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -2703,7 +2722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E5" s="18" t="inlineStr">
@@ -2713,7 +2732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2725,12 +2744,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ML-02</t>
+          <t>NS-06</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Deep learning</t>
+          <t>Earnings call / announcement NLP</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -2750,24 +2769,24 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W28b developed 2026-10-01 on branch w28b-news-weighting (on w33-wealth-qa) — independent validation PENDING (ChatGPT); see docs/W28B_NEWS_WEIGHTING_HANDOFF.md |</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ML-04</t>
+          <t>ML-02</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Reinforcement learning</t>
+          <t>Deep learning</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -2787,7 +2806,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2799,59 +2818,59 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PF-06</t>
+          <t>ML-04</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Rebalancing</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
+          <t>Reinforcement learning</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>W6 developed 2026-09-25 — coding only; independent testing PENDING (ChatGPT); see docs/W6_ADVANCED_QUANT_HANDOFF.md</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DP-04</t>
+          <t>PF-06</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Tick data</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Rebalancing</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
@@ -2861,24 +2880,24 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
+          <t>W6 developed 2026-09-25 — coding only; independent testing PENDING (ChatGPT); see docs/W6_ADVANCED_QUANT_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DP-05</t>
+          <t>DP-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Order book / depth</t>
+          <t>Tick data</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -2910,22 +2929,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AF-06</t>
+          <t>DP-05</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Derivatives factors</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>Order book / depth</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
@@ -2935,34 +2954,34 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EX-11</t>
+          <t>AF-06</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Execution algos</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Derivatives factors</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -2977,19 +2996,19 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>W34 developed 2026-10-01 on branch w34-execution-microstructure — independent validation PENDING (ChatGPT); see docs/W34_EXECUTION_MICROSTRUCTURE_HANDOFF.md | W</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EX-12</t>
+          <t>EX-11</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Market impact model</t>
+          <t>Execution algos</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -3021,12 +3040,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EX-15</t>
+          <t>EX-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Latency telemetry</t>
+          <t>Market impact model</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
@@ -3058,12 +3077,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EX-16</t>
+          <t>EX-15</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Event-driven OMS</t>
+          <t>Latency telemetry</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -3073,7 +3092,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" s="18" t="inlineStr">
@@ -3095,12 +3114,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BT-17</t>
+          <t>EX-16</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Event-driven backtester</t>
+          <t>Event-driven OMS</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
@@ -3110,7 +3129,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E16" s="18" t="inlineStr">
@@ -3132,12 +3151,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>DP-14</t>
+          <t>BT-17</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Macroeconomic data</t>
+          <t>Event-driven backtester</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -3162,19 +3181,19 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
+          <t>W34 developed 2026-10-01 on branch w34-execution-microstructure — independent validation PENDING (ChatGPT); see docs/W34_EXECUTION_MICROSTRUCTURE_HANDOFF.md | W</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AD-01</t>
+          <t>DP-14</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Alt-data framework</t>
+          <t>Macroeconomic data</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -3206,12 +3225,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AD-02</t>
+          <t>AD-01</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Alt-data sources</t>
+          <t>Alt-data framework</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -3231,7 +3250,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3243,12 +3262,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DP-22</t>
+          <t>AD-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Point-in-time data lake</t>
+          <t>Alt-data sources</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -3258,7 +3277,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
@@ -3268,7 +3287,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3280,12 +3299,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DP-21</t>
+          <t>DP-22</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Multi-asset data</t>
+          <t>Point-in-time data lake</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -3295,7 +3314,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
@@ -3305,71 +3324,71 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check: AMFI mutual-</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>API-05</t>
+          <t>DP-21</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>API contracts/docs</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
+          <t>Multi-asset data</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check: AMFI mutual-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>API-06</t>
+          <t>API-05</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Widget JSON schemas</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>API contracts/docs</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
@@ -3379,24 +3398,24 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>DBS-05</t>
+          <t>API-06</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Scalable database</t>
+          <t>Widget JSON schemas</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
@@ -3406,7 +3425,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
@@ -3416,24 +3435,24 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ENT-06</t>
+          <t>DBS-05</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Per-user broker credential vault</t>
+          <t>Scalable database</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
@@ -3453,24 +3472,24 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
+          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ENT-14</t>
+          <t>ENT-06</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Regulatory approvals</t>
+          <t>Per-user broker credential vault</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
@@ -3483,31 +3502,31 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
+          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SEC-05</t>
+          <t>ENT-14</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Compliance monitoring</t>
+          <t>Regulatory approvals</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
@@ -3520,14 +3539,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3539,12 +3558,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ENT-17</t>
+          <t>SEC-05</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Data privacy</t>
+          <t>Compliance monitoring</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
@@ -3564,7 +3583,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3576,133 +3595,133 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ENT-04</t>
+          <t>ENT-17</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Subscriptions &amp; billing</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>Data privacy</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>W7 developed 2026-09-25 (enterprise layer, off by default) — coding only; independent testing PENDING (ChatGPT); see docs/W7_ENTERPRISE_HANDOFF.md</t>
+          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ENT-09</t>
+          <t>ENT-04</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Mobile apps</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Subscriptions &amp; billing</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
+          <t>W7 developed 2026-09-25 (enterprise layer, off by default) — coding only; independent testing PENDING (ChatGPT); see docs/W7_ENTERPRISE_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>API-03</t>
+          <t>ENT-09</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Versioned public API</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
+          <t>Mobile apps</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
-        </is>
-      </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
+          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>PF-12</t>
+          <t>API-03</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Multi-broker import</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Versioned public API</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
@@ -3712,24 +3731,24 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
+          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>BR-07</t>
+          <t>PF-12</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Additional brokers</t>
+          <t>Multi-broker import</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
@@ -3749,7 +3768,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3761,12 +3780,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ENT-15</t>
+          <t>BR-07</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Multi-asset trading</t>
+          <t>Additional brokers</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
@@ -3798,12 +3817,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>SE-10</t>
+          <t>ENT-15</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>No/low-code strategy builder</t>
+          <t>Multi-asset trading</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
@@ -3823,24 +3842,24 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ML-16</t>
+          <t>SE-10</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>AI chat assistant</t>
+          <t>No/low-code strategy builder</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
@@ -3872,12 +3891,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>OPS-04</t>
+          <t>ML-16</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Cloud deployment</t>
+          <t>AI chat assistant</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
@@ -3897,165 +3916,202 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ENT-16</t>
+          <t>OPS-04</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Scalability, HA &amp; observability</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>Cloud deployment</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
+          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>PERF-001</t>
+          <t>ENT-16</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Investor performance attribution</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+          <t>Scalability, HA &amp; observability</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>branch w20-release; merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
+          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>QA-001</t>
+          <t>PERF-001</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Wealth QA / security / performance</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>Investor performance attribution</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>RC line = w33-wealth-qa (W11-W32); merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
+          <t>branch w20-release; merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>QA-001</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Wealth QA / security / performance</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>RC line = w33-wealth-qa (W11-W32); merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>UAT-001</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Beta / UAT</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E41" s="19" t="inlineStr">
+      <c r="E42" s="19" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>RC line = w33-wealth-qa; merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G41"/>
+  <autoFilter ref="A1:G42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4228,7 +4284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z328"/>
+  <dimension ref="A1:Z332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4698,7 +4754,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>92% of 24 lines in 1 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_regressions, test_risk_controls (+15 more)</t>
+          <t>92% of 24 lines in 1 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_regressions, test_risk_controls (+21 more)</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
@@ -6050,7 +6106,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>86% of 335 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
+          <t>86% of 346 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr"/>
@@ -6154,7 +6210,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>35% of 1213 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>35% of 1222 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+1 more)</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr"/>
@@ -6882,7 +6938,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -6986,7 +7042,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr"/>
@@ -7090,7 +7146,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr"/>
@@ -7194,7 +7250,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr"/>
@@ -7506,7 +7562,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>68% of 184 lines in 1 key file(s) run by: test_strategy_live</t>
+          <t>70% of 195 lines in 1 key file(s) run by: test_strategy_live</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr"/>
@@ -7610,7 +7666,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>92% of 153 lines in 1 key file(s) run by: test_aggressive_backtest, test_aggressive_decisions, test_aggressive_lifecycle, test_strategy_live</t>
+          <t>92% of 156 lines in 1 key file(s) run by: test_aggressive_backtest, test_aggressive_decisions, test_aggressive_lifecycle, test_strategy_live</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr"/>
@@ -7714,7 +7770,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>92% of 153 lines in 1 key file(s) run by: test_aggressive_backtest, test_aggressive_decisions, test_aggressive_lifecycle, test_strategy_live</t>
+          <t>92% of 156 lines in 1 key file(s) run by: test_aggressive_backtest, test_aggressive_decisions, test_aggressive_lifecycle, test_strategy_live</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr"/>
@@ -7818,7 +7874,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>92% of 153 lines in 1 key file(s) run by: test_aggressive_backtest, test_aggressive_decisions, test_aggressive_lifecycle, test_strategy_live</t>
+          <t>92% of 156 lines in 1 key file(s) run by: test_aggressive_backtest, test_aggressive_decisions, test_aggressive_lifecycle, test_strategy_live</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr"/>
@@ -8338,7 +8394,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr"/>
@@ -8442,7 +8498,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr"/>
@@ -8546,7 +8602,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr"/>
@@ -8650,7 +8706,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr"/>
@@ -8754,7 +8810,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr"/>
@@ -8858,7 +8914,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr"/>
@@ -8962,7 +9018,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr"/>
@@ -9066,7 +9122,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr"/>
@@ -9170,7 +9226,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr"/>
@@ -9274,7 +9330,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr"/>
@@ -9378,7 +9434,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr"/>
@@ -9586,7 +9642,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>62% of 785 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+22 more)</t>
+          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr"/>
@@ -9690,7 +9746,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>93% of 43 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w38_platform_compliance, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+18 more)</t>
+          <t>93% of 43 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w38_platform_compliance, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+24 more)</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr"/>
@@ -9794,7 +9850,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>86% of 335 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
+          <t>86% of 346 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr"/>
@@ -10018,7 +10074,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>37% of 202 lines in 2 key file(s) run by: test_regressions, test_risk_controls, test_w37_brokers_multi_asset, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_perf_budget, test_w39_ui_smoke</t>
+          <t>36% of 202 lines in 2 key file(s) run by: test_regressions, test_risk_controls, test_w37_brokers_multi_asset, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_perf_budget, test_w39_ui_smoke (+1 more)</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr"/>
@@ -10122,7 +10178,7 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>76% of 234 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_index_feed, test_w39_notify_transactions</t>
+          <t>78% of 234 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_index_feed, test_risk_controls, test_w39_notify_transactions</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr"/>
@@ -10242,7 +10298,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>65% of 360 lines in 2 key file(s) run by: test_auto_recover, test_w39_ops_tests, test_w39_perf_budget</t>
+          <t>69% of 360 lines in 2 key file(s) run by: test_auto_recover, test_w39_ops_tests, test_w39_perf_budget, test_w39b_razorpay</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr"/>
@@ -10566,7 +10622,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>47% of 3154 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+7 more)</t>
+          <t>47% of 3163 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+8 more)</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr"/>
@@ -10686,7 +10742,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>85% of 925 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
+          <t>85% of 936 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr"/>
@@ -10806,7 +10862,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>47% of 3154 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+7 more)</t>
+          <t>47% of 3163 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+8 more)</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr"/>
@@ -10926,7 +10982,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>72% of 1094 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
+          <t>72% of 1105 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr"/>
@@ -11042,7 +11098,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>46% of 1548 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
+          <t>46% of 1568 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr"/>
@@ -11162,7 +11218,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>39% of 1329 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+6 more)</t>
+          <t>39% of 1338 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+7 more)</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr"/>
@@ -11282,7 +11338,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>61% of 1047 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_api_contract, test_w39_backtest (+24 more)</t>
+          <t>64% of 1070 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_api_contract, test_w39_backtest (+31 more)</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr"/>
@@ -11522,7 +11578,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>66% of 502 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
+          <t>66% of 502 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr"/>
@@ -11754,7 +11810,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>57% of 504 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
+          <t>57% of 515 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr"/>
@@ -11874,7 +11930,7 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>31% of 1382 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>31% of 1391 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+1 more)</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr"/>
@@ -12210,7 +12266,7 @@
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>test_postmarket_scores_a_seeded_session_end_to_end; test_postmarket_refuses_a_session_that_is_a_copy_of_the_previous_one | 35% of 1213 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>test_postmarket_scores_a_seeded_session_end_to_end; test_postmarket_refuses_a_session_that_is_a_copy_of_the_previous_one | 35% of 1222 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+1 more)</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr"/>
@@ -12322,7 +12378,7 @@
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>28% of 1667 lines in 4 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_fundamentals_screener, test_job_monitoring, test_signal_pipeline, test_w38_platform_compliance, test_w39_history, test_w39_notify_transactions (+2 more)</t>
+          <t>30% of 1676 lines in 4 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_fundamentals_screener, test_job_monitoring, test_signal_pipeline, test_w38_platform_compliance, test_w39_history, test_w39_notify_transactions (+3 more)</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr"/>
@@ -12886,7 +12942,7 @@
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>40% of 881 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
+          <t>41% of 881 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr"/>
@@ -13006,7 +13062,7 @@
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>39% of 1329 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+6 more)</t>
+          <t>39% of 1338 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+7 more)</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr"/>
@@ -13126,7 +13182,7 @@
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>60% of 919 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+26 more)</t>
+          <t>63% of 942 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+33 more)</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr"/>
@@ -13246,7 +13302,7 @@
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>76% of 469 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
+          <t>76% of 480 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr"/>
@@ -13362,7 +13418,7 @@
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>70% of 807 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_exec_data_tests (+7 more)</t>
+          <t>70% of 807 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_exec_data_tests (+8 more)</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr"/>
@@ -13482,7 +13538,7 @@
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr"/>
@@ -13602,7 +13658,7 @@
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr"/>
@@ -14054,7 +14110,7 @@
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>40% of 1336 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>40% of 1345 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+1 more)</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr"/>
@@ -14174,7 +14230,7 @@
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>83% of 448 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
+          <t>83% of 459 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr"/>
@@ -14398,7 +14454,7 @@
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>57% of 1159 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
+          <t>58% of 1170 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr"/>
@@ -16334,7 +16390,7 @@
       </c>
       <c r="Y110" s="2" t="inlineStr">
         <is>
-          <t>87% of 412 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+47 more)</t>
+          <t>87% of 423 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
         </is>
       </c>
       <c r="Z110" s="2" t="inlineStr"/>
@@ -16454,7 +16510,7 @@
       </c>
       <c r="Y111" s="2" t="inlineStr">
         <is>
-          <t>92% of 363 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
+          <t>92% of 364 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z111" s="2" t="inlineStr"/>
@@ -16574,7 +16630,7 @@
       </c>
       <c r="Y112" s="2" t="inlineStr">
         <is>
-          <t>95% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_wealth_performance</t>
+          <t>96% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo, test_w39b_mf_analytics, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z112" s="2" t="inlineStr"/>
@@ -16694,7 +16750,7 @@
       </c>
       <c r="Y113" s="2" t="inlineStr">
         <is>
-          <t>95% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_wealth_performance</t>
+          <t>96% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo, test_w39b_mf_analytics, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z113" s="2" t="inlineStr"/>
@@ -16806,7 +16862,7 @@
       </c>
       <c r="Y114" s="2" t="inlineStr">
         <is>
-          <t>95% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_wealth_performance</t>
+          <t>96% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo, test_w39b_mf_analytics, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z114" s="2" t="inlineStr"/>
@@ -16922,7 +16978,7 @@
       </c>
       <c r="Y115" s="2" t="inlineStr">
         <is>
-          <t>87% of 84 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_contract_note_fees, test_w39_performance_detail, test_w39_qa_suite, test_wealth_performance, test_wealth_planning</t>
+          <t>87% of 84 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_contract_note_fees, test_w39_performance_detail, test_w39_qa_suite, test_w39b_cpcv_pbo, test_wealth_performance (+1 more)</t>
         </is>
       </c>
       <c r="Z115" s="2" t="inlineStr"/>
@@ -17042,7 +17098,7 @@
       </c>
       <c r="Y116" s="2" t="inlineStr">
         <is>
-          <t>69% of 29 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
+          <t>69% of 29 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z116" s="2" t="inlineStr"/>
@@ -17158,7 +17214,7 @@
       </c>
       <c r="Y117" s="2" t="inlineStr">
         <is>
-          <t>56% of 36 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
+          <t>56% of 36 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z117" s="2" t="inlineStr"/>
@@ -17262,7 +17318,7 @@
       </c>
       <c r="Y118" s="2" t="inlineStr">
         <is>
-          <t>85% of 105 lines in 1 key file(s) run by: test_index_feed, test_w39_index_constituents, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_ui_smoke, test_wealth_api_security, test_wealth_dna_holdings (+2 more)</t>
+          <t>87% of 105 lines in 1 key file(s) run by: test_index_feed, test_w39_index_constituents, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_ui_smoke, test_w39b_tf75, test_wealth_api_security (+3 more)</t>
         </is>
       </c>
       <c r="Z118" s="2" t="inlineStr"/>
@@ -17382,7 +17438,7 @@
       </c>
       <c r="Y119" s="2" t="inlineStr">
         <is>
-          <t>91% of 499 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio</t>
+          <t>91% of 500 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z119" s="2" t="inlineStr"/>
@@ -17502,7 +17558,7 @@
       </c>
       <c r="Y120" s="2" t="inlineStr">
         <is>
-          <t>81% of 175 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
+          <t>81% of 175 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z120" s="2" t="inlineStr"/>
@@ -17622,7 +17678,7 @@
       </c>
       <c r="Y121" s="2" t="inlineStr">
         <is>
-          <t>82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial</t>
+          <t>82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z121" s="2" t="inlineStr"/>
@@ -17798,9 +17854,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K123" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K123" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
@@ -17854,7 +17910,7 @@
       </c>
       <c r="Y123" s="2" t="inlineStr">
         <is>
-          <t>45% of 197 lines in 1 key file(s) run by: test_w39_backtest, test_w39_qa_suite, test_w39_untested_modules</t>
+          <t>71% of 197 lines in 1 key file(s) run by: test_w39_backtest, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z123" s="2" t="inlineStr"/>
@@ -17927,12 +17983,12 @@
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>W23: one-at-a-time sensitivity curves, stability, knife-edge flags, 2-D heat map</t>
+          <t>W23: one-at-a-time sensitivity curves, stability, knife-edge flags, 2-D heat map. W39b: a +-1 step neighbour with fewer than min_trades trades (or a failed run) is listed in thin_neighbours / thin_edges (study summary and CLI too) instead of vanishing; knife_edge and robust_share still compare only neighbours that have a metric</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Independent QA</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
@@ -17942,7 +17998,7 @@
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>branch w23-research-backtest</t>
+          <t>test_a_neighbour_that_stops_trading_is_a_thin_edge_not_a_knife_edge; test_stability_and_knife_edge_by_hand (tests/test_w39_qa_suite.py)</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr"/>
@@ -17960,7 +18016,7 @@
       </c>
       <c r="W124" s="2" t="inlineStr">
         <is>
-          <t>W39 QA finding (owner methodology call): a neighbouring parameter value with too few trades is ignored, so 'stops trading one step away' is not flagged as a knife edge (backtest/sensitivity.py)</t>
+          <t>W39 QA finding (owner methodology call): a neighbouring parameter value with too few trades is ignored, so 'stops trading one step away' is not flagged as a knife edge (backtest/sensitivity.py) | W39 QA finding (methodology call): 'stops trading one step away' was not flagged. W39b decision: report it as a separate thin-edge fragility flag rather than a knife edge, so robust_share keeps its meaning</t>
         </is>
       </c>
       <c r="X124" s="2" t="inlineStr">
@@ -17970,7 +18026,7 @@
       </c>
       <c r="Y124" s="2" t="inlineStr">
         <is>
-          <t>100% of 70 lines in 1 key file(s) run by: test_w39_qa_suite</t>
+          <t>test_a_neighbour_that_stops_trading_is_a_thin_edge_not_a_knife_edge; test_stability_and_knife_edge_by_hand (tests/test_w39_qa_suite.py) | 100% of 71 lines in 1 key file(s) run by: test_w39_qa_suite</t>
         </is>
       </c>
       <c r="Z124" s="2" t="inlineStr"/>
@@ -18026,14 +18082,14 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K125" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K125" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -18043,22 +18099,22 @@
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>W23: robustness battery (costs x2, slippage x3, universe halves, period halves, regimes, Monte Carlo) with verdict</t>
+          <t>W23: robustness battery (costs x2, slippage x3, universe halves, period halves, regimes, Monte Carlo) with verdict. W39b: backtest/cpcv.py -- combinatorial purged cross-validation (N groups, k test groups, purge + embargo per AFML 7.4, C(N-1,k-1) out-of-sample paths with their distribution) and PBO by CSCV (Bailey et al.: logits, degradation regression, probability of loss; from a matrix or an optimisation's trials); python -m backtest cpcv | pbo; POST /api/backtests/cpcv and /api/backtests/{id}/pbo</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Independent QA; the stochastic-dominance test is not implemented; CPCV runs on the W2 engine only</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>backtest/robustness.py</t>
+          <t>backtest/robustness.py; backtest/cpcv.py</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>branch w23-research-backtest</t>
+          <t>tests/test_w39b_cpcv_pbo.py</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr"/>
@@ -18071,7 +18127,7 @@
       <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W125" s="2" t="inlineStr"/>
@@ -18082,7 +18138,7 @@
       </c>
       <c r="Y125" s="2" t="inlineStr">
         <is>
-          <t>45% of 175 lines in 1 key file(s) run by: test_w39_backtest</t>
+          <t>tests/test_w39b_cpcv_pbo.py | 79% of 531 lines in 2 key file(s) run by: test_w39_backtest, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z125" s="2" t="inlineStr"/>
@@ -18314,7 +18370,7 @@
       </c>
       <c r="Y127" s="2" t="inlineStr">
         <is>
-          <t>32% of 257 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
+          <t>32% of 257 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z127" s="2" t="inlineStr"/>
@@ -18426,7 +18482,7 @@
       </c>
       <c r="Y128" s="2" t="inlineStr">
         <is>
-          <t>32% of 257 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite</t>
+          <t>32% of 257 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z128" s="2" t="inlineStr"/>
@@ -19654,7 +19710,7 @@
       </c>
       <c r="Y139" s="2" t="inlineStr">
         <is>
-          <t>40% of 834 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
+          <t>41% of 834 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
         </is>
       </c>
       <c r="Z139" s="2" t="inlineStr"/>
@@ -21422,7 +21478,7 @@
       </c>
       <c r="Y154" s="2" t="inlineStr">
         <is>
-          <t>33% of 1349 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_intraday, test_w39_notify_transactions, test_w39_qa_suite (+1 more)</t>
+          <t>33% of 1358 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_intraday, test_w39_notify_transactions, test_w39_qa_suite (+2 more)</t>
         </is>
       </c>
       <c r="Z154" s="2" t="inlineStr"/>
@@ -23546,7 +23602,7 @@
       </c>
       <c r="Y172" s="2" t="inlineStr">
         <is>
-          <t>34% of 1411 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w36_ml_strategy_tooling, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite (+2 more)</t>
+          <t>34% of 1420 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w36_ml_strategy_tooling, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite (+3 more)</t>
         </is>
       </c>
       <c r="Z172" s="2" t="inlineStr"/>
@@ -25046,7 +25102,7 @@
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>52% of 933 lines in 3 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
+          <t>52% of 933 lines in 3 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr"/>
@@ -25274,7 +25330,7 @@
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+4 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr"/>
@@ -25584,12 +25640,12 @@
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
-          <t>Independent QA; the event-driven engine (BT-17) still trades whole positions (it says so)</t>
+          <t>Independent QA. W39b: the event-driven engine (BT-17) now trades ADD / REDUCE too, through its own order model</t>
         </is>
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>portfolio/optimize.py; strategy_engine/kinds.py; backtest/engine.py; strategy_engine/adapter.py</t>
+          <t>portfolio/optimize.py; strategy_engine/kinds.py; backtest/engine.py; backtest/event_driven.py; strategy_engine/adapter.py</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -25626,7 +25682,7 @@
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_backtest_partial.py | 68% of 1355 lines in 4 key file(s) run by: test_auto_recover, test_signal_pipeline, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio</t>
+          <t>tests/test_w39_backtest_partial.py | 73% of 1784 lines in 5 key file(s) run by: test_auto_recover, test_signal_pipeline, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr"/>
@@ -25962,7 +26018,7 @@
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>39% of 437 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_wealth_math, test_wealth_performance</t>
+          <t>39% of 437 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_w39b_mf_analytics, test_wealth_math (+1 more)</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr"/>
@@ -28658,7 +28714,7 @@
       </c>
       <c r="Y216" s="2" t="inlineStr">
         <is>
-          <t>72% of 101 lines in 1 key file(s) run by: test_w39_backtest_partial, test_w39_performance_detail, test_w39_untested_modules</t>
+          <t>71% of 101 lines in 1 key file(s) run by: test_w39_backtest_partial, test_w39_performance_detail, test_w39_untested_modules</t>
         </is>
       </c>
       <c r="Z216" s="2" t="inlineStr"/>
@@ -28770,7 +28826,7 @@
       </c>
       <c r="Y217" s="2" t="inlineStr">
         <is>
-          <t>49% of 1316 lines in 4 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live (+5 more)</t>
+          <t>50% of 1316 lines in 4 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live (+5 more)</t>
         </is>
       </c>
       <c r="Z217" s="2" t="inlineStr"/>
@@ -28959,12 +29015,12 @@
       </c>
       <c r="N219" s="2" t="inlineStr">
         <is>
-          <t>W34: backtest/event_driven.py -- event queue over daily or intraday bars; latency, partial fills vs bar volume, MARKET/LIMIT/STOP, impact-priced fills, TWAP slices, intrabar protective exits; same Strategy interface; stored as kind event_driven</t>
+          <t>W34: backtest/event_driven.py -- event queue over daily or intraday bars; latency, partial fills vs bar volume, MARKET/LIMIT/STOP, impact-priced fills, TWAP slices, intrabar protective exits; same Strategy interface; stored as kind event_driven. W39b: ADD / REDUCE through the order model (matches the W2 engine leg for leg on a hand-computed case; BUY / SELL-only runs byte-identical); fix: a SELL with nothing left to sell (a max-hold exit queued on the bar a stop fired) was charged costs and a fill, an over-sized SELL was charged on its full size, and a slow max-hold exit was queued again every session</t>
         </is>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
-          <t>Independent QA; compare with engine on the same config</t>
+          <t>Independent QA; the engine does not yet report the adapter's skipped decisions the way W2 does</t>
         </is>
       </c>
       <c r="P219" s="2" t="inlineStr">
@@ -28974,7 +29030,7 @@
       </c>
       <c r="Q219" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tests/test_w39_backtest_partial.py (test_event_driven_*)</t>
         </is>
       </c>
       <c r="R219" s="2" t="inlineStr"/>
@@ -28987,7 +29043,7 @@
       <c r="U219" s="2" t="inlineStr"/>
       <c r="V219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W219" s="2" t="inlineStr">
@@ -29002,7 +29058,7 @@
       </c>
       <c r="Y219" s="2" t="inlineStr">
         <is>
-          <t>65% of 407 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest_partial</t>
+          <t>tests/test_w39_backtest_partial.py (test_event_driven_*) | 79% of 532 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest_partial</t>
         </is>
       </c>
       <c r="Z219" s="2" t="inlineStr"/>
@@ -29914,7 +29970,7 @@
       </c>
       <c r="Y227" s="2" t="inlineStr">
         <is>
-          <t>47% of 1469 lines in 6 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w37_brokers_multi_asset (+11 more)</t>
+          <t>47% of 1469 lines in 6 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w37_brokers_multi_asset (+12 more)</t>
         </is>
       </c>
       <c r="Z227" s="2" t="inlineStr"/>
@@ -30378,7 +30434,7 @@
       </c>
       <c r="Y231" s="2" t="inlineStr">
         <is>
-          <t>49% of 375 lines in 3 key file(s) run by: test_auto_recover, test_w37_brokers_multi_asset, test_w39_api_contract, test_w39_depth20, test_w39_risk_gateway</t>
+          <t>49% of 377 lines in 3 key file(s) run by: test_auto_recover, test_w37_brokers_multi_asset, test_w39_api_contract, test_w39_depth20, test_w39_risk_gateway</t>
         </is>
       </c>
       <c r="Z231" s="2" t="inlineStr"/>
@@ -30494,7 +30550,7 @@
       </c>
       <c r="Y232" s="2" t="inlineStr">
         <is>
-          <t>67% of 486 lines in 4 key file(s) run by: test_mysql_backend, test_postgres_backend, test_w38_platform_compliance, test_w39_perf_budget</t>
+          <t>67% of 486 lines in 4 key file(s) run by: test_mysql_backend, test_postgres_backend, test_w38_platform_compliance, test_w39_perf_budget, test_w39b_razorpay</t>
         </is>
       </c>
       <c r="Z232" s="2" t="inlineStr"/>
@@ -30734,7 +30790,7 @@
       </c>
       <c r="Y234" s="2" t="inlineStr">
         <is>
-          <t>24% of 513 lines in 3 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_risk_gateway</t>
+          <t>26% of 520 lines in 3 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_risk_gateway, test_w39b_mf_analytics, test_w39b_razorpay</t>
         </is>
       </c>
       <c r="Z234" s="2" t="inlineStr"/>
@@ -30858,7 +30914,7 @@
       </c>
       <c r="Y235" s="2" t="inlineStr">
         <is>
-          <t>32% of 673 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_exec_data_tests</t>
+          <t>32% of 673 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_exec_data_tests, test_w39b_mf_analytics, test_w39b_razorpay</t>
         </is>
       </c>
       <c r="Z235" s="2" t="inlineStr"/>
@@ -31098,7 +31154,7 @@
       </c>
       <c r="Y237" s="2" t="inlineStr">
         <is>
-          <t>45% of 750 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_risk_gateway</t>
+          <t>46% of 757 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_risk_gateway, test_w39b_razorpay</t>
         </is>
       </c>
       <c r="Z237" s="2" t="inlineStr"/>
@@ -31562,7 +31618,7 @@
       </c>
       <c r="Y241" s="2" t="inlineStr">
         <is>
-          <t>48% of 231 lines in 2 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_depth20, test_w39_event_calendar, test_w39_global_sync, test_w39_intraday, test_w39_market_pulse, test_w39_perf_budget (+6 more)</t>
+          <t>48% of 231 lines in 2 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_depth20, test_w39_event_calendar, test_w39_global_sync, test_w39_intraday, test_w39_market_pulse, test_w39_perf_budget (+8 more)</t>
         </is>
       </c>
       <c r="Z241" s="2" t="inlineStr"/>
@@ -31745,7 +31801,7 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M243" s="2" t="inlineStr">
@@ -31755,22 +31811,22 @@
       </c>
       <c r="N243" s="2" t="inlineStr">
         <is>
-          <t>Plans, subscriptions, invoices DRAFT/OPEN/PAID, provider interface (sandbox/noop), dunning + grace, payment webhook consumer</t>
+          <t>Plans, subscriptions, invoices DRAFT/OPEN/PAID, provider interface (sandbox/noop), dunning + grace, payment webhook consumer. W39b (gateway decision delegated: Razorpay -- UPI / cards / netbanking, native Subscriptions): enterprise/razorpay.py on the existing payments interface -- REST v1 invoices with idempotent receipts, customers, plans, autopay subscriptions, cancel; signed webhook mapping onto invoices, payments, refunds, dunning and grace (out-of-order safe, money once per Razorpay id); reconcile() polling so payments settle without a public webhook; keys only from the vault; live keys refused without billing.razorpay.allow_live and the production environment</t>
         </is>
       </c>
       <c r="O243" s="2" t="inlineStr">
         <is>
-          <t>Payment gateway (owner decision)</t>
+          <t>Owner: run the flows in Razorpay test mode (docs/BILLING_RAZORPAY.md); GST tax lines are not built (ENT-14 PAYMENTS-TAX)</t>
         </is>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>enterprise/payments.py; enterprise/billing.py; enterprise/w32.py</t>
+          <t>enterprise/payments.py; enterprise/razorpay.py; enterprise/billing.py; enterprise/w32.py; db/schema_billing.py</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
         <is>
-          <t>W32 smoke (scratch)</t>
+          <t>tests/test_w39b_razorpay.py (26 tests on recorded Razorpay v1 response shapes)</t>
         </is>
       </c>
       <c r="R243" s="2" t="inlineStr">
@@ -31803,7 +31859,7 @@
       <c r="Y243" s="2" t="inlineStr"/>
       <c r="Z243" s="2" t="inlineStr">
         <is>
-          <t>Owner decision: payment gateway (Razorpay / Stripe / Cashfree) and its merchant credentials</t>
+          <t>Owner: a KYC-activated Razorpay business account with Invoices and Subscriptions enabled; store RAZORPAY_KEY_ID / RAZORPAY_KEY_SECRET / WEBHOOK_SECRET_RAZORPAY with python -m ops vault-set; registering the webhook URL needs ENT-07 (public HTTPS)</t>
         </is>
       </c>
     </row>
@@ -31922,7 +31978,7 @@
       </c>
       <c r="Y244" s="2" t="inlineStr">
         <is>
-          <t>33% of 577 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_exec_data_tests</t>
+          <t>40% of 612 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_exec_data_tests, test_w39b_mf_analytics, test_w39b_razorpay</t>
         </is>
       </c>
       <c r="Z244" s="2" t="inlineStr"/>
@@ -32166,7 +32222,7 @@
       </c>
       <c r="Y246" s="2" t="inlineStr">
         <is>
-          <t>44% of 271 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_perf_budget, test_w39_risk_gateway</t>
+          <t>47% of 278 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_perf_budget, test_w39_risk_gateway, test_w39b_razorpay</t>
         </is>
       </c>
       <c r="Z246" s="2" t="inlineStr"/>
@@ -32286,7 +32342,7 @@
       </c>
       <c r="Y247" s="2" t="inlineStr">
         <is>
-          <t>33% of 1421 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>33% of 1430 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+1 more)</t>
         </is>
       </c>
       <c r="Z247" s="2" t="inlineStr"/>
@@ -32526,7 +32582,7 @@
       </c>
       <c r="Y249" s="2" t="inlineStr">
         <is>
-          <t>test_a_deprecated_v1_resource_warns_then_answers_410_after_sunset | 59% of 657 lines in 3 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+20 more)</t>
+          <t>test_a_deprecated_v1_resource_warns_then_answers_410_after_sunset | 59% of 657 lines in 3 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+27 more)</t>
         </is>
       </c>
       <c r="Z249" s="2" t="inlineStr"/>
@@ -32582,9 +32638,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K250" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K250" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L250" s="2" t="inlineStr">
@@ -32599,22 +32655,22 @@
       </c>
       <c r="N250" s="2" t="inlineStr">
         <is>
-          <t>Signed inbound/outbound webhooks + W32 business consumers (payments, broker order.update), event status PROCESSED/IGNORED/FAILED</t>
+          <t>Signed inbound/outbound webhooks + W32 business consumers (payments, broker order.update), event status PROCESSED/IGNORED/FAILED. W39b: the Razorpay provider payloads are mapped (POST /api/webhooks/razorpay: X-Razorpay-Signature HMAC-SHA256 of the raw body, event-id and body-digest dedupe, 72 h replay bound, REJECTED rows for bad signatures)</t>
         </is>
       </c>
       <c r="O250" s="2" t="inlineStr">
         <is>
-          <t>Real provider payload mapping once a gateway / broker postback is chosen</t>
+          <t>Independent QA; verify against real Razorpay test-mode deliveries once ENT-07 gives ATIP a public URL; a broker postback mapping when a broker offers one</t>
         </is>
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>enterprise/w32.py; ops/webhooks.py; dashboard/ops_routes.py</t>
+          <t>enterprise/w32.py; enterprise/razorpay.py; ops/webhooks.py; dashboard/ops_routes.py</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
         <is>
-          <t>W32 smoke (scratch)</t>
+          <t>tests/test_w39b_razorpay.py</t>
         </is>
       </c>
       <c r="R250" s="2" t="inlineStr">
@@ -32631,7 +32687,7 @@
       <c r="U250" s="2" t="inlineStr"/>
       <c r="V250" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W250" s="2" t="inlineStr">
@@ -32646,7 +32702,7 @@
       </c>
       <c r="Y250" s="2" t="inlineStr">
         <is>
-          <t>27% of 447 lines in 3 key file(s) run by: test_auto_recover, test_w39_ops_tests, test_w39_perf_budget, test_w39_risk_gateway</t>
+          <t>tests/test_w39b_razorpay.py | 70% of 1134 lines in 4 key file(s) run by: test_auto_recover, test_w39_ops_tests, test_w39_perf_budget, test_w39_risk_gateway, test_w39b_razorpay</t>
         </is>
       </c>
       <c r="Z250" s="2" t="inlineStr"/>
@@ -33234,7 +33290,7 @@
       </c>
       <c r="Y255" s="2" t="inlineStr">
         <is>
-          <t>38% of 321 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract</t>
+          <t>49% of 356 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39b_razorpay</t>
         </is>
       </c>
       <c r="Z255" s="2" t="inlineStr"/>
@@ -33529,7 +33585,7 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>75</t>
         </is>
       </c>
       <c r="M258" s="2" t="inlineStr">
@@ -33539,22 +33595,22 @@
       </c>
       <c r="N258" s="2" t="inlineStr">
         <is>
-          <t>W38: Dockerfile (IST, non-root, volume, healthcheck), docker-compose (127.0.0.1-only ports, optional postgres profile), deploy/atip.env.example, provider-neutral cloud-init VM (SSH-only firewall, systemd unit), ATIP_DASHBOARD_HOST; LF pinned in .gitattributes</t>
+          <t>W38: Dockerfile (IST, non-root, volume, healthcheck), docker-compose (127.0.0.1-only ports, optional postgres profile), deploy/atip.env.example, cloud-init VM. W39b: the image is BUILT and smoke-tested (dev container + .github/workflows/docker.yml on every PR): --init on an empty volume, /health/live and /health/ready 200, uid 10001, IST, no state / .git / .claude in the image, live_gate() closed; BASE_IMAGE build arg for registry mirrors; .dockerignore fix (local agent worktrees had added 75 MB)</t>
         </is>
       </c>
       <c r="O258" s="2" t="inlineStr">
         <is>
-          <t>Build the image on a machine with Docker (not installed on the dev laptop); public exposure stays gated by ENT-07; Kubernetes not started</t>
+          <t>Owner: choose a host (ENT-16) and exposure (ENT-07); Kubernetes manifests and a registry push only after that</t>
         </is>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>Dockerfile; docker-compose.yml; deploy/cloud/cloud-init.yaml; docs/CONTAINER_DEPLOYMENT.md</t>
+          <t>Dockerfile; docker-compose.yml; .dockerignore; .github/workflows/docker.yml; docs/CONTAINER_DEPLOYMENT.md</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
         <is>
-          <t>SRS 2</t>
+          <t>.github/workflows/docker.yml; docs/CONTAINER_DEPLOYMENT.md (Status)</t>
         </is>
       </c>
       <c r="R258" s="2" t="inlineStr"/>
@@ -33567,7 +33623,7 @@
       <c r="U258" s="2" t="inlineStr"/>
       <c r="V258" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W258" s="2" t="inlineStr">
@@ -33818,7 +33874,7 @@
       </c>
       <c r="Y260" s="2" t="inlineStr">
         <is>
-          <t>71% of 254 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+20 more)</t>
+          <t>71% of 254 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+27 more)</t>
         </is>
       </c>
       <c r="Z260" s="2" t="inlineStr"/>
@@ -33934,7 +33990,7 @@
       </c>
       <c r="Y261" s="2" t="inlineStr">
         <is>
-          <t>44% of 206 lines in 2 key file(s) run by: test_auto_recover, test_regressions, test_risk_controls, test_w38_platform_compliance, test_w39_api_contract, test_w39_backtest, test_w39_delivery, test_w39_depth20 (+22 more)</t>
+          <t>53% of 232 lines in 2 key file(s) run by: test_auto_recover, test_regressions, test_risk_controls, test_w38_platform_compliance, test_w39_api_contract, test_w39_backtest, test_w39_delivery, test_w39_depth20 (+31 more)</t>
         </is>
       </c>
       <c r="Z261" s="2" t="inlineStr"/>
@@ -34050,7 +34106,7 @@
       </c>
       <c r="Y262" s="2" t="inlineStr">
         <is>
-          <t>35% of 1341 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget (+2 more)</t>
+          <t>36% of 1350 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget (+3 more)</t>
         </is>
       </c>
       <c r="Z262" s="2" t="inlineStr"/>
@@ -34166,7 +34222,7 @@
       </c>
       <c r="Y263" s="2" t="inlineStr">
         <is>
-          <t>31% of 1132 lines in 4 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
+          <t>32% of 1132 lines in 4 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
         </is>
       </c>
       <c r="Z263" s="2" t="inlineStr"/>
@@ -35322,7 +35378,7 @@
       </c>
       <c r="Y273" s="2" t="inlineStr">
         <is>
-          <t>89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
+          <t>89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_w39b_mf_analytics, test_wealth_api_security, test_wealth_math, test_wealth_performance (+1 more)</t>
         </is>
       </c>
       <c r="Z273" s="2" t="inlineStr"/>
@@ -35670,7 +35726,7 @@
       </c>
       <c r="Y276" s="2" t="inlineStr">
         <is>
-          <t>75% of 204 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+20 more)</t>
+          <t>75% of 204 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+27 more)</t>
         </is>
       </c>
       <c r="Z276" s="2" t="inlineStr"/>
@@ -36018,7 +36074,7 @@
       </c>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 76% of 314 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance (+1 more)</t>
+          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 77% of 317 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance (+1 more)</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr"/>
@@ -36482,7 +36538,7 @@
       </c>
       <c r="Y283" s="2" t="inlineStr">
         <is>
-          <t>test_benchmark_return_is_the_price_return_over_the_sessions | 93% of 299 lines in 2 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_benchmark_return_is_the_price_return_over_the_sessions | 93% of 299 lines in 2 key file(s) run by: test_w39_performance_detail, test_w39b_mf_analytics, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z283" s="2" t="inlineStr"/>
@@ -36830,7 +36886,7 @@
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 95% of 216 lines in 2 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_wealth_math, test_wealth_performance</t>
+          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 96% of 216 lines in 2 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo, test_w39b_mf_analytics, test_wealth_math (+1 more)</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr"/>
@@ -37526,7 +37582,7 @@
       </c>
       <c r="Y292" s="2" t="inlineStr">
         <is>
-          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
+          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_w39b_mf_analytics, test_wealth_api_security, test_wealth_math, test_wealth_performance (+1 more)</t>
         </is>
       </c>
       <c r="Z292" s="2" t="inlineStr"/>
@@ -37645,11 +37701,7 @@
           <t>tests/test_dhan_token_refresh.py | 71% of 105 lines in 1 key file(s) run by: test_dhan_token_refresh, test_w38_platform_compliance</t>
         </is>
       </c>
-      <c r="Z293" s="2" t="inlineStr">
-        <is>
-          <t>Owner input (not a code blocker): dhan_pin + base32 dhan_totp_secret from web.dhan.co</t>
-        </is>
-      </c>
+      <c r="Z293" s="2" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -37762,7 +37814,7 @@
       </c>
       <c r="Y294" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_history.py; tests/test_w39b_merge.py | 50% of 1001 lines in 3 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests (+3 more)</t>
+          <t>tests/test_w39_history.py; tests/test_w39b_merge.py | 51% of 1001 lines in 3 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests (+3 more)</t>
         </is>
       </c>
       <c r="Z294" s="2" t="inlineStr"/>
@@ -37878,7 +37930,7 @@
       </c>
       <c r="Y295" s="2" t="inlineStr">
         <is>
-          <t>test_stock_history_reports_multi_year_returns | 80% of 74 lines in 1 key file(s) run by: test_auto_recover, test_w39_owner_notes, test_w39_perf_budget</t>
+          <t>test_stock_history_reports_multi_year_returns | 84% of 113 lines in 1 key file(s) run by: test_auto_recover, test_w39_owner_notes, test_w39_perf_budget, test_w39b_patterns_more</t>
         </is>
       </c>
       <c r="Z295" s="2" t="inlineStr"/>
@@ -37994,7 +38046,7 @@
       </c>
       <c r="Y296" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_risk_gateway.py | 50% of 1617 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+9 more)</t>
+          <t>tests/test_w39_risk_gateway.py | 51% of 1617 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+10 more)</t>
         </is>
       </c>
       <c r="Z296" s="2" t="inlineStr"/>
@@ -38806,7 +38858,7 @@
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_backtest.py | 82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial</t>
+          <t>tests/test_w39_backtest.py | 82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr"/>
@@ -38973,30 +39025,30 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J305" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="K305" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="J305" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K305" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L305" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="M305" s="2" t="inlineStr"/>
       <c r="N305" s="2" t="inlineStr">
         <is>
-          <t>strategy/aggressive.py: ATR trail, T1 partial, T2 checkpoint; DEFAULTS aggressive_enabled=False but no code reads the flag (off only because nothing schedules strategy.live); bypasses the W4 risk engine</t>
+          <t>strategy/aggressive.py: ATR trail, T1 partial, T2 checkpoint. W39b (decision taken under the owner's 'take the decisions' instruction): aggressive_enabled=false refuses NEW entries in strategy.live, while open positions keep being managed (stops / targets / trails), so switching it off never strands a position; new cri_exit_threshold (default off) closes the remaining quantity with MARKET_RISK_EXIT when the stock's crash-risk index reaches it, on the existing broker path (pretrade checks incl. price band and circuit limits unchanged); threshold validated to (0, 100]</t>
         </is>
       </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
-          <t>Decide whether the flag gates strategy.live enter/manage, and whether to add a CRI-spike exit</t>
+          <t>Independent QA; the owner picks a CRI threshold (e.g. 80) after reviewing CRI history before turning it on; the aggressive strategy stays unscheduled and PAPER</t>
         </is>
       </c>
       <c r="P305" s="2" t="inlineStr">
@@ -39006,7 +39058,7 @@
       </c>
       <c r="Q305" s="2" t="inlineStr">
         <is>
-          <t>tests/test_aggressive_*.py (74 tests)</t>
+          <t>tests/test_strategy_live.py (test_disabled_flag_refuses_new_entries_but_keeps_managing_open_positions, test_cri_spike_exits_the_whole_position_only_when_configured, test_cri_below_threshold_or_unknown_does_not_exit, test_cri_threshold_is_validated); tests/test_aggressive_*.py</t>
         </is>
       </c>
       <c r="R305" s="2" t="inlineStr">
@@ -39028,7 +39080,7 @@
       </c>
       <c r="W305" s="2" t="inlineStr">
         <is>
-          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+          <t>W39b developed 2026-10-08 on branch claude/wizardly-curie-fbjeoa (PR #5); was BLOCKED on an owner decision, decided as described (reversible: one config key each); independent validation PENDING</t>
         </is>
       </c>
       <c r="X305" s="2" t="inlineStr">
@@ -39036,12 +39088,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="Y305" s="2" t="inlineStr"/>
-      <c r="Z305" s="2" t="inlineStr">
-        <is>
-          <t>Owner decision: (1) should aggressive_enabled=false stop `python -m strategy.live --manage` (today it runs regardless)? (2) add a CRI-spike exit (threshold?) and route orders through the W4 risk engine? Changing either alters live exit behaviour</t>
-        </is>
-      </c>
+      <c r="Y305" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_strategy_live.py (test_disabled_flag_refuses_new_entries_but_keeps_managing_open_positions, test_cri_spike_exits_the_whole_position_only_when_configured, test_cri_below_threshold_or_unknown_does_not_exit, test_cri_threshold_is_validated); tests/test_aggressive_*.py | 80% of 351 lines in 2 key file(s) run by: test_aggressive_backtest, test_aggressive_decisions, test_aggressive_lifecycle, test_strategy_live</t>
+        </is>
+      </c>
+      <c r="Z305" s="2" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -39614,7 +39666,7 @@
       </c>
       <c r="Y310" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_research.py | 90% of 554 lines in 2 key file(s) run by: test_w39_mcp, test_w39_research, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+          <t>tests/test_w39_research.py | 90% of 554 lines in 2 key file(s) run by: test_w39_mcp, test_w39_research, test_w39_scorecard, test_w39_screener, test_w39_technicals, test_w39b_dvm, test_w39b_earnings_surprise, test_w39b_tf75</t>
         </is>
       </c>
       <c r="Z310" s="2" t="inlineStr"/>
@@ -39730,7 +39782,7 @@
       </c>
       <c r="Y311" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_screener.py | 90% of 427 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_screener_nl, test_w39_technicals (+1 more)</t>
+          <t>tests/test_w39_screener.py | 88% of 446 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_screener_nl, test_w39_technicals (+5 more)</t>
         </is>
       </c>
       <c r="Z311" s="2" t="inlineStr"/>
@@ -39962,7 +40014,7 @@
       </c>
       <c r="Y313" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_technicals.py | 87% of 765 lines in 2 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener (+3 more)</t>
+          <t>tests/test_w39_technicals.py | 88% of 820 lines in 2 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+9 more)</t>
         </is>
       </c>
       <c r="Z313" s="2" t="inlineStr"/>
@@ -40194,7 +40246,7 @@
       </c>
       <c r="Y315" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_regime_gate.py | 83% of 248 lines in 1 key file(s) run by: test_w39_delivery, test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_technicals (+2 more)</t>
+          <t>tests/test_w39_regime_gate.py | 83% of 248 lines in 1 key file(s) run by: test_w39_delivery, test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_technicals (+4 more)</t>
         </is>
       </c>
       <c r="Z315" s="2" t="inlineStr"/>
@@ -40310,7 +40362,7 @@
       </c>
       <c r="Y316" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_track_record.py | 84% of 506 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+2 more)</t>
+          <t>tests/test_w39_track_record.py | 84% of 522 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+6 more)</t>
         </is>
       </c>
       <c r="Z316" s="2" t="inlineStr"/>
@@ -40426,7 +40478,7 @@
       </c>
       <c r="Y317" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_weekly.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+          <t>tests/test_w39_weekly.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
         </is>
       </c>
       <c r="Z317" s="2" t="inlineStr"/>
@@ -40459,12 +40511,12 @@
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>Chart patterns from swing pivots (CP-01..03)</t>
+          <t>Chart patterns from swing pivots (CP-01..04) and marks on the stock chart</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>Darvas box, VCP, double bottom, ascending triangle, head and shoulders</t>
+          <t>Darvas box, VCP, double bottom, ascending triangle, head and shoulders; W39b: inverse H&amp;S, descending triangle, channels, wedges, chart marks</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -40495,22 +40547,22 @@
       <c r="M318" s="2" t="inlineStr"/>
       <c r="N318" s="2" t="inlineStr">
         <is>
-          <t>research/patterns.py: patterns as scans with levels, screener setups, alerts held until a positive 30-signal record</t>
+          <t>research/patterns.py: patterns as scans with levels, screener setups, alerts held until a positive 30-signal record. W39b (CP-04): inverse head and shoulders, descending triangle, rising / falling channels (breakout and breakdown each), rising / falling wedges -- 14 pattern scans, each calibrated at 0.02-0.1 % of stock-days on random walks; the stock chart (/api/stock/{symbol}/history chart_marks) marks signals, pattern breakouts, candle patterns and the lines of the patterns in place, on daily / weekly / monthly bars, with a toggle</t>
         </is>
       </c>
       <c r="O318" s="2" t="inlineStr">
         <is>
-          <t>Rule-based approximations; no inverse H&amp;S, descending triangles, channels or wedges yet</t>
+          <t>Rule-based approximations; independent QA; each new scan needs 30 closed signals before its alerts start</t>
         </is>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>research/patterns.py</t>
+          <t>research/patterns.py; dashboard/stock_view.py</t>
         </is>
       </c>
       <c r="Q318" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_patterns.py</t>
+          <t>tests/test_w39_patterns.py; tests/test_w39b_patterns_more.py</t>
         </is>
       </c>
       <c r="R318" s="2" t="inlineStr">
@@ -40542,7 +40594,7 @@
       </c>
       <c r="Y318" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_patterns.py | 92% of 216 lines in 1 key file(s) run by: test_w39_delivery, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+          <t>tests/test_w39_patterns.py; tests/test_w39b_patterns_more.py | 93% of 491 lines in 2 key file(s) run by: test_auto_recover, test_w39_delivery, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
         </is>
       </c>
       <c r="Z318" s="2" t="inlineStr"/>
@@ -40658,7 +40710,7 @@
       </c>
       <c r="Y319" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_rs_line.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+          <t>tests/test_w39_rs_line.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
         </is>
       </c>
       <c r="Z319" s="2" t="inlineStr"/>
@@ -40774,7 +40826,7 @@
       </c>
       <c r="Y320" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_delivery.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+          <t>tests/test_w39_delivery.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
         </is>
       </c>
       <c r="Z320" s="2" t="inlineStr"/>
@@ -40890,7 +40942,7 @@
       </c>
       <c r="Y321" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_scorecard.py | 89% of 413 lines in 1 key file(s) run by: test_w39_mcp, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+          <t>tests/test_w39_scorecard.py | 89% of 420 lines in 1 key file(s) run by: test_w39_mcp, test_w39_scorecard, test_w39_screener, test_w39_technicals, test_w39b_dvm, test_w39b_earnings_surprise, test_w39b_tf75</t>
         </is>
       </c>
       <c r="Z321" s="2" t="inlineStr"/>
@@ -41122,7 +41174,7 @@
       </c>
       <c r="Y323" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_intraday.py | 87% of 225 lines in 1 key file(s) run by: test_w39_intraday, test_w39_mcp</t>
+          <t>tests/test_w39_intraday.py | 88% of 225 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly, test_w39b_tf75</t>
         </is>
       </c>
       <c r="Z323" s="2" t="inlineStr"/>
@@ -41155,12 +41207,12 @@
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>20-level depth and depth-weighted imbalance (DP-01..03)</t>
+          <t>20-level depth, depth-weighted imbalance and order-flow imbalance (DP-01..03, OF-01..03)</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>Dhan 20-level depth WebSocket, DWI, persistent flags, validation</t>
+          <t>Dhan 20-level depth WebSocket, DWI, OFI from quote changes (best level and multi-level), persistent flags, validation</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
@@ -41191,12 +41243,12 @@
       <c r="M324" s="2" t="inlineStr"/>
       <c r="N324" s="2" t="inlineStr">
         <is>
-          <t>data/depth20.py: depth feed (off by default), DWI, logistic validation vs the next 1 / 5 minutes</t>
+          <t>data/depth20.py: depth feed (off by default), DWI, OFI summed over every book update, logistic validation vs the next 1 / 5 minutes and OFI vs its own interval</t>
         </is>
       </c>
       <c r="O324" s="2" t="inlineStr">
         <is>
-          <t>Owner: depth20.enabled and the Dhan Data API; no order-flow imbalance yet</t>
+          <t>Owner: depth20.enabled and the Dhan Data API</t>
         </is>
       </c>
       <c r="P324" s="2" t="inlineStr">
@@ -41206,7 +41258,7 @@
       </c>
       <c r="Q324" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_depth20.py</t>
+          <t>tests/test_w39_depth20.py; tests/test_w39b_ofi.py</t>
         </is>
       </c>
       <c r="R324" s="2" t="inlineStr">
@@ -41238,7 +41290,7 @@
       </c>
       <c r="Y324" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_depth20.py | 76% of 282 lines in 1 key file(s) run by: test_w39_depth20</t>
+          <t>tests/test_w39_depth20.py; tests/test_w39b_ofi.py | 82% of 379 lines in 1 key file(s) run by: test_w39_depth20, test_w39b_ofi</t>
         </is>
       </c>
       <c r="Z324" s="2" t="inlineStr"/>
@@ -41702,13 +41754,481 @@
       </c>
       <c r="Y328" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_market_pulse.py | 56% of 190 lines in 2 key file(s) run by: test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+          <t>tests/test_w39_market_pulse.py | 56% of 190 lines in 2 key file(s) run by: test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_scorecard, test_w39_screener, test_w39_technicals, test_w39b_dvm (+2 more)</t>
         </is>
       </c>
       <c r="Z328" s="2" t="inlineStr"/>
     </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>W39B-TF75</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>75-minute technical rating and its agreement with the daily one</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>Trendlyne / TradingView-style intraday timeframe rating</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4; docs/ANALYSIS_TOOLS_AND_SIGNALS_PLAN_2026-10.md</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J329" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K329" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr"/>
+      <c r="N329" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py bars_75 / rating_75: the daily rating's votes on 75-minute bars built only from stored 15-minute bars (09:15 / 10:30 / 11:45 / 13:00 / 14:15), completed bars only, 35 bars (7 sessions) needed, never a stale session; stored in technical_snapshot (tech_rating_75*, rsi_14_75, supertrend_dir_75, bar_75_end, mtf_alignment_75) by the 20:30 run; screener fields and a preset</t>
+        </is>
+      </c>
+      <c r="O329" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA; no live intraday refresh (once a day, as of the close); /signals has no 75-minute column</t>
+        </is>
+      </c>
+      <c r="P329" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py; research/tech_signals.py; research/screener.py</t>
+        </is>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_tf75.py</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S329" s="2" t="inlineStr"/>
+      <c r="T329" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U329" s="2" t="inlineStr"/>
+      <c r="V329" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W329" s="2" t="inlineStr">
+        <is>
+          <t>W39b developed 2026-10-08 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X329" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5)</t>
+        </is>
+      </c>
+      <c r="Y329" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_tf75.py | 88% of 1266 lines in 3 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+10 more)</t>
+        </is>
+      </c>
+      <c r="Z329" s="2" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>W39B-DVM</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>DVM view: durability, valuation, momentum 0-100 and zones</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>Trendlyne-style DVM scores with explanations</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4; docs/ANALYSIS_TOOLS_AND_SIGNALS_PLAN_2026-10.md</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J330" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K330" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr"/>
+      <c r="N330" s="2" t="inlineStr">
+        <is>
+          <t>research/dvm.py: durability from the scorecard's 12 health / past-performance checks, valuation from the research fair value (60 %) and P/E (P/B for financials) vs the industry median (40 %), momentum from the technical and RS ratings; every score explains itself with its numbers; seven zones; stored nightly on fundamental_scorecard (dvm_*); GET /api/research/dvm/{symbol}; DVM card on /research; 3 screener presets</t>
+        </is>
+      </c>
+      <c r="O330" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA; weights are ATIP's definitions, not backtested -- record whether the zones pay before using them</t>
+        </is>
+      </c>
+      <c r="P330" s="2" t="inlineStr">
+        <is>
+          <t>research/dvm.py; research/scorecard.py; dashboard/w39_routes.py</t>
+        </is>
+      </c>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_dvm.py</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S330" s="2" t="inlineStr"/>
+      <c r="T330" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U330" s="2" t="inlineStr"/>
+      <c r="V330" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W330" s="2" t="inlineStr">
+        <is>
+          <t>W39b developed 2026-10-08 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X330" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5)</t>
+        </is>
+      </c>
+      <c r="Y330" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_dvm.py | 86% of 1041 lines in 3 key file(s) run by: test_auto_recover, test_w39_depth20, test_w39_event_calendar, test_w39_global_sync, test_w39_intraday, test_w39_market_pulse, test_w39_mcp, test_w39_options (+12 more)</t>
+        </is>
+      </c>
+      <c r="Z330" s="2" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>W39B-PEAD</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Earnings surprise (SUE), EPS-trend proxy and a post-earnings-drift scan</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>Earnings surprise and PEAD (gap analysis 4.7)</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4; docs/ANALYSIS_TOOLS_AND_SIGNALS_PLAN_2026-10.md</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J331" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K331" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L331" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="inlineStr"/>
+      <c r="N331" s="2" t="inlineStr">
+        <is>
+          <t>research/earnings_surprise.py: SUE and revenue SUE vs the same quarter a year earlier (8-quarter standard deviation, 4 needed), point in time from the NSE broadcast date; EPS-trend revisions proxy; pead_bull / pead_bear scans (|SUE| &gt;= 2, first session after the filing, 60-session horizon) stored and tracked like every scan, alerts held until 30 closed signals with positive expectancy; 20:35 job; screener fields and a preset; GET /api/research/earnings-surprise/{symbol}</t>
+        </is>
+      </c>
+      <c r="O331" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA; needs 9+ quarters of NSE XBRL history (run the history backfill); no consensus estimates (ATIP's own history only); filings arrive with the Saturday fundamentals job</t>
+        </is>
+      </c>
+      <c r="P331" s="2" t="inlineStr">
+        <is>
+          <t>research/earnings_surprise.py; research/tech_signals.py</t>
+        </is>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_earnings_surprise.py</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S331" s="2" t="inlineStr"/>
+      <c r="T331" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U331" s="2" t="inlineStr"/>
+      <c r="V331" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W331" s="2" t="inlineStr">
+        <is>
+          <t>W39b developed 2026-10-08 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X331" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5)</t>
+        </is>
+      </c>
+      <c r="Y331" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_earnings_surprise.py | 85% of 905 lines in 2 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+6 more)</t>
+        </is>
+      </c>
+      <c r="Z331" s="2" t="inlineStr">
+        <is>
+          <t>For a consensus-based surprise: a consensus estimates feed (not available today)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>W39B-MFA</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Wealth / Mutual funds</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>Mutual fund analytics on stored AMFI NAVs (read-only)</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>Value Research / Kuvera-style scheme analytics (gap analysis 4.3)</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4; docs/ANALYSIS_TOOLS_AND_SIGNALS_PLAN_2026-10.md</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J332" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K332" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr"/>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>data/mf_analytics.py: point-to-point and CAGR returns, 1Y / 3Y rolling returns with hurdle stats, volatility / Sharpe / Sortino, drawdown with dates, beta / alpha / tracking error vs a price index, SIP and lump-sum XIRR, category rank among stored schemes, side-by-side compare; 3 read-only GET routes; scheme detail card on /data-platform</t>
+        </is>
+      </c>
+      <c r="O332" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA. Holding MFs in the wealth ledger stays out of scope (owner Scope Exclusions); benchmark is a price index, not total return; peers limited to stored schemes</t>
+        </is>
+      </c>
+      <c r="P332" s="2" t="inlineStr">
+        <is>
+          <t>data/mf_analytics.py; dashboard/w35_routes.py; dashboard/w35_page.py</t>
+        </is>
+      </c>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_mf_analytics.py</t>
+        </is>
+      </c>
+      <c r="R332" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S332" s="2" t="inlineStr"/>
+      <c r="T332" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U332" s="2" t="inlineStr"/>
+      <c r="V332" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W332" s="2" t="inlineStr">
+        <is>
+          <t>W39b developed 2026-10-08 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X332" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5)</t>
+        </is>
+      </c>
+      <c r="Y332" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_mf_analytics.py | 86% of 626 lines in 3 key file(s) run by: test_auto_recover, test_w39_ml_regime_lineage_surface, test_w39_perf_budget, test_w39_ui_smoke, test_w39b_mf_analytics</t>
+        </is>
+      </c>
+      <c r="Z332" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z328"/>
+  <autoFilter ref="A1:Z332"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41719,7 +42239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z51"/>
+  <dimension ref="A1:Z55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -41993,7 +42513,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 76% of 314 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance (+1 more)</t>
+          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 77% of 317 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance (+1 more)</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -42457,7 +42977,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>test_benchmark_return_is_the_price_return_over_the_sessions | 93% of 299 lines in 2 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_benchmark_return_is_the_price_return_over_the_sessions | 93% of 299 lines in 2 key file(s) run by: test_w39_performance_detail, test_w39b_mf_analytics, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr"/>
@@ -42805,7 +43325,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 95% of 216 lines in 2 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_wealth_math, test_wealth_performance</t>
+          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 96% of 216 lines in 2 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo, test_w39b_mf_analytics, test_wealth_math (+1 more)</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr"/>
@@ -43501,7 +44021,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_wealth_api_security, test_wealth_math, test_wealth_performance, test_wealth_planning</t>
+          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_w39b_mf_analytics, test_wealth_api_security, test_wealth_math, test_wealth_performance (+1 more)</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr"/>
@@ -43620,11 +44140,7 @@
           <t>tests/test_dhan_token_refresh.py | 71% of 105 lines in 1 key file(s) run by: test_dhan_token_refresh, test_w38_platform_compliance</t>
         </is>
       </c>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>Owner input (not a code blocker): dhan_pin + base32 dhan_totp_secret from web.dhan.co</t>
-        </is>
-      </c>
+      <c r="Z16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -43737,7 +44253,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_history.py; tests/test_w39b_merge.py | 50% of 1001 lines in 3 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests (+3 more)</t>
+          <t>tests/test_w39_history.py; tests/test_w39b_merge.py | 51% of 1001 lines in 3 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests (+3 more)</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr"/>
@@ -43853,7 +44369,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>test_stock_history_reports_multi_year_returns | 80% of 74 lines in 1 key file(s) run by: test_auto_recover, test_w39_owner_notes, test_w39_perf_budget</t>
+          <t>test_stock_history_reports_multi_year_returns | 84% of 113 lines in 1 key file(s) run by: test_auto_recover, test_w39_owner_notes, test_w39_perf_budget, test_w39b_patterns_more</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr"/>
@@ -43969,7 +44485,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_risk_gateway.py | 50% of 1617 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+9 more)</t>
+          <t>tests/test_w39_risk_gateway.py | 51% of 1617 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+10 more)</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr"/>
@@ -44781,7 +45297,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_backtest.py | 82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial</t>
+          <t>tests/test_w39_backtest.py | 82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr"/>
@@ -44948,30 +45464,30 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J28" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>strategy/aggressive.py: ATR trail, T1 partial, T2 checkpoint; DEFAULTS aggressive_enabled=False but no code reads the flag (off only because nothing schedules strategy.live); bypasses the W4 risk engine</t>
+          <t>strategy/aggressive.py: ATR trail, T1 partial, T2 checkpoint. W39b (decision taken under the owner's 'take the decisions' instruction): aggressive_enabled=false refuses NEW entries in strategy.live, while open positions keep being managed (stops / targets / trails), so switching it off never strands a position; new cri_exit_threshold (default off) closes the remaining quantity with MARKET_RISK_EXIT when the stock's crash-risk index reaches it, on the existing broker path (pretrade checks incl. price band and circuit limits unchanged); threshold validated to (0, 100]</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Decide whether the flag gates strategy.live enter/manage, and whether to add a CRI-spike exit</t>
+          <t>Independent QA; the owner picks a CRI threshold (e.g. 80) after reviewing CRI history before turning it on; the aggressive strategy stays unscheduled and PAPER</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -44981,7 +45497,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>tests/test_aggressive_*.py (74 tests)</t>
+          <t>tests/test_strategy_live.py (test_disabled_flag_refuses_new_entries_but_keeps_managing_open_positions, test_cri_spike_exits_the_whole_position_only_when_configured, test_cri_below_threshold_or_unknown_does_not_exit, test_cri_threshold_is_validated); tests/test_aggressive_*.py</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -45003,7 +45519,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>W39 developed 2026-10-07 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+          <t>W39b developed 2026-10-08 on branch claude/wizardly-curie-fbjeoa (PR #5); was BLOCKED on an owner decision, decided as described (reversible: one config key each); independent validation PENDING</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
@@ -45011,12 +45527,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="Y28" s="2" t="inlineStr"/>
-      <c r="Z28" s="2" t="inlineStr">
-        <is>
-          <t>Owner decision: (1) should aggressive_enabled=false stop `python -m strategy.live --manage` (today it runs regardless)? (2) add a CRI-spike exit (threshold?) and route orders through the W4 risk engine? Changing either alters live exit behaviour</t>
-        </is>
-      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_strategy_live.py (test_disabled_flag_refuses_new_entries_but_keeps_managing_open_positions, test_cri_spike_exits_the_whole_position_only_when_configured, test_cri_below_threshold_or_unknown_does_not_exit, test_cri_threshold_is_validated); tests/test_aggressive_*.py | 80% of 351 lines in 2 key file(s) run by: test_aggressive_backtest, test_aggressive_decisions, test_aggressive_lifecycle, test_strategy_live</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -45589,7 +46105,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_research.py | 90% of 554 lines in 2 key file(s) run by: test_w39_mcp, test_w39_research, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+          <t>tests/test_w39_research.py | 90% of 554 lines in 2 key file(s) run by: test_w39_mcp, test_w39_research, test_w39_scorecard, test_w39_screener, test_w39_technicals, test_w39b_dvm, test_w39b_earnings_surprise, test_w39b_tf75</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr"/>
@@ -45705,7 +46221,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_screener.py | 90% of 427 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_screener_nl, test_w39_technicals (+1 more)</t>
+          <t>tests/test_w39_screener.py | 88% of 446 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_screener_nl, test_w39_technicals (+5 more)</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr"/>
@@ -45937,7 +46453,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_technicals.py | 87% of 765 lines in 2 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener (+3 more)</t>
+          <t>tests/test_w39_technicals.py | 88% of 820 lines in 2 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+9 more)</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr"/>
@@ -46169,7 +46685,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_regime_gate.py | 83% of 248 lines in 1 key file(s) run by: test_w39_delivery, test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_technicals (+2 more)</t>
+          <t>tests/test_w39_regime_gate.py | 83% of 248 lines in 1 key file(s) run by: test_w39_delivery, test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_technicals (+4 more)</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr"/>
@@ -46285,7 +46801,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_track_record.py | 84% of 506 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+2 more)</t>
+          <t>tests/test_w39_track_record.py | 84% of 522 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+6 more)</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr"/>
@@ -46401,7 +46917,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_weekly.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+          <t>tests/test_w39_weekly.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr"/>
@@ -46434,12 +46950,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Chart patterns from swing pivots (CP-01..03)</t>
+          <t>Chart patterns from swing pivots (CP-01..04) and marks on the stock chart</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Darvas box, VCP, double bottom, ascending triangle, head and shoulders</t>
+          <t>Darvas box, VCP, double bottom, ascending triangle, head and shoulders; W39b: inverse H&amp;S, descending triangle, channels, wedges, chart marks</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -46470,22 +46986,22 @@
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>research/patterns.py: patterns as scans with levels, screener setups, alerts held until a positive 30-signal record</t>
+          <t>research/patterns.py: patterns as scans with levels, screener setups, alerts held until a positive 30-signal record. W39b (CP-04): inverse head and shoulders, descending triangle, rising / falling channels (breakout and breakdown each), rising / falling wedges -- 14 pattern scans, each calibrated at 0.02-0.1 % of stock-days on random walks; the stock chart (/api/stock/{symbol}/history chart_marks) marks signals, pattern breakouts, candle patterns and the lines of the patterns in place, on daily / weekly / monthly bars, with a toggle</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Rule-based approximations; no inverse H&amp;S, descending triangles, channels or wedges yet</t>
+          <t>Rule-based approximations; independent QA; each new scan needs 30 closed signals before its alerts start</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>research/patterns.py</t>
+          <t>research/patterns.py; dashboard/stock_view.py</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_patterns.py</t>
+          <t>tests/test_w39_patterns.py; tests/test_w39b_patterns_more.py</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -46517,7 +47033,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_patterns.py | 92% of 216 lines in 1 key file(s) run by: test_w39_delivery, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+          <t>tests/test_w39_patterns.py; tests/test_w39b_patterns_more.py | 93% of 491 lines in 2 key file(s) run by: test_auto_recover, test_w39_delivery, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr"/>
@@ -46633,7 +47149,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_rs_line.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+          <t>tests/test_w39_rs_line.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr"/>
@@ -46749,7 +47265,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_delivery.py | 95% of 259 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly</t>
+          <t>tests/test_w39_delivery.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr"/>
@@ -46865,7 +47381,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_scorecard.py | 89% of 413 lines in 1 key file(s) run by: test_w39_mcp, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+          <t>tests/test_w39_scorecard.py | 89% of 420 lines in 1 key file(s) run by: test_w39_mcp, test_w39_scorecard, test_w39_screener, test_w39_technicals, test_w39b_dvm, test_w39b_earnings_surprise, test_w39b_tf75</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr"/>
@@ -47097,7 +47613,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_intraday.py | 87% of 225 lines in 1 key file(s) run by: test_w39_intraday, test_w39_mcp</t>
+          <t>tests/test_w39_intraday.py | 88% of 225 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly, test_w39b_tf75</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr"/>
@@ -47130,12 +47646,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>20-level depth and depth-weighted imbalance (DP-01..03)</t>
+          <t>20-level depth, depth-weighted imbalance and order-flow imbalance (DP-01..03, OF-01..03)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Dhan 20-level depth WebSocket, DWI, persistent flags, validation</t>
+          <t>Dhan 20-level depth WebSocket, DWI, OFI from quote changes (best level and multi-level), persistent flags, validation</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -47166,12 +47682,12 @@
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>data/depth20.py: depth feed (off by default), DWI, logistic validation vs the next 1 / 5 minutes</t>
+          <t>data/depth20.py: depth feed (off by default), DWI, OFI summed over every book update, logistic validation vs the next 1 / 5 minutes and OFI vs its own interval</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Owner: depth20.enabled and the Dhan Data API; no order-flow imbalance yet</t>
+          <t>Owner: depth20.enabled and the Dhan Data API</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -47181,7 +47697,7 @@
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_depth20.py</t>
+          <t>tests/test_w39_depth20.py; tests/test_w39b_ofi.py</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
@@ -47213,7 +47729,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_depth20.py | 76% of 282 lines in 1 key file(s) run by: test_w39_depth20</t>
+          <t>tests/test_w39_depth20.py; tests/test_w39b_ofi.py | 82% of 379 lines in 1 key file(s) run by: test_w39_depth20, test_w39b_ofi</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr"/>
@@ -47677,13 +48193,481 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_market_pulse.py | 56% of 190 lines in 2 key file(s) run by: test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_scorecard, test_w39_screener, test_w39_technicals</t>
+          <t>tests/test_w39_market_pulse.py | 56% of 190 lines in 2 key file(s) run by: test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_scorecard, test_w39_screener, test_w39_technicals, test_w39b_dvm (+2 more)</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>W39B-TF75</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>75-minute technical rating and its agreement with the daily one</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Trendlyne / TradingView-style intraday timeframe rating</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4; docs/ANALYSIS_TOOLS_AND_SIGNALS_PLAN_2026-10.md</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J52" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K52" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py bars_75 / rating_75: the daily rating's votes on 75-minute bars built only from stored 15-minute bars (09:15 / 10:30 / 11:45 / 13:00 / 14:15), completed bars only, 35 bars (7 sessions) needed, never a stale session; stored in technical_snapshot (tech_rating_75*, rsi_14_75, supertrend_dir_75, bar_75_end, mtf_alignment_75) by the 20:30 run; screener fields and a preset</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA; no live intraday refresh (once a day, as of the close); /signals has no 75-minute column</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>research/technicals.py; research/tech_signals.py; research/screener.py</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_tf75.py</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>W39b developed 2026-10-08 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5)</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_tf75.py | 88% of 1266 lines in 3 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+10 more)</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>W39B-DVM</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>DVM view: durability, valuation, momentum 0-100 and zones</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Trendlyne-style DVM scores with explanations</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4; docs/ANALYSIS_TOOLS_AND_SIGNALS_PLAN_2026-10.md</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J53" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K53" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>research/dvm.py: durability from the scorecard's 12 health / past-performance checks, valuation from the research fair value (60 %) and P/E (P/B for financials) vs the industry median (40 %), momentum from the technical and RS ratings; every score explains itself with its numbers; seven zones; stored nightly on fundamental_scorecard (dvm_*); GET /api/research/dvm/{symbol}; DVM card on /research; 3 screener presets</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA; weights are ATIP's definitions, not backtested -- record whether the zones pay before using them</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>research/dvm.py; research/scorecard.py; dashboard/w39_routes.py</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_dvm.py</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>W39b developed 2026-10-08 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5)</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_dvm.py | 86% of 1041 lines in 3 key file(s) run by: test_auto_recover, test_w39_depth20, test_w39_event_calendar, test_w39_global_sync, test_w39_intraday, test_w39_market_pulse, test_w39_mcp, test_w39_options (+12 more)</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>W39B-PEAD</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Earnings surprise (SUE), EPS-trend proxy and a post-earnings-drift scan</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Earnings surprise and PEAD (gap analysis 4.7)</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4; docs/ANALYSIS_TOOLS_AND_SIGNALS_PLAN_2026-10.md</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J54" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K54" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>research/earnings_surprise.py: SUE and revenue SUE vs the same quarter a year earlier (8-quarter standard deviation, 4 needed), point in time from the NSE broadcast date; EPS-trend revisions proxy; pead_bull / pead_bear scans (|SUE| &gt;= 2, first session after the filing, 60-session horizon) stored and tracked like every scan, alerts held until 30 closed signals with positive expectancy; 20:35 job; screener fields and a preset; GET /api/research/earnings-surprise/{symbol}</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA; needs 9+ quarters of NSE XBRL history (run the history backfill); no consensus estimates (ATIP's own history only); filings arrive with the Saturday fundamentals job</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>research/earnings_surprise.py; research/tech_signals.py</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_earnings_surprise.py</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>W39b developed 2026-10-08 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5)</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_earnings_surprise.py | 85% of 905 lines in 2 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+6 more)</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>For a consensus-based surprise: a consensus estimates feed (not available today)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>W39B-MFA</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Wealth / Mutual funds</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Mutual fund analytics on stored AMFI NAVs (read-only)</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Value Research / Kuvera-style scheme analytics (gap analysis 4.3)</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4; docs/ANALYSIS_TOOLS_AND_SIGNALS_PLAN_2026-10.md</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J55" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K55" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>data/mf_analytics.py: point-to-point and CAGR returns, 1Y / 3Y rolling returns with hurdle stats, volatility / Sharpe / Sortino, drawdown with dates, beta / alpha / tracking error vs a price index, SIP and lump-sum XIRR, category rank among stored schemes, side-by-side compare; 3 read-only GET routes; scheme detail card on /data-platform</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA. Holding MFs in the wealth ledger stays out of scope (owner Scope Exclusions); benchmark is a price index, not total return; peers limited to stored schemes</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>data/mf_analytics.py; dashboard/w35_routes.py; dashboard/w35_page.py</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_mf_analytics.py</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>W39b developed 2026-10-08 on branch claude/wizardly-curie-fbjeoa (PR #5); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>W39b (PR #5)</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w39b_mf_analytics.py | 86% of 626 lines in 3 key file(s) run by: test_auto_recover, test_w39_ml_regime_lineage_surface, test_w39_perf_budget, test_w39_ui_smoke, test_w39b_mf_analytics</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z51"/>
+  <autoFilter ref="A1:Z55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47694,7 +48678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -47946,22 +48930,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Owner decision: payment gateway (Razorpay / Stripe / Cashfree) and its merchant credentials</t>
+          <t>Owner: a KYC-activated Razorpay business account with Invoices and Subscriptions enabled; store RAZORPAY_KEY_ID / RAZORPAY_KEY_SECRET / WEBHOOK_SECRET_RAZORPAY with python -m ops vault-set; registering the webhook URL needs ENT-07 (public HTTPS)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Plans, subscriptions, invoices DRAFT/OPEN/PAID, provider interface (sandbox/noop), dunning + grace, payment webhook consumer</t>
+          <t>Plans, subscriptions, invoices DRAFT/OPEN/PAID, provider interface (sandbox/noop), dunning + grace, payment webhook consumer. W39b (gateway decision delegated: Razorpay -- UPI / cards / netbanking, native Subscriptions): enterprise/razorpay.py on the existing payments interface -- REST v1 invoices with idempotent receipts, customers, plans, autopay subscriptions, cancel; signed webhook mapping onto invoices, payments, refunds, dunning and grace (out-of-order safe, money once per Razorpay id); reconcile() polling so payments settle without a public webhook; keys only from the vault; live keys refused without billing.razorpay.allow_live and the production environment</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Payment gateway (owner decision)</t>
+          <t>Owner: run the flows in Razorpay test mode (docs/BILLING_RAZORPAY.md); GST tax lines are not built (ENT-14 PAYMENTS-TAX)</t>
         </is>
       </c>
     </row>
@@ -48079,116 +49063,79 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>OPS-12</t>
+          <t>EX-19</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Dhan token auto-renewal (TOTP)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+          <t>Broker-side GTT / forever orders</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Owner input (not a code blocker): dhan_pin + base32 dhan_totp_secret from web.dhan.co</t>
+          <t>Owner authorization for LIVE broker order placement (live trading is off by design) and the Dhan forever-order API enabled on the account</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>tools/dhan_token_refresh.py (RenewToken with the documented dhanClientId header, else TOTP + PIN generateAccessToken; writes config or vault), run daily at 06:30 and at login by the macOS LaunchAgent com.atip.dhan-token-refresh (W39, PR #4) and at 08:00 by the Windows task. W39b's own scheduler job was dropped on merging #4 (two renewals a day)</t>
+          <t>ATIP-side trigger rules (orders/rules.py) fire while ATIP runs; nothing is placed at the broker</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Owner: add dhan_pin + dhan_totp_secret (or vault them) once; run deploy/launchd/install.sh token</t>
+          <t>Place / modify / cancel broker GTT (Dhan forever-order API, Kite GTT) for LIVE positions</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EX-17</t>
+          <t>W39B-PEAD</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Aggressive exit: enable flag + CRI-spike / momentum-decay exit</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>Earnings surprise (SUE), EPS-trend proxy and a post-earnings-drift scan</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Owner decision: (1) should aggressive_enabled=false stop `python -m strategy.live --manage` (today it runs regardless)? (2) add a CRI-spike exit (threshold?) and route orders through the W4 risk engine? Changing either alters live exit behaviour</t>
+          <t>For a consensus-based surprise: a consensus estimates feed (not available today)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>strategy/aggressive.py: ATR trail, T1 partial, T2 checkpoint; DEFAULTS aggressive_enabled=False but no code reads the flag (off only because nothing schedules strategy.live); bypasses the W4 risk engine</t>
+          <t>research/earnings_surprise.py: SUE and revenue SUE vs the same quarter a year earlier (8-quarter standard deviation, 4 needed), point in time from the NSE broadcast date; EPS-trend revisions proxy; pead_bull / pead_bear scans (|SUE| &gt;= 2, first session after the filing, 60-session horizon) stored and tracked like every scan, alerts held until 30 closed signals with positive expectancy; 20:35 job; screener fields and a preset; GET /api/research/earnings-surprise/{symbol}</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Decide whether the flag gates strategy.live enter/manage, and whether to add a CRI-spike exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>EX-19</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Broker-side GTT / forever orders</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Owner authorization for LIVE broker order placement (live trading is off by design) and the Dhan forever-order API enabled on the account</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>ATIP-side trigger rules (orders/rules.py) fire while ATIP runs; nothing is placed at the broker</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Place / modify / cancel broker GTT (Dhan forever-order API, Kite GTT) for LIVE positions</t>
+          <t>Independent QA; needs 9+ quarters of NSE XBRL history (run the history backfill); no consensus estimates (ATIP's own history only); filings arrive with the Saturday fundamentals job</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48290,7 +49237,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Owner input (not a code blocker): dhan_pin + base32 dhan_totp_secret from web.dhan.co</t>
+          <t>Independent QA (QA-001) + owner UAT (UAT-001)</t>
         </is>
       </c>
     </row>
@@ -48485,7 +49432,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 32/32 features developed (15 COMPLETED, 17 awaiting independent QA); automated tests: 17 covered, 15 partly, 0 none</t>
+          <t>[2026-10-07] 32/32 features developed (15 COMPLETED, 17 awaiting independent QA); automated tests: 19 covered, 13 partly, 0 none</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -48525,12 +49472,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 46/49 features developed (25 COMPLETED, 21 awaiting independent QA); automated tests: 25 covered, 21 partly, 0 none; BLOCKED: BR-08, EX-17, EX-19</t>
+          <t>[2026-10-07] 47/49 features developed (25 COMPLETED, 22 awaiting independent QA); automated tests: 26 covered, 21 partly, 0 none; BLOCKED: BR-08, EX-19</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Owner authorization for LIVE broker order placement (live trading is off by design) and the Dhan forever-order API enabled on the account | Owner decision: (1) should aggressive_enabled=false stop `python -m strategy.live --manage` (today it runs regardless)? (2) add a CRI-spike exit (threshold?) and route orders through the W4 risk engine? Changing either alters live exit behaviour | Owner: a Dhan-issued sandbox token, then run python -m orders.sandbox_check --place-test-order</t>
+          <t>Owner authorization for LIVE broker order placement (live trading is off by design) and the Dhan forever-order API enabled on the account | Owner: a Dhan-issued sandbox token, then run python -m orders.sandbox_check --place-test-order</t>
         </is>
       </c>
     </row>
@@ -48605,7 +49552,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 18/23 features developed (2 COMPLETED, 16 awaiting independent QA); automated tests: 4 covered, 14 partly, 0 none; BLOCKED: ENT-07, ENT-14, ENT-08, ENT-04, ENT-16</t>
+          <t>[2026-10-07] 18/23 features developed (2 COMPLETED, 16 awaiting independent QA); automated tests: 5 covered, 13 partly, 0 none; BLOCKED: ENT-07, ENT-14, ENT-08, ENT-04, ENT-16</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -49171,7 +50118,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 2 covered, 4 partly, 0 none</t>
+          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 4 covered, 2 partly, 0 none</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -49591,7 +50538,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[2026-10-07] 5/6 features developed (0 COMPLETED, 5 awaiting independent QA); automated tests: 0 covered, 5 partly, 0 none; BLOCKED: ENT-08</t>
+          <t>[2026-10-07] 5/6 features developed (0 COMPLETED, 5 awaiting independent QA); automated tests: 1 covered, 4 partly, 0 none; BLOCKED: ENT-08</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -49885,7 +50832,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[2026-10-07] 52/55 features developed (1 COMPLETED, 51 awaiting independent QA); automated tests: 53 covered, 0 partly, 0 none; BLOCKED: EX-17, EX-19; open: QA-001</t>
+          <t>[2026-10-07] 57/59 features developed (1 COMPLETED, 56 awaiting independent QA); automated tests: 58 covered, 0 partly, 0 none; BLOCKED: EX-19; open: QA-001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -50075,7 +51022,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>84.5</v>
+        <v>85</v>
       </c>
       <c r="G5" t="n">
         <v>19</v>
@@ -50139,14 +51086,14 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>79.7</v>
+        <v>80.2</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BR-08, EX-17, EX-19</t>
+          <t>BR-08, EX-19</t>
         </is>
       </c>
     </row>

--- a/docs/ATIP_Master_Deployment_Tracker_Wave_1_to_20_UPDATED.xlsx
+++ b/docs/ATIP_Master_Deployment_Tracker_Wave_1_to_20_UPDATED.xlsx
@@ -22,8 +22,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Legend" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Features'!$A$1:$Z$332</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'New Items (W39)'!$A$1:$Z$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Features'!$A$1:$Z$334</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'New Items (W39)'!$A$1:$Z$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Blockers'!$A$1:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Master Tracker'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Gap Analysis'!$A$1:$E$15</definedName>
@@ -32,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'PERF-001 Detail'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Implementation Sequence'!$A$1:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Master Dev Prompt'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Owner CSV vs repo'!$A$1:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Owner CSV vs repo'!$A$1:$G$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14">
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1132,55 +1132,58 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>W40 (PR #9)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>Developed</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>0 Delivered baseline (maintain)</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>58</v>
-      </c>
-      <c r="C43" t="n">
-        <v>58</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1 Foundation</t>
+          <t>0 Delivered baseline (maintain)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C44" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1189,14 +1192,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2 Quant Research (data, factors, backtesting)</t>
+          <t>1 Foundation</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C45" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1205,14 +1208,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3 Strategy Engine</t>
+          <t>2 Quant Research (data, factors, backtesting)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C46" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -1221,78 +1224,78 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4 AI/ML</t>
+          <t>3 Strategy Engine</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C47" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5 Risk &amp; Portfolio</t>
+          <t>4 AI/ML</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C48" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6 Execution</t>
+          <t>5 Risk &amp; Portfolio</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7 Advanced Quant</t>
+          <t>6 Execution</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C50" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8 Production Hardening</t>
+          <t>7 Advanced Quant</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -1301,14 +1304,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8 Production hardening</t>
+          <t>8 Production Hardening</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -1317,48 +1320,64 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9 Enterprise SaaS (final objective)</t>
+          <t>8 Production hardening</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C53" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10 Wealth track (Waves 11-20)</t>
+          <t>9 Enterprise SaaS (final objective)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>10 Wealth track (Waves 11-20)</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>11</v>
+      </c>
+      <c r="C55" t="n">
+        <v>9</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>11 W39 reconciliation (owner tracker 2026-10-07)</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>54</v>
-      </c>
-      <c r="C55" t="n">
-        <v>53</v>
-      </c>
-      <c r="D55" t="n">
+      <c r="B56" t="n">
+        <v>56</v>
+      </c>
+      <c r="C56" t="n">
+        <v>55</v>
+      </c>
+      <c r="D56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2544,7 +2563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2596,12 +2615,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BT-14</t>
+          <t>BT-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Robustness</t>
+          <t>Parameter optimisation</t>
         </is>
       </c>
       <c r="C2" s="18" t="inlineStr">
@@ -2626,29 +2645,29 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>W23: robustness battery (costs x2, slippage x3, universe halves, period halves, regimes, Monte Carlo) with verdict. W39b: backtest/cpcv.py -- combinatorial purg</t>
+          <t>W23: grid / random / adaptive optimiser with trial runs, test-window refusal, Deflated Sharpe + overfit warning. W40: method="bayes" -- a Tree-structured Parzen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DP-08</t>
+          <t>BT-14</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Derivatives data</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E3" s="18" t="inlineStr">
@@ -2658,24 +2677,24 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
+          <t>W23: robustness battery (costs x2, slippage x3, universe halves, period halves, regimes, Monte Carlo) with verdict. W39b: backtest/cpcv.py -- combinatorial purg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SE-05</t>
+          <t>DP-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AI-driven strategies</t>
+          <t>Derivatives data</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
@@ -2685,71 +2704,71 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>W5 developed 2026-09-25 (incl. completion pass) — framework only, no model trained or validated; independent testing PENDING (ChatGPT); see docs/W5_AI_ML_HANDOF</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NS-05</t>
+          <t>SE-05</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Novelty/decay/source weighting</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>AI-driven strategies</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>W28b developed 2026-10-01 on branch w28b-news-weighting (on w33-wealth-qa) — independent validation PENDING (ChatGPT); see docs/W28B_NEWS_WEIGHTING_HANDOFF.md |</t>
+          <t>W5 developed 2026-09-25 (incl. completion pass) — framework only, no model trained or validated; independent testing PENDING (ChatGPT); see docs/W5_AI_ML_HANDOF</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NS-06</t>
+          <t>NS-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Earnings call / announcement NLP</t>
+          <t>Novelty/decay/source weighting</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -2759,7 +2778,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
@@ -2769,7 +2788,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2781,12 +2800,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ML-02</t>
+          <t>NS-06</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Deep learning</t>
+          <t>Earnings call / announcement NLP</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -2806,24 +2825,24 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W28b developed 2026-10-01 on branch w28b-news-weighting (on w33-wealth-qa) — independent validation PENDING (ChatGPT); see docs/W28B_NEWS_WEIGHTING_HANDOFF.md |</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ML-04</t>
+          <t>ML-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Reinforcement learning</t>
+          <t>Deep learning</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
@@ -2843,7 +2862,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2855,59 +2874,59 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PF-06</t>
+          <t>ML-04</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Rebalancing</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
+          <t>Reinforcement learning</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>W6 developed 2026-09-25 — coding only; independent testing PENDING (ChatGPT); see docs/W6_ADVANCED_QUANT_HANDOFF.md</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DP-04</t>
+          <t>PF-06</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Tick data</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Rebalancing</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
@@ -2917,24 +2936,24 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
+          <t>W6 developed 2026-09-25 — coding only; independent testing PENDING (ChatGPT); see docs/W6_ADVANCED_QUANT_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DP-05</t>
+          <t>DP-04</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Order book / depth</t>
+          <t>Tick data</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -2966,22 +2985,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AF-06</t>
+          <t>DP-05</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Derivatives factors</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>Order book / depth</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -2991,34 +3010,34 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EX-11</t>
+          <t>AF-06</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Execution algos</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Derivatives factors</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
@@ -3033,29 +3052,29 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>W34 developed 2026-10-01 on branch w34-execution-microstructure — independent validation PENDING (ChatGPT); see docs/W34_EXECUTION_MICROSTRUCTURE_HANDOFF.md | W</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EX-12</t>
+          <t>QR-05</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Market impact model</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Stat-arb / pairs / cointegration</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
@@ -3065,24 +3084,24 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>W34 developed 2026-10-01 on branch w34-execution-microstructure — independent validation PENDING (ChatGPT); see docs/W34_EXECUTION_MICROSTRUCTURE_HANDOFF.md | W</t>
+          <t>W6 developed 2026-09-25 — coding only; independent testing PENDING (ChatGPT); see docs/W6_ADVANCED_QUANT_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EX-15</t>
+          <t>EX-11</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Latency telemetry</t>
+          <t>Execution algos</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -3114,12 +3133,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EX-16</t>
+          <t>EX-12</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Event-driven OMS</t>
+          <t>Market impact model</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
@@ -3129,7 +3148,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E16" s="18" t="inlineStr">
@@ -3151,12 +3170,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BT-17</t>
+          <t>EX-15</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Event-driven backtester</t>
+          <t>Latency telemetry</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -3188,12 +3207,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>DP-14</t>
+          <t>EX-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Macroeconomic data</t>
+          <t>Event-driven OMS</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -3203,7 +3222,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
@@ -3218,19 +3237,19 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
+          <t>W34 developed 2026-10-01 on branch w34-execution-microstructure — independent validation PENDING (ChatGPT); see docs/W34_EXECUTION_MICROSTRUCTURE_HANDOFF.md | W</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AD-01</t>
+          <t>BT-17</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Alt-data framework</t>
+          <t>Event-driven backtester</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -3255,19 +3274,19 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
+          <t>W34 developed 2026-10-01 on branch w34-execution-microstructure — independent validation PENDING (ChatGPT); see docs/W34_EXECUTION_MICROSTRUCTURE_HANDOFF.md | W</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AD-02</t>
+          <t>DP-14</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Alt-data sources</t>
+          <t>Macroeconomic data</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -3287,7 +3306,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3299,12 +3318,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DP-22</t>
+          <t>AD-01</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Point-in-time data lake</t>
+          <t>Alt-data framework</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -3314,7 +3333,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
@@ -3336,12 +3355,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DP-21</t>
+          <t>AD-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Multi-asset data</t>
+          <t>Alt-data sources</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -3366,56 +3385,56 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check: AMFI mutual-</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>API-05</t>
+          <t>DP-22</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>API contracts/docs</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
+          <t>Point-in-time data lake</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
-        </is>
-      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check 2026-10-07: c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>API-06</t>
+          <t>DP-21</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Widget JSON schemas</t>
+          <t>Multi-asset data</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
@@ -3425,7 +3444,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
@@ -3435,34 +3454,34 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W35 developed 2026-10-01 on branch w35-data-platform — independent validation PENDING (ChatGPT); see docs/W35_DATA_PLATFORM_HANDOFF.md | W39 check: AMFI mutual-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>DBS-05</t>
+          <t>API-05</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Scalable database</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>API contracts/docs</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
@@ -3472,24 +3491,24 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
+          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ENT-06</t>
+          <t>API-06</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Per-user broker credential vault</t>
+          <t>Widget JSON schemas</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
@@ -3499,7 +3518,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
@@ -3514,19 +3533,19 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ENT-14</t>
+          <t>DBS-05</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Regulatory approvals</t>
+          <t>Scalable database</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
@@ -3539,14 +3558,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3558,12 +3577,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SEC-05</t>
+          <t>ENT-06</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Compliance monitoring</t>
+          <t>Per-user broker credential vault</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
@@ -3583,24 +3602,24 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
+          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ENT-17</t>
+          <t>ENT-14</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Data privacy</t>
+          <t>Regulatory approvals</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
@@ -3613,14 +3632,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3632,49 +3651,49 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ENT-04</t>
+          <t>SEC-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Subscriptions &amp; billing</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>Compliance monitoring</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>W7 developed 2026-09-25 (enterprise layer, off by default) — coding only; independent testing PENDING (ChatGPT); see docs/W7_ENTERPRISE_HANDOFF.md</t>
+          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ENT-09</t>
+          <t>ENT-17</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Mobile apps</t>
+          <t>Data privacy</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
@@ -3694,7 +3713,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3706,27 +3725,27 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>API-03</t>
+          <t>ENT-04</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Versioned public API</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+          <t>Subscriptions &amp; billing</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3736,19 +3755,19 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
+          <t>W7 developed 2026-09-25 (enterprise layer, off by default) — coding only; independent testing PENDING (ChatGPT); see docs/W7_ENTERPRISE_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PF-12</t>
+          <t>ENT-09</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Multi-broker import</t>
+          <t>Mobile apps</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
@@ -3768,34 +3787,34 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
+          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>BR-07</t>
+          <t>API-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Additional brokers</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>YET TO START</t>
+          <t>Versioned public API</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
@@ -3805,24 +3824,24 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
+          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ENT-15</t>
+          <t>PF-12</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Multi-asset trading</t>
+          <t>Multi-broker import</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
@@ -3842,7 +3861,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3854,12 +3873,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SE-10</t>
+          <t>BR-07</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>No/low-code strategy builder</t>
+          <t>Additional brokers</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
@@ -3879,24 +3898,24 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ML-16</t>
+          <t>ENT-15</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>AI chat assistant</t>
+          <t>Multi-asset trading</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
@@ -3921,19 +3940,19 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
+          <t>W37 developed 2026-10-02 on branch w37-brokers-multi-asset; 9 new tests + full suite 508/508 pass; independent validation PENDING (ChatGPT); see docs/W37_BROKER</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>OPS-04</t>
+          <t>SE-10</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Cloud deployment</t>
+          <t>No/low-code strategy builder</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
@@ -3953,98 +3972,98 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ENT-16</t>
+          <t>ML-16</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Scalability, HA &amp; observability</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>AI chat assistant</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
+          <t>W36 developed 2026-10-02 on branch w36-ml-strategy-tooling; 13 new tests + full suite 499/499 pass; independent validation PENDING (ChatGPT); see docs/W36_ML_ST</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>PERF-001</t>
+          <t>OPS-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Investor performance attribution</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
+          <t>Cloud deployment</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>YET TO START</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
         <is>
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED BUT NOT VERIFIED</t>
-        </is>
-      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>branch w20-release; merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
+          <t>W38 developed 2026-10-02 on branch w38-platform-compliance; 15 new tests + full suite pass; independent validation PENDING (ChatGPT); see docs/W38_PLATFORM_COMP</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>QA-001</t>
+          <t>ENT-16</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Wealth QA / security / performance</t>
+          <t>Scalability, HA &amp; observability</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -4054,64 +4073,138 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>RC line = w33-wealth-qa (W11-W32); merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
+          <t>W8 developed 2026-09-25 (production hardening) — coding only; independent testing PENDING (ChatGPT); see docs/W8_PRODUCTION_HARDENING_HANDOFF.md</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>PERF-001</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Investor performance attribution</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>branch w20-release; merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>QA-001</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Wealth QA / security / performance</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>RC line = w33-wealth-qa (W11-W32); merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>UAT-001</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Beta / UAT</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E42" s="19" t="inlineStr">
+      <c r="E44" s="19" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>RC line = w33-wealth-qa; merged to master; not deployed | W39 check 2026-10-07: commit is an ancestor of master</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G42"/>
+  <autoFilter ref="A1:G44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4284,7 +4377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z332"/>
+  <dimension ref="A1:Z334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4754,7 +4847,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>92% of 24 lines in 1 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_regressions, test_risk_controls (+21 more)</t>
+          <t>95% of 41 lines in 1 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_regressions, test_risk_controls (+28 more)</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
@@ -4858,7 +4951,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib</t>
+          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w40_stock_chart</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr"/>
@@ -4962,7 +5055,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib</t>
+          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w40_stock_chart</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr"/>
@@ -5066,7 +5159,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_technical_rs_fib.py | 86% of 728 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
+          <t>tests/test_w39_technical_rs_fib.py | 86% of 728 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules, test_w40_stock_chart</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr"/>
@@ -5170,7 +5263,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib</t>
+          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w40_stock_chart</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr"/>
@@ -6106,7 +6199,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>86% of 346 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
+          <t>86% of 346 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+65 more)</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr"/>
@@ -6210,7 +6303,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>35% of 1222 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+1 more)</t>
+          <t>35% of 1229 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+2 more)</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr"/>
@@ -6522,7 +6615,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_perf_budget, test_w39_performance_detail (+5 more)</t>
+          <t>64% of 301 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_perf_budget, test_w39_performance_detail (+6 more)</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr"/>
@@ -6626,7 +6719,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_perf_budget, test_w39_performance_detail (+5 more)</t>
+          <t>64% of 301 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_perf_budget, test_w39_performance_detail (+6 more)</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr"/>
@@ -6938,7 +7031,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+10 more)</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -7042,7 +7135,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+10 more)</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr"/>
@@ -7146,7 +7239,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+10 more)</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr"/>
@@ -7250,7 +7343,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+10 more)</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr"/>
@@ -7978,7 +8071,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>tests/test_paper_broker.py | 55% of 321 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w37_brokers_multi_asset, test_w39_exec_data_tests, test_w39_performance_detail, test_w39_qa_suite, test_wealth_dna_holdings (+1 more)</t>
+          <t>tests/test_paper_broker.py | 55% of 321 lines in 1 key file(s) run by: test_paper_broker, test_risk_controls, test_strategy_live, test_w37_brokers_multi_asset, test_w39_exec_data_tests, test_w39_performance_detail, test_w39_qa_suite, test_w40_futures_backtest (+4 more)</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr"/>
@@ -8394,7 +8487,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr"/>
@@ -8498,7 +8591,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr"/>
@@ -8602,7 +8695,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr"/>
@@ -8706,7 +8799,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr"/>
@@ -8810,7 +8903,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr"/>
@@ -8914,7 +9007,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr"/>
@@ -9018,7 +9111,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr"/>
@@ -9122,7 +9215,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr"/>
@@ -9226,7 +9319,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr"/>
@@ -9330,7 +9423,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr"/>
@@ -9434,7 +9527,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr"/>
@@ -9642,7 +9735,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>65% of 808 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+29 more)</t>
+          <t>64% of 812 lines in 1 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+36 more)</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr"/>
@@ -9746,7 +9839,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>93% of 43 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w38_platform_compliance, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+24 more)</t>
+          <t>93% of 43 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w38_platform_compliance, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+30 more)</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr"/>
@@ -9850,7 +9943,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>86% of 346 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
+          <t>86% of 346 lines in 1 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+65 more)</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr"/>
@@ -10178,7 +10271,7 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>78% of 234 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_index_feed, test_risk_controls, test_w39_notify_transactions</t>
+          <t>76% of 234 lines in 1 key file(s) run by: test_fii_dii_and_delivery_factor, test_index_feed, test_regressions, test_w39_notify_transactions</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr"/>
@@ -10298,7 +10391,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>69% of 360 lines in 2 key file(s) run by: test_auto_recover, test_w39_ops_tests, test_w39_perf_budget, test_w39b_razorpay</t>
+          <t>68% of 360 lines in 2 key file(s) run by: test_auto_recover, test_w39_ops_tests, test_w39_perf_budget, test_w39b_razorpay</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr"/>
@@ -10622,7 +10715,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>47% of 3163 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+8 more)</t>
+          <t>46% of 3170 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+9 more)</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr"/>
@@ -10742,7 +10835,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>85% of 936 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
+          <t>85% of 936 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+65 more)</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr"/>
@@ -10862,7 +10955,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>47% of 3163 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+8 more)</t>
+          <t>46% of 3170 lines in 5 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_job_monitoring, test_market_health, test_regressions, test_risk_controls, test_signal_pipeline (+9 more)</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr"/>
@@ -10982,7 +11075,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>72% of 1105 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
+          <t>72% of 1105 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+65 more)</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr"/>
@@ -11098,7 +11191,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>46% of 1568 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
+          <t>46% of 1575 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+65 more)</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr"/>
@@ -11218,7 +11311,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>39% of 1338 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+7 more)</t>
+          <t>39% of 1345 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+8 more)</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr"/>
@@ -11338,7 +11431,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>64% of 1070 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_api_contract, test_w39_backtest (+31 more)</t>
+          <t>63% of 1074 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_api_contract, test_w39_backtest (+38 more)</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr"/>
@@ -11578,7 +11671,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>66% of 502 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
+          <t>66% of 502 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+10 more)</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr"/>
@@ -11810,7 +11903,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>57% of 515 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
+          <t>57% of 515 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+65 more)</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr"/>
@@ -11930,7 +12023,7 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>31% of 1391 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+1 more)</t>
+          <t>31% of 1398 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+2 more)</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr"/>
@@ -12266,7 +12359,7 @@
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>test_postmarket_scores_a_seeded_session_end_to_end; test_postmarket_refuses_a_session_that_is_a_copy_of_the_previous_one | 35% of 1222 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+1 more)</t>
+          <t>test_postmarket_scores_a_seeded_session_end_to_end; test_postmarket_refuses_a_session_that_is_a_copy_of_the_previous_one | 35% of 1229 lines in 1 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+2 more)</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr"/>
@@ -12378,7 +12471,7 @@
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>30% of 1676 lines in 4 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_fundamentals_screener, test_job_monitoring, test_signal_pipeline, test_w38_platform_compliance, test_w39_history, test_w39_notify_transactions (+3 more)</t>
+          <t>30% of 1683 lines in 4 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_fundamentals_screener, test_job_monitoring, test_signal_pipeline, test_w38_platform_compliance, test_w39_history, test_w39_notify_transactions (+4 more)</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr"/>
@@ -12942,7 +13035,7 @@
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>41% of 881 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
+          <t>40% of 881 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr"/>
@@ -13062,7 +13155,7 @@
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>39% of 1338 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+7 more)</t>
+          <t>39% of 1345 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_risk_controls, test_signal_pipeline, test_w38_platform_compliance, test_w39_api_contract, test_w39_exec_data_tests (+8 more)</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr"/>
@@ -13182,7 +13275,7 @@
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>63% of 942 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+33 more)</t>
+          <t>62% of 946 lines in 2 key file(s) run by: test_auto_recover, test_index_feed, test_job_monitoring, test_regressions, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20 (+40 more)</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr"/>
@@ -13302,7 +13395,7 @@
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>76% of 480 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
+          <t>76% of 480 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+65 more)</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr"/>
@@ -13418,7 +13511,7 @@
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>70% of 807 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_exec_data_tests (+8 more)</t>
+          <t>70% of 807 lines in 2 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_exec_data_tests (+13 more)</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr"/>
@@ -13538,7 +13631,7 @@
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+10 more)</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr"/>
@@ -13658,7 +13751,7 @@
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+10 more)</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr"/>
@@ -14110,7 +14203,7 @@
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>40% of 1345 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+1 more)</t>
+          <t>40% of 1352 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+2 more)</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr"/>
@@ -14230,7 +14323,7 @@
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>83% of 459 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
+          <t>83% of 459 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+65 more)</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr"/>
@@ -14454,7 +14547,7 @@
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>58% of 1170 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
+          <t>58% of 1170 lines in 3 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+65 more)</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr"/>
@@ -14566,7 +14659,7 @@
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>86% of 728 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
+          <t>86% of 728 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules, test_w40_stock_chart</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr"/>
@@ -14674,7 +14767,7 @@
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib</t>
+          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w40_stock_chart</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr"/>
@@ -15006,7 +15099,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib</t>
+          <t>80% of 357 lines in 1 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w40_stock_chart</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr"/>
@@ -15230,7 +15323,7 @@
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>61% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
+          <t>68% of 269 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr"/>
@@ -15454,7 +15547,7 @@
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>61% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
+          <t>68% of 269 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr"/>
@@ -16094,9 +16187,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K108" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K108" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -16162,7 +16255,7 @@
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>46% of 242 lines in 3 key file(s) run by: test_auto_recover, test_w39_quant_portfolio</t>
+          <t>70% of 242 lines in 3 key file(s) run by: test_auto_recover, test_w39_quant_portfolio, test_w40_futures_backtest</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr"/>
@@ -16274,7 +16367,7 @@
       </c>
       <c r="Y109" s="2" t="inlineStr">
         <is>
-          <t>45% of 167 lines in 2 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial, test_w39_exec_data_tests</t>
+          <t>45% of 167 lines in 2 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial, test_w39_exec_data_tests, test_w39b_event_driven_skips, test_w40_futures_backtest, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z109" s="2" t="inlineStr"/>
@@ -16390,7 +16483,7 @@
       </c>
       <c r="Y110" s="2" t="inlineStr">
         <is>
-          <t>87% of 423 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+55 more)</t>
+          <t>87% of 423 lines in 2 key file(s) run by: test_aggressive_lifecycle, test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_job_monitoring, test_market_health, test_mysql_backend (+65 more)</t>
         </is>
       </c>
       <c r="Z110" s="2" t="inlineStr"/>
@@ -16510,7 +16603,7 @@
       </c>
       <c r="Y111" s="2" t="inlineStr">
         <is>
-          <t>92% of 364 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
+          <t>93% of 409 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo, test_w39b_event_driven_skips (+1 more)</t>
         </is>
       </c>
       <c r="Z111" s="2" t="inlineStr"/>
@@ -16630,7 +16723,7 @@
       </c>
       <c r="Y112" s="2" t="inlineStr">
         <is>
-          <t>96% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo, test_w39b_mf_analytics, test_wealth_performance</t>
+          <t>96% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_mcp, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_bayes_optimize, test_w39b_cpcv_dominance (+6 more)</t>
         </is>
       </c>
       <c r="Z112" s="2" t="inlineStr"/>
@@ -16750,7 +16843,7 @@
       </c>
       <c r="Y113" s="2" t="inlineStr">
         <is>
-          <t>96% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo, test_w39b_mf_analytics, test_wealth_performance</t>
+          <t>96% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_mcp, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_bayes_optimize, test_w39b_cpcv_dominance (+6 more)</t>
         </is>
       </c>
       <c r="Z113" s="2" t="inlineStr"/>
@@ -16862,7 +16955,7 @@
       </c>
       <c r="Y114" s="2" t="inlineStr">
         <is>
-          <t>96% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo, test_w39b_mf_analytics, test_wealth_performance</t>
+          <t>96% of 121 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_mcp, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_bayes_optimize, test_w39b_cpcv_dominance (+6 more)</t>
         </is>
       </c>
       <c r="Z114" s="2" t="inlineStr"/>
@@ -16978,7 +17071,7 @@
       </c>
       <c r="Y115" s="2" t="inlineStr">
         <is>
-          <t>87% of 84 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_contract_note_fees, test_w39_performance_detail, test_w39_qa_suite, test_w39b_cpcv_pbo, test_wealth_performance (+1 more)</t>
+          <t>91% of 131 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_contract_note_fees, test_w39_performance_detail, test_w39_qa_suite, test_w39b_bayes_optimize, test_w39b_cpcv_dominance (+7 more)</t>
         </is>
       </c>
       <c r="Z115" s="2" t="inlineStr"/>
@@ -17098,7 +17191,7 @@
       </c>
       <c r="Y116" s="2" t="inlineStr">
         <is>
-          <t>69% of 29 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
+          <t>69% of 29 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo, test_w39b_event_driven_skips (+1 more)</t>
         </is>
       </c>
       <c r="Z116" s="2" t="inlineStr"/>
@@ -17214,7 +17307,7 @@
       </c>
       <c r="Y117" s="2" t="inlineStr">
         <is>
-          <t>56% of 36 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
+          <t>56% of 36 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo, test_w39b_event_driven_skips (+1 more)</t>
         </is>
       </c>
       <c r="Z117" s="2" t="inlineStr"/>
@@ -17318,7 +17411,7 @@
       </c>
       <c r="Y118" s="2" t="inlineStr">
         <is>
-          <t>87% of 105 lines in 1 key file(s) run by: test_index_feed, test_w39_index_constituents, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_ui_smoke, test_w39b_tf75, test_wealth_api_security (+3 more)</t>
+          <t>84% of 105 lines in 1 key file(s) run by: test_index_feed, test_w39_index_constituents, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_ui_smoke, test_w39b_tf75, test_w40_total_return (+4 more)</t>
         </is>
       </c>
       <c r="Z118" s="2" t="inlineStr"/>
@@ -17438,7 +17531,7 @@
       </c>
       <c r="Y119" s="2" t="inlineStr">
         <is>
-          <t>91% of 500 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio, test_w39b_cpcv_pbo</t>
+          <t>92% of 545 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo (+3 more)</t>
         </is>
       </c>
       <c r="Z119" s="2" t="inlineStr"/>
@@ -17558,7 +17651,7 @@
       </c>
       <c r="Y120" s="2" t="inlineStr">
         <is>
-          <t>81% of 175 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
+          <t>81% of 181 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo, test_w39b_event_driven_skips (+2 more)</t>
         </is>
       </c>
       <c r="Z120" s="2" t="inlineStr"/>
@@ -17678,7 +17771,7 @@
       </c>
       <c r="Y121" s="2" t="inlineStr">
         <is>
-          <t>82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39b_cpcv_pbo</t>
+          <t>83% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo, test_w39b_event_driven_skips, test_w40_futures_backtest</t>
         </is>
       </c>
       <c r="Z121" s="2" t="inlineStr"/>
@@ -17798,7 +17891,7 @@
       </c>
       <c r="Y122" s="2" t="inlineStr">
         <is>
-          <t>94% of 53 lines in 1 key file(s) run by: test_w39_backtest_partial, test_w39_untested_modules</t>
+          <t>94% of 53 lines in 1 key file(s) run by: test_w39_backtest_partial, test_w39_untested_modules, test_w40_futures_backtest</t>
         </is>
       </c>
       <c r="Z122" s="2" t="inlineStr"/>
@@ -17861,7 +17954,7 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -17871,12 +17964,12 @@
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>W23: grid / random / adaptive optimiser with trial runs, test-window refusal, Deflated Sharpe + overfit warning</t>
+          <t>W23: grid / random / adaptive optimiser with trial runs, test-window refusal, Deflated Sharpe + overfit warning. W40: method="bayes" -- a Tree-structured Parzen Estimator (Bergstra et al. 2011) in numpy after a seeded random start, same trial storage and deflated-Sharpe accounting</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>QA; optional true Bayesian search</t>
+          <t>Independent QA</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
@@ -17886,7 +17979,7 @@
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>branch w23-research-backtest; docs/W23_RESEARCH_BACKTEST_HANDOFF.md</t>
+          <t>tests/test_w39b_bayes_optimize.py</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr"/>
@@ -17899,7 +17992,7 @@
       <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr"/>
@@ -17910,7 +18003,7 @@
       </c>
       <c r="Y123" s="2" t="inlineStr">
         <is>
-          <t>71% of 197 lines in 1 key file(s) run by: test_w39_backtest, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo</t>
+          <t>tests/test_w39b_bayes_optimize.py | 88% of 352 lines in 1 key file(s) run by: test_w39_backtest, test_w39_qa_suite, test_w39_untested_modules, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z123" s="2" t="inlineStr"/>
@@ -18104,7 +18197,7 @@
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Independent QA; the stochastic-dominance test is not implemented; CPCV runs on the W2 engine only</t>
+          <t>Independent QA. W40: first / second-order stochastic dominance of the selected trial's out-of-sample results over a random selection (in pbo() and CPCV); CPCV on the event-driven engine (engine="event_driven")</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
@@ -18114,7 +18207,7 @@
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_cpcv_pbo.py</t>
+          <t>tests/test_w39b_cpcv_pbo.py; tests/test_w39b_cpcv_dominance.py</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr"/>
@@ -18138,7 +18231,7 @@
       </c>
       <c r="Y125" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_cpcv_pbo.py | 79% of 531 lines in 2 key file(s) run by: test_w39_backtest, test_w39b_cpcv_pbo</t>
+          <t>tests/test_w39b_cpcv_pbo.py; tests/test_w39b_cpcv_dominance.py | 83% of 678 lines in 2 key file(s) run by: test_w39_backtest, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo</t>
         </is>
       </c>
       <c r="Z125" s="2" t="inlineStr"/>
@@ -18370,7 +18463,7 @@
       </c>
       <c r="Y127" s="2" t="inlineStr">
         <is>
-          <t>32% of 257 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
+          <t>43% of 259 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo, test_w39b_event_driven_skips (+2 more)</t>
         </is>
       </c>
       <c r="Z127" s="2" t="inlineStr"/>
@@ -18482,7 +18575,7 @@
       </c>
       <c r="Y128" s="2" t="inlineStr">
         <is>
-          <t>32% of 257 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_cpcv_pbo</t>
+          <t>43% of 259 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo, test_w39b_event_driven_skips (+2 more)</t>
         </is>
       </c>
       <c r="Z128" s="2" t="inlineStr"/>
@@ -18590,7 +18683,7 @@
       </c>
       <c r="Y129" s="2" t="inlineStr">
         <is>
-          <t>64% of 300 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_perf_budget, test_w39_performance_detail (+5 more)</t>
+          <t>64% of 301 lines in 1 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_w39_exec_data_tests, test_w39_notify_transactions, test_w39_perf_budget, test_w39_performance_detail (+6 more)</t>
         </is>
       </c>
       <c r="Z129" s="2" t="inlineStr"/>
@@ -18926,7 +19019,7 @@
       </c>
       <c r="Y132" s="2" t="inlineStr">
         <is>
-          <t>86% of 728 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules</t>
+          <t>86% of 728 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite, test_w39_technical_rs_fib, test_w39_untested_modules, test_w40_stock_chart</t>
         </is>
       </c>
       <c r="Z132" s="2" t="inlineStr"/>
@@ -19046,7 +19139,7 @@
       </c>
       <c r="Y133" s="2" t="inlineStr">
         <is>
-          <t>17% of 275 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite</t>
+          <t>31% of 347 lines in 2 key file(s) run by: test_regressions, test_w37_brokers_multi_asset, test_w39_qa_suite, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z133" s="2" t="inlineStr"/>
@@ -19710,7 +19803,7 @@
       </c>
       <c r="Y139" s="2" t="inlineStr">
         <is>
-          <t>41% of 834 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
+          <t>40% of 834 lines in 2 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
         </is>
       </c>
       <c r="Z139" s="2" t="inlineStr"/>
@@ -20174,7 +20267,7 @@
       </c>
       <c r="Y143" s="2" t="inlineStr">
         <is>
-          <t>72% of 126 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest_partial</t>
+          <t>88% of 132 lines in 1 key file(s) run by: test_auto_recover, test_w39_backtest_partial, test_w39b_event_driven_skips, test_w40_futures_backtest, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z143" s="2" t="inlineStr"/>
@@ -20402,7 +20495,7 @@
       </c>
       <c r="Y145" s="2" t="inlineStr">
         <is>
-          <t>78% of 195 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial</t>
+          <t>79% of 204 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial, test_w39b_event_driven_skips, test_w40_futures_backtest, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z145" s="2" t="inlineStr"/>
@@ -20522,7 +20615,7 @@
       </c>
       <c r="Y146" s="2" t="inlineStr">
         <is>
-          <t>68% of 98 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial</t>
+          <t>68% of 98 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial, test_w39b_event_driven_skips, test_w40_futures_backtest, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z146" s="2" t="inlineStr"/>
@@ -20642,7 +20735,7 @@
       </c>
       <c r="Y147" s="2" t="inlineStr">
         <is>
-          <t>38% of 119 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract</t>
+          <t>58% of 119 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z147" s="2" t="inlineStr"/>
@@ -20698,9 +20791,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K148" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K148" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -20762,7 +20855,7 @@
       </c>
       <c r="Y148" s="2" t="inlineStr">
         <is>
-          <t>50% of 495 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio</t>
+          <t>66% of 502 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio, test_w39b_event_driven_skips, test_w40_futures_backtest, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z148" s="2" t="inlineStr"/>
@@ -20818,9 +20911,9 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="K149" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K149" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
@@ -20882,7 +20975,7 @@
       </c>
       <c r="Y149" s="2" t="inlineStr">
         <is>
-          <t>50% of 495 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio</t>
+          <t>66% of 502 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio, test_w39b_event_driven_skips, test_w40_futures_backtest, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z149" s="2" t="inlineStr"/>
@@ -21002,7 +21095,7 @@
       </c>
       <c r="Y150" s="2" t="inlineStr">
         <is>
-          <t>88% of 64 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial, test_w39_exec_data_tests</t>
+          <t>88% of 64 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_backtest_partial, test_w39_exec_data_tests, test_w39b_event_driven_skips, test_w40_futures_backtest, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z150" s="2" t="inlineStr"/>
@@ -21478,7 +21571,7 @@
       </c>
       <c r="Y154" s="2" t="inlineStr">
         <is>
-          <t>33% of 1358 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_intraday, test_w39_notify_transactions, test_w39_qa_suite (+2 more)</t>
+          <t>33% of 1365 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_intraday, test_w39_notify_transactions, test_w39_qa_suite (+3 more)</t>
         </is>
       </c>
       <c r="Z154" s="2" t="inlineStr"/>
@@ -21710,7 +21803,7 @@
       </c>
       <c r="Y156" s="2" t="inlineStr">
         <is>
-          <t>91% of 68 lines in 2 key file(s) run by: test_w39_exec_data_tests, test_w39_perf_budget</t>
+          <t>89% of 75 lines in 2 key file(s) run by: test_w39_exec_data_tests, test_w39_perf_budget, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z156" s="2" t="inlineStr"/>
@@ -21834,7 +21927,7 @@
       </c>
       <c r="Y157" s="2" t="inlineStr">
         <is>
-          <t>76% of 104 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_qa_suite</t>
+          <t>76% of 106 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_qa_suite, test_w40_meta_label</t>
         </is>
       </c>
       <c r="Z157" s="2" t="inlineStr"/>
@@ -22074,7 +22167,7 @@
       </c>
       <c r="Y159" s="2" t="inlineStr">
         <is>
-          <t>85% of 159 lines in 1 key file(s) run by: test_auto_recover, test_w39_qa_suite</t>
+          <t>87% of 198 lines in 1 key file(s) run by: test_auto_recover, test_w39_qa_suite, test_w40_meta_label</t>
         </is>
       </c>
       <c r="Z159" s="2" t="inlineStr"/>
@@ -22194,7 +22287,7 @@
       </c>
       <c r="Y160" s="2" t="inlineStr">
         <is>
-          <t>63% of 379 lines in 2 key file(s) run by: test_auto_recover, test_w39_qa_suite</t>
+          <t>71% of 385 lines in 2 key file(s) run by: test_auto_recover, test_w39_qa_suite, test_w40_meta_label</t>
         </is>
       </c>
       <c r="Z160" s="2" t="inlineStr"/>
@@ -22318,7 +22411,7 @@
       </c>
       <c r="Y161" s="2" t="inlineStr">
         <is>
-          <t>70% of 178 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite</t>
+          <t>88% of 184 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite, test_w40_meta_label</t>
         </is>
       </c>
       <c r="Z161" s="2" t="inlineStr"/>
@@ -22374,9 +22467,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K162" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K162" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -22438,7 +22531,7 @@
       </c>
       <c r="Y162" s="2" t="inlineStr">
         <is>
-          <t>57% of 316 lines in 1 key file(s) run by: test_auto_recover, test_w39_qa_suite</t>
+          <t>67% of 322 lines in 1 key file(s) run by: test_auto_recover, test_w39_qa_suite, test_w40_meta_label</t>
         </is>
       </c>
       <c r="Z162" s="2" t="inlineStr"/>
@@ -22678,7 +22771,7 @@
       </c>
       <c r="Y164" s="2" t="inlineStr">
         <is>
-          <t>67% of 475 lines in 2 key file(s) run by: test_auto_recover, test_w39_qa_suite</t>
+          <t>75% of 520 lines in 2 key file(s) run by: test_auto_recover, test_w39_qa_suite, test_w40_meta_label</t>
         </is>
       </c>
       <c r="Z164" s="2" t="inlineStr"/>
@@ -23602,7 +23695,7 @@
       </c>
       <c r="Y172" s="2" t="inlineStr">
         <is>
-          <t>34% of 1420 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w36_ml_strategy_tooling, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite (+3 more)</t>
+          <t>34% of 1427 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w36_ml_strategy_tooling, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite (+4 more)</t>
         </is>
       </c>
       <c r="Z172" s="2" t="inlineStr"/>
@@ -23950,7 +24043,7 @@
       </c>
       <c r="Y175" s="2" t="inlineStr">
         <is>
-          <t>68% of 598 lines in 3 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite</t>
+          <t>72% of 614 lines in 3 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite, test_w40_meta_label</t>
         </is>
       </c>
       <c r="Z175" s="2" t="inlineStr"/>
@@ -24302,7 +24395,7 @@
       </c>
       <c r="Y178" s="2" t="inlineStr">
         <is>
-          <t>36% of 484 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
+          <t>39% of 507 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z178" s="2" t="inlineStr"/>
@@ -24414,7 +24507,7 @@
       </c>
       <c r="Y179" s="2" t="inlineStr">
         <is>
-          <t>23% of 342 lines in 1 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
+          <t>29% of 365 lines in 1 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z179" s="2" t="inlineStr"/>
@@ -24534,7 +24627,7 @@
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>24% of 346 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
+          <t>30% of 369 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr"/>
@@ -24646,7 +24739,7 @@
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>45% of 595 lines in 2 key file(s) run by: test_auto_recover, test_w39_risk_gateway</t>
+          <t>46% of 600 lines in 2 key file(s) run by: test_auto_recover, test_w39_risk_gateway, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr"/>
@@ -24758,7 +24851,7 @@
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>37% of 937 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_risk_gateway, test_w39_ui_smoke</t>
+          <t>40% of 965 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_risk_gateway, test_w39_ui_smoke, test_w40_option_intents, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr"/>
@@ -24878,7 +24971,7 @@
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>51% of 604 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
+          <t>52% of 609 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke, test_w40_option_intents, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr"/>
@@ -24990,7 +25083,7 @@
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>46% of 692 lines in 3 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
+          <t>47% of 697 lines in 3 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke (+1 more)</t>
         </is>
       </c>
       <c r="Z184" s="2" t="inlineStr"/>
@@ -25102,7 +25195,7 @@
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>52% of 933 lines in 3 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
+          <t>53% of 938 lines in 3 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+10 more)</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr"/>
@@ -25222,7 +25315,7 @@
       </c>
       <c r="Y186" s="2" t="inlineStr">
         <is>
-          <t>51% of 604 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
+          <t>52% of 609 lines in 2 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke, test_w40_option_intents, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z186" s="2" t="inlineStr"/>
@@ -25330,7 +25423,7 @@
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+5 more)</t>
+          <t>66% of 338 lines in 1 key file(s) run by: test_auto_recover, test_job_monitoring, test_risk_controls, test_strategy_live, test_w38_platform_compliance, test_w39_backtest, test_w39_backtest_partial, test_w39_notify_transactions (+10 more)</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr"/>
@@ -25682,7 +25775,7 @@
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_backtest_partial.py | 73% of 1784 lines in 5 key file(s) run by: test_auto_recover, test_signal_pipeline, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio, test_w39b_cpcv_pbo</t>
+          <t>tests/test_w39_backtest_partial.py | 79% of 1894 lines in 5 key file(s) run by: test_auto_recover, test_signal_pipeline, test_w39_backtest, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio, test_w39b_bayes_optimize, test_w39b_cpcv_dominance (+4 more)</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr"/>
@@ -25794,7 +25887,7 @@
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>23% of 342 lines in 1 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
+          <t>29% of 365 lines in 1 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr"/>
@@ -25906,7 +25999,7 @@
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>23% of 342 lines in 1 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke</t>
+          <t>29% of 365 lines in 1 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr"/>
@@ -26018,7 +26111,7 @@
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>39% of 437 lines in 2 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_w39b_mf_analytics, test_wealth_math (+1 more)</t>
+          <t>43% of 461 lines in 2 key file(s) run by: test_auto_recover, test_w39_mcp, test_w39_perf_budget, test_w39_performance_detail, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_w39b_mf_analytics (+4 more)</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr"/>
@@ -26134,7 +26227,7 @@
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>100% of 4 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>100% of 4 lines in 1 key file(s) run by: test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr"/>
@@ -26250,7 +26343,7 @@
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>55% of 684 lines in 4 key file(s) run by: test_auto_recover, test_paper_broker, test_risk_controls, test_strategy_live, test_w37_brokers_multi_asset, test_w39_exec_data_tests, test_w39_performance_detail, test_w39_qa_suite (+3 more)</t>
+          <t>56% of 695 lines in 4 key file(s) run by: test_auto_recover, test_paper_broker, test_risk_controls, test_strategy_live, test_w37_brokers_multi_asset, test_w39_exec_data_tests, test_w39_performance_detail, test_w39_qa_suite (+6 more)</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr"/>
@@ -26366,7 +26459,7 @@
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>49% of 510 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>52% of 542 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr"/>
@@ -26594,7 +26687,7 @@
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>73% of 135 lines in 1 key file(s) run by: test_w39_exec_data_tests, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
+          <t>73% of 135 lines in 1 key file(s) run by: test_w39_exec_data_tests, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr"/>
@@ -26714,7 +26807,7 @@
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>55% of 669 lines in 2 key file(s) run by: test_auto_recover, test_w39_exec_data_tests, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
+          <t>55% of 674 lines in 2 key file(s) run by: test_auto_recover, test_w39_exec_data_tests, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr"/>
@@ -27066,7 +27159,7 @@
       </c>
       <c r="Y202" s="2" t="inlineStr">
         <is>
-          <t>100% of 78 lines in 2 key file(s) run by: test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>100% of 78 lines in 2 key file(s) run by: test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z202" s="2" t="inlineStr"/>
@@ -27294,7 +27387,7 @@
       </c>
       <c r="Y204" s="2" t="inlineStr">
         <is>
-          <t>82% of 89 lines in 2 key file(s) run by: test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke</t>
+          <t>82% of 89 lines in 2 key file(s) run by: test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_ui_smoke, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z204" s="2" t="inlineStr"/>
@@ -27762,7 +27855,7 @@
       </c>
       <c r="Y208" s="2" t="inlineStr">
         <is>
-          <t>35% of 398 lines in 3 key file(s) run by: test_auto_recover, test_signal_pipeline, test_w39_untested_modules</t>
+          <t>38% of 398 lines in 3 key file(s) run by: test_auto_recover, test_signal_pipeline, test_w39_untested_modules, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z208" s="2" t="inlineStr"/>
@@ -27882,7 +27975,7 @@
       </c>
       <c r="Y209" s="2" t="inlineStr">
         <is>
-          <t>61% of 419 lines in 2 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
+          <t>65% of 422 lines in 2 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z209" s="2" t="inlineStr"/>
@@ -28002,7 +28095,7 @@
       </c>
       <c r="Y210" s="2" t="inlineStr">
         <is>
-          <t>12% of 208 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite</t>
+          <t>32% of 208 lines in 2 key file(s) run by: test_regressions, test_w39_qa_suite, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z210" s="2" t="inlineStr"/>
@@ -28058,14 +28151,14 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K211" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K211" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr">
@@ -28080,17 +28173,17 @@
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
-          <t>Backtest engine does not simulate futures shorts; no auto-roll (re-entry on next signal); paper capital must exceed one lot (~Rs 5-10 lakh notional)</t>
+          <t>Independent QA. W40: the W2 backtest simulates SHORT / COVER as near-month stock futures (lots, margin, daily variation margin, NSE F&amp;O costs, a roll N sessions before expiry; refused, never priced off spot, without futures history); the paper book can auto-roll (futures.auto_roll, off by default). Not modelled: physical settlement, SPAN margin</t>
         </is>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>execution/futures_paper.py; execution/risk_engine.py; execution/order_manager.py; execution/adapters.py; strategy_engine/kinds.py; strategy_engine/decisions.py</t>
+          <t>execution/futures_paper.py; backtest/futures.py; backtest/engine.py</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
         <is>
-          <t>Scratch: SBIN 1 lot short @958.52, cover @959.48, cash -760 = realised -760; reconciliation unaffected</t>
+          <t>tests/test_w40_futures_backtest.py</t>
         </is>
       </c>
       <c r="R211" s="2" t="inlineStr">
@@ -28107,7 +28200,7 @@
       <c r="U211" s="2" t="inlineStr"/>
       <c r="V211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W211" s="2" t="inlineStr">
@@ -28122,7 +28215,7 @@
       </c>
       <c r="Y211" s="2" t="inlineStr">
         <is>
-          <t>50% of 1704 lines in 6 key file(s) run by: test_auto_recover, test_risk_controls, test_signal_pipeline, test_w39_backtest_partial, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio (+2 more)</t>
+          <t>tests/test_w40_futures_backtest.py | 90% of 1065 lines in 3 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_backtest, test_w39_backtest_partial, test_w39_exec_data_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway (+7 more)</t>
         </is>
       </c>
       <c r="Z211" s="2" t="inlineStr"/>
@@ -28178,9 +28271,9 @@
           <t>IMPLEMENTED BUT NOT VERIFIED</t>
         </is>
       </c>
-      <c r="K212" s="15" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="K212" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="L212" s="2" t="inlineStr">
@@ -28200,7 +28293,7 @@
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
-          <t>Same limits as QR-05; lot granularity makes small books non-neutral -- check exposure after sizing</t>
+          <t>Independent QA. W40: long/short portfolios backtest with their futures legs (see QR-05); lot granularity still makes small books non-neutral -- check exposure after sizing</t>
         </is>
       </c>
       <c r="P212" s="2" t="inlineStr">
@@ -28210,7 +28303,7 @@
       </c>
       <c r="Q212" s="2" t="inlineStr">
         <is>
-          <t>Compile + definition validation</t>
+          <t>tests/test_w40_futures_backtest.py</t>
         </is>
       </c>
       <c r="R212" s="2" t="inlineStr">
@@ -28227,7 +28320,7 @@
       <c r="U212" s="2" t="inlineStr"/>
       <c r="V212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W212" s="2" t="inlineStr">
@@ -28242,7 +28335,7 @@
       </c>
       <c r="Y212" s="2" t="inlineStr">
         <is>
-          <t>50% of 495 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio</t>
+          <t>tests/test_w40_futures_backtest.py | 66% of 502 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_backtest_partial, test_w39_qa_suite, test_w39_quant_portfolio, test_w39b_event_driven_skips, test_w40_futures_backtest, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z212" s="2" t="inlineStr"/>
@@ -28362,7 +28455,7 @@
       </c>
       <c r="Y213" s="2" t="inlineStr">
         <is>
-          <t>5% of 258 lines in 4 key file(s) run by: test_auto_recover, test_signal_pipeline</t>
+          <t>11% of 258 lines in 4 key file(s) run by: test_auto_recover, test_signal_pipeline, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z213" s="2" t="inlineStr"/>
@@ -28482,7 +28575,7 @@
       </c>
       <c r="Y214" s="2" t="inlineStr">
         <is>
-          <t>61% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
+          <t>68% of 269 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z214" s="2" t="inlineStr"/>
@@ -28598,7 +28691,7 @@
       </c>
       <c r="Y215" s="2" t="inlineStr">
         <is>
-          <t>11% of 466 lines in 3 key file(s) run by: test_auto_recover</t>
+          <t>29% of 466 lines in 3 key file(s) run by: test_auto_recover, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z215" s="2" t="inlineStr"/>
@@ -28714,7 +28807,7 @@
       </c>
       <c r="Y216" s="2" t="inlineStr">
         <is>
-          <t>71% of 101 lines in 1 key file(s) run by: test_w39_backtest_partial, test_w39_performance_detail, test_w39_untested_modules</t>
+          <t>71% of 101 lines in 1 key file(s) run by: test_w39_backtest_partial, test_w39_performance_detail, test_w39_untested_modules, test_w40_futures_backtest</t>
         </is>
       </c>
       <c r="Z216" s="2" t="inlineStr"/>
@@ -28826,7 +28919,7 @@
       </c>
       <c r="Y217" s="2" t="inlineStr">
         <is>
-          <t>50% of 1316 lines in 4 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live (+5 more)</t>
+          <t>50% of 1327 lines in 4 key file(s) run by: test_auto_recover, test_corporate_actions, test_fii_dii_and_delivery_factor, test_index_feed, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live (+6 more)</t>
         </is>
       </c>
       <c r="Z217" s="2" t="inlineStr"/>
@@ -28942,7 +29035,7 @@
       </c>
       <c r="Y218" s="2" t="inlineStr">
         <is>
-          <t>34% of 407 lines in 3 key file(s) run by: test_auto_recover</t>
+          <t>36% of 418 lines in 3 key file(s) run by: test_auto_recover, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z218" s="2" t="inlineStr"/>
@@ -29020,7 +29113,7 @@
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
-          <t>Independent QA; the engine does not yet report the adapter's skipped decisions the way W2 does</t>
+          <t>Independent QA. W40: reports the adapter's skipped decisions like W2; fix: the end-of-window close-out is now in the last day's return (chained returns overstated final equity by the close-out costs). It still does not trade SHORT (W2 does, as futures)</t>
         </is>
       </c>
       <c r="P219" s="2" t="inlineStr">
@@ -29030,7 +29123,7 @@
       </c>
       <c r="Q219" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_backtest_partial.py (test_event_driven_*)</t>
+          <t>tests/test_w39_backtest_partial.py (test_event_driven_*); tests/test_w39b_event_driven_skips.py</t>
         </is>
       </c>
       <c r="R219" s="2" t="inlineStr"/>
@@ -29058,7 +29151,7 @@
       </c>
       <c r="Y219" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_backtest_partial.py (test_event_driven_*) | 79% of 532 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest_partial</t>
+          <t>tests/test_w39_backtest_partial.py (test_event_driven_*); tests/test_w39b_event_driven_skips.py | 81% of 568 lines in 2 key file(s) run by: test_auto_recover, test_w39_backtest_partial, test_w39b_cpcv_dominance, test_w39b_event_driven_skips, test_w40_futures_backtest</t>
         </is>
       </c>
       <c r="Z219" s="2" t="inlineStr"/>
@@ -30434,7 +30527,7 @@
       </c>
       <c r="Y231" s="2" t="inlineStr">
         <is>
-          <t>49% of 377 lines in 3 key file(s) run by: test_auto_recover, test_w37_brokers_multi_asset, test_w39_api_contract, test_w39_depth20, test_w39_risk_gateway</t>
+          <t>51% of 403 lines in 3 key file(s) run by: test_auto_recover, test_w37_brokers_multi_asset, test_w39_api_contract, test_w39_depth20, test_w39_risk_gateway, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z231" s="2" t="inlineStr"/>
@@ -30550,7 +30643,7 @@
       </c>
       <c r="Y232" s="2" t="inlineStr">
         <is>
-          <t>67% of 486 lines in 4 key file(s) run by: test_mysql_backend, test_postgres_backend, test_w38_platform_compliance, test_w39_perf_budget, test_w39b_razorpay</t>
+          <t>69% of 531 lines in 4 key file(s) run by: test_mysql_backend, test_postgres_backend, test_w36_ml_strategy_tooling, test_w38_platform_compliance, test_w39_perf_budget, test_w39b_razorpay</t>
         </is>
       </c>
       <c r="Z232" s="2" t="inlineStr"/>
@@ -31154,7 +31247,7 @@
       </c>
       <c r="Y237" s="2" t="inlineStr">
         <is>
-          <t>46% of 757 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_risk_gateway, test_w39b_razorpay</t>
+          <t>47% of 762 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_risk_gateway, test_w39b_razorpay, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z237" s="2" t="inlineStr"/>
@@ -31618,7 +31711,7 @@
       </c>
       <c r="Y241" s="2" t="inlineStr">
         <is>
-          <t>48% of 231 lines in 2 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_depth20, test_w39_event_calendar, test_w39_global_sync, test_w39_intraday, test_w39_market_pulse, test_w39_perf_budget (+8 more)</t>
+          <t>48% of 231 lines in 2 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_depth20, test_w39_event_calendar, test_w39_global_sync, test_w39_intraday, test_w39_market_pulse, test_w39_perf_budget (+10 more)</t>
         </is>
       </c>
       <c r="Z241" s="2" t="inlineStr"/>
@@ -32342,7 +32435,7 @@
       </c>
       <c r="Y247" s="2" t="inlineStr">
         <is>
-          <t>33% of 1430 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+1 more)</t>
+          <t>33% of 1437 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_qa_suite, test_w39_ui_smoke (+2 more)</t>
         </is>
       </c>
       <c r="Z247" s="2" t="inlineStr"/>
@@ -32582,7 +32675,7 @@
       </c>
       <c r="Y249" s="2" t="inlineStr">
         <is>
-          <t>test_a_deprecated_v1_resource_warns_then_answers_410_after_sunset | 59% of 657 lines in 3 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+27 more)</t>
+          <t>test_a_deprecated_v1_resource_warns_then_answers_410_after_sunset | 59% of 657 lines in 3 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+34 more)</t>
         </is>
       </c>
       <c r="Z249" s="2" t="inlineStr"/>
@@ -32997,7 +33090,7 @@
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="M253" s="2" t="inlineStr">
@@ -33012,17 +33105,17 @@
       </c>
       <c r="O253" s="2" t="inlineStr">
         <is>
-          <t>Owner: options.enabled; QA; strategies do not emit option intents yet</t>
+          <t>Owner: options.enabled; QA. W40: option-overlay strategies (strategy_engine/option_overlay.py) emit multi-leg OPTION intents -- covered call, protective put, spreads, iron condor and more, strikes by delta or % OTM, monthly expiry -- sized by the risk engine (max loss, margin approximation, naked short calls refused unless allowed), filled all-or-nothing in the paper options book, marked daily, exited by rule, settled at expiry; PAPER only, LIVE refused; a replay on stored daily option prices</t>
         </is>
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>execution/options_paper.py; execution/assets.py</t>
+          <t>execution/options_paper.py; execution/option_intents.py; strategy_engine/option_overlay.py</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
         <is>
-          <t>BRD-001</t>
+          <t>tests/test_w40_option_intents.py; docs/W40_OPTION_INTENTS_HANDOFF.md</t>
         </is>
       </c>
       <c r="R253" s="2" t="inlineStr"/>
@@ -33035,7 +33128,7 @@
       <c r="U253" s="2" t="inlineStr"/>
       <c r="V253" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="W253" s="2" t="inlineStr">
@@ -33050,7 +33143,7 @@
       </c>
       <c r="Y253" s="2" t="inlineStr">
         <is>
-          <t>75% of 167 lines in 2 key file(s) run by: test_w37_brokers_multi_asset</t>
+          <t>tests/test_w40_option_intents.py; docs/W40_OPTION_INTENTS_HANDOFF.md | 84% of 1203 lines in 3 key file(s) run by: test_signal_pipeline, test_w37_brokers_multi_asset, test_w39_exec_data_tests, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z253" s="2" t="inlineStr"/>
@@ -33874,7 +33967,7 @@
       </c>
       <c r="Y260" s="2" t="inlineStr">
         <is>
-          <t>71% of 254 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+27 more)</t>
+          <t>71% of 254 lines in 1 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+34 more)</t>
         </is>
       </c>
       <c r="Z260" s="2" t="inlineStr"/>
@@ -33990,7 +34083,7 @@
       </c>
       <c r="Y261" s="2" t="inlineStr">
         <is>
-          <t>53% of 232 lines in 2 key file(s) run by: test_auto_recover, test_regressions, test_risk_controls, test_w38_platform_compliance, test_w39_api_contract, test_w39_backtest, test_w39_delivery, test_w39_depth20 (+31 more)</t>
+          <t>53% of 232 lines in 2 key file(s) run by: test_auto_recover, test_regressions, test_risk_controls, test_w38_platform_compliance, test_w39_api_contract, test_w39_backtest, test_w39_delivery, test_w39_depth20 (+37 more)</t>
         </is>
       </c>
       <c r="Z261" s="2" t="inlineStr"/>
@@ -34106,7 +34199,7 @@
       </c>
       <c r="Y262" s="2" t="inlineStr">
         <is>
-          <t>36% of 1350 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget (+3 more)</t>
+          <t>35% of 1357 lines in 2 key file(s) run by: test_auto_recover, test_fii_dii_and_delivery_factor, test_job_monitoring, test_signal_pipeline, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget (+4 more)</t>
         </is>
       </c>
       <c r="Z262" s="2" t="inlineStr"/>
@@ -34222,7 +34315,7 @@
       </c>
       <c r="Y263" s="2" t="inlineStr">
         <is>
-          <t>32% of 1132 lines in 4 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
+          <t>31% of 1132 lines in 4 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_risk_gateway (+2 more)</t>
         </is>
       </c>
       <c r="Z263" s="2" t="inlineStr"/>
@@ -34454,7 +34547,7 @@
       </c>
       <c r="Y265" s="2" t="inlineStr">
         <is>
-          <t>50% of 880 lines in 3 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke</t>
+          <t>51% of 896 lines in 3 key file(s) run by: test_auto_recover, test_w38_platform_compliance, test_w39_exec_data_tests, test_w39_ops_tests, test_w39_perf_budget, test_w39_qa_suite, test_w39_risk_gateway, test_w39_ui_smoke (+1 more)</t>
         </is>
       </c>
       <c r="Z265" s="2" t="inlineStr"/>
@@ -35378,7 +35471,7 @@
       </c>
       <c r="Y273" s="2" t="inlineStr">
         <is>
-          <t>89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_w39b_mf_analytics, test_wealth_api_security, test_wealth_math, test_wealth_performance (+1 more)</t>
+          <t>90% of 1207 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_mcp, test_w39_notify_transactions, test_w39_performance_detail, test_w39b_mf_analytics, test_w40_total_return, test_wealth_api_security (+3 more)</t>
         </is>
       </c>
       <c r="Z273" s="2" t="inlineStr"/>
@@ -35726,7 +35819,7 @@
       </c>
       <c r="Y276" s="2" t="inlineStr">
         <is>
-          <t>75% of 204 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+27 more)</t>
+          <t>75% of 204 lines in 2 key file(s) run by: test_auto_recover, test_risk_controls, test_w39_api_contract, test_w39_backtest, test_w39_depth20, test_w39_event_calendar, test_w39_exec_data_tests, test_w39_global_sync (+34 more)</t>
         </is>
       </c>
       <c r="Z276" s="2" t="inlineStr"/>
@@ -36074,7 +36167,7 @@
       </c>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 77% of 317 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance (+1 more)</t>
+          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 77% of 317 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_w40_total_return, test_wealth_api_security (+2 more)</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr"/>
@@ -36190,7 +36283,7 @@
       </c>
       <c r="Y280" s="2" t="inlineStr">
         <is>
-          <t>test_model_return_is_reproducible_and_matches_a_hand_calculation; test_model_and_executable_are_reported_separately | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_model_return_is_reproducible_and_matches_a_hand_calculation; test_model_and_executable_are_reported_separately | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z280" s="2" t="inlineStr"/>
@@ -36306,7 +36399,7 @@
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap; test_impact_slippage_uses_the_square_root_estimate_known_at_the_signal | 83% of 331 lines in 2 key file(s) run by: test_w39_backtest_partial, test_w39_contract_note_fees, test_w39_performance_detail, test_w39_untested_modules, test_wealth_performance</t>
+          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap; test_impact_slippage_uses_the_square_root_estimate_known_at_the_signal | 83% of 331 lines in 2 key file(s) run by: test_w39_backtest_partial, test_w39_contract_note_fees, test_w39_performance_detail, test_w39_untested_modules, test_w40_futures_backtest, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr"/>
@@ -36422,7 +36515,7 @@
       </c>
       <c r="Y282" s="2" t="inlineStr">
         <is>
-          <t>test_period_scope_is_separate_from_lifetime; test_xirr_and_pme_match_hand_computed_flows; test_average_cost_realized_pnl_and_fees | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_period_scope_is_separate_from_lifetime; test_xirr_and_pme_match_hand_computed_flows; test_average_cost_realized_pnl_and_fees | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z282" s="2" t="inlineStr"/>
@@ -36491,22 +36584,22 @@
       <c r="M283" s="2" t="inlineStr"/>
       <c r="N283" s="2" t="inlineStr">
         <is>
-          <t>any prices_daily symbol (NIFTY50, NIFTYBANK, midcap, smallcap, sector indices); price return over the same sessions + PME of the investor's flows; W39: days invested shown and exported</t>
+          <t>any prices_daily symbol (NIFTY50, NIFTYBANK, midcap, smallcap, sector indices); price return over the same sessions + PME of the investor's flows; W39: days invested shown and exported. W40: benchmark "nifty50tr" -- the Nifty 50 with dividends reinvested (data/total_return.py: NSE's TRI method, the price index exact, its dividend points estimated from the top 50 stored stocks by cap, picked monthly and weighted daily; nightly 21:10; GET /api/data/total-return), part of the report's audited inputs</t>
         </is>
       </c>
       <c r="O283" s="2" t="inlineStr">
         <is>
-          <t>Total-return index (dividends) not available from the data source</t>
+          <t>Independent QA; the dividend part is an estimate (no free-float or constituent data) -- compare once with NSE's published TRI</t>
         </is>
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>wealth/perf/data.py; wealth/perf/report.py</t>
+          <t>wealth/perf/data.py; wealth/perf/report.py; data/total_return.py</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
         <is>
-          <t>test_benchmark_return_is_the_price_return_over_the_sessions</t>
+          <t>test_benchmark_return_is_the_price_return_over_the_sessions; tests/test_w40_total_return.py</t>
         </is>
       </c>
       <c r="R283" s="2" t="inlineStr">
@@ -36538,7 +36631,7 @@
       </c>
       <c r="Y283" s="2" t="inlineStr">
         <is>
-          <t>test_benchmark_return_is_the_price_return_over_the_sessions | 93% of 299 lines in 2 key file(s) run by: test_w39_performance_detail, test_w39b_mf_analytics, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_benchmark_return_is_the_price_return_over_the_sessions; tests/test_w40_total_return.py | 91% of 502 lines in 3 key file(s) run by: test_w39_mcp, test_w39_performance_detail, test_w39b_mf_analytics, test_w40_total_return, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z283" s="2" t="inlineStr"/>
@@ -36654,7 +36747,7 @@
       </c>
       <c r="Y284" s="2" t="inlineStr">
         <is>
-          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades; tests/test_w39_contract_note_fees.py | 89% of 587 lines in 2 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades; tests/test_w39_contract_note_fees.py | 89% of 587 lines in 2 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z284" s="2" t="inlineStr"/>
@@ -36770,7 +36863,7 @@
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win; test_position_attribution_identity | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win; test_position_attribution_identity | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr"/>
@@ -36886,7 +36979,7 @@
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 96% of 216 lines in 2 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo, test_w39b_mf_analytics, test_wealth_math (+1 more)</t>
+          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 96% of 217 lines in 2 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_mcp, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_bayes_optimize, test_w39b_cpcv_dominance (+7 more)</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr"/>
@@ -37002,7 +37095,7 @@
       </c>
       <c r="Y287" s="2" t="inlineStr">
         <is>
-          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win | 92% of 461 lines in 2 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win | 92% of 461 lines in 2 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z287" s="2" t="inlineStr"/>
@@ -37118,7 +37211,7 @@
       </c>
       <c r="Y288" s="2" t="inlineStr">
         <is>
-          <t>test_risk_contribution_reconciles_and_groups_sum_to_the_total; test_contributions_reconcile_to_the_total | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_risk_contribution_reconciles_and_groups_sum_to_the_total; test_contributions_reconcile_to_the_total | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z288" s="2" t="inlineStr"/>
@@ -37350,7 +37443,7 @@
       </c>
       <c r="Y290" s="2" t="inlineStr">
         <is>
-          <t>test_verify_reproduces_and_detects_changed_inputs | 95% of 231 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_verify_reproduces_and_detects_changed_inputs | 96% of 231 lines in 1 key file(s) run by: test_w39_performance_detail, test_w40_total_return, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z290" s="2" t="inlineStr"/>
@@ -37466,7 +37559,7 @@
       </c>
       <c r="Y291" s="2" t="inlineStr">
         <is>
-          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio; test_printable_html_has_the_csv_sections_and_numbers_and_escapes_text | 87% of 594 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_performance_detail, test_w39_ui_smoke, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio; test_printable_html_has_the_csv_sections_and_numbers_and_escapes_text | 87% of 594 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_performance_detail, test_w39_ui_smoke, test_w40_total_return, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z291" s="2" t="inlineStr"/>
@@ -37582,7 +37675,7 @@
       </c>
       <c r="Y292" s="2" t="inlineStr">
         <is>
-          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_w39b_mf_analytics, test_wealth_api_security, test_wealth_math, test_wealth_performance (+1 more)</t>
+          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 90% of 1207 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_mcp, test_w39_notify_transactions, test_w39_performance_detail, test_w39b_mf_analytics, test_w40_total_return, test_wealth_api_security (+3 more)</t>
         </is>
       </c>
       <c r="Z292" s="2" t="inlineStr"/>
@@ -37814,7 +37907,7 @@
       </c>
       <c r="Y294" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_history.py; tests/test_w39b_merge.py | 51% of 1001 lines in 3 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests (+3 more)</t>
+          <t>tests/test_w39_history.py; tests/test_w39b_merge.py | 50% of 1001 lines in 3 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests (+3 more)</t>
         </is>
       </c>
       <c r="Z294" s="2" t="inlineStr"/>
@@ -37883,7 +37976,7 @@
       <c r="M295" s="2" t="inlineStr"/>
       <c r="N295" s="2" t="inlineStr">
         <is>
-          <t>W26 stock panel + W39: 3Y / 5Y / All, daily / weekly / monthly bars, SMA 20/50/200, EMA 21, Bollinger, log scale, multi-year returns; checked in headless Chromium</t>
+          <t>W26 stock panel + W39: 3Y / 5Y / All, daily / weekly / monthly bars, SMA 20/50/200, EMA 21, Bollinger, log scale, multi-year returns; checked in headless Chromium. W39b: signal / pattern marks. W40: RSI 14 and MACD 12-26-9 panels (the server's definitions), an intraday chart (1D / 5D on 15-minute bars, session VWAP, previous close, intraday scan marks; GET /api/stock/{symbol}/intraday) and the on-demand 75-minute rating</t>
         </is>
       </c>
       <c r="O295" s="2" t="inlineStr">
@@ -37898,7 +37991,7 @@
       </c>
       <c r="Q295" s="2" t="inlineStr">
         <is>
-          <t>test_stock_history_reports_multi_year_returns</t>
+          <t>test_stock_history_reports_multi_year_returns; tests/test_w40_stock_chart.py</t>
         </is>
       </c>
       <c r="R295" s="2" t="inlineStr">
@@ -37930,7 +38023,7 @@
       </c>
       <c r="Y295" s="2" t="inlineStr">
         <is>
-          <t>test_stock_history_reports_multi_year_returns | 84% of 113 lines in 1 key file(s) run by: test_auto_recover, test_w39_owner_notes, test_w39_perf_budget, test_w39b_patterns_more</t>
+          <t>test_stock_history_reports_multi_year_returns; tests/test_w40_stock_chart.py | 88% of 248 lines in 1 key file(s) run by: test_auto_recover, test_w39_mcp, test_w39_owner_notes, test_w39_perf_budget, test_w39b_patterns_more, test_w39b_tf75_signals, test_w40_stock_chart</t>
         </is>
       </c>
       <c r="Z295" s="2" t="inlineStr"/>
@@ -38046,7 +38139,7 @@
       </c>
       <c r="Y296" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_risk_gateway.py | 51% of 1617 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+10 more)</t>
+          <t>tests/test_w39_risk_gateway.py | 51% of 1622 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+15 more)</t>
         </is>
       </c>
       <c r="Z296" s="2" t="inlineStr"/>
@@ -38162,7 +38255,7 @@
       </c>
       <c r="Y297" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_quant_portfolio.py | 61% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
+          <t>tests/test_w39_quant_portfolio.py | 68% of 269 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z297" s="2" t="inlineStr"/>
@@ -38510,7 +38603,7 @@
       </c>
       <c r="Y300" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_ml_regime_lineage_surface.py | 86% of 140 lines in 1 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_ml_regime_lineage_surface, test_w39_options</t>
+          <t>tests/test_w39_ml_regime_lineage_surface.py | 86% of 140 lines in 1 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_ml_regime_lineage_surface, test_w39_options, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z300" s="2" t="inlineStr"/>
@@ -38626,7 +38719,7 @@
       </c>
       <c r="Y301" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_ml_regime_lineage_surface.py | 87% of 341 lines in 2 key file(s) run by: test_w39_ml_regime_lineage_surface</t>
+          <t>tests/test_w39_ml_regime_lineage_surface.py | 87% of 341 lines in 2 key file(s) run by: test_w39_ml_regime_lineage_surface, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z301" s="2" t="inlineStr"/>
@@ -38742,7 +38835,7 @@
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_ml_regime_lineage_surface.py | 73% of 148 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite</t>
+          <t>tests/test_w39_ml_regime_lineage_surface.py | 88% of 154 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite, test_w40_meta_label</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr"/>
@@ -38858,7 +38951,7 @@
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_backtest.py | 82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39b_cpcv_pbo</t>
+          <t>tests/test_w39_backtest.py | 83% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo, test_w39b_event_driven_skips, test_w40_futures_backtest</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr"/>
@@ -39898,7 +39991,7 @@
       </c>
       <c r="Y312" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_options.py | 88% of 209 lines in 1 key file(s) run by: test_w39_options</t>
+          <t>tests/test_w39_options.py | 88% of 209 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_options, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z312" s="2" t="inlineStr"/>
@@ -40014,7 +40107,7 @@
       </c>
       <c r="Y313" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_technicals.py | 88% of 820 lines in 2 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+9 more)</t>
+          <t>tests/test_w39_technicals.py | 89% of 885 lines in 2 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+12 more)</t>
         </is>
       </c>
       <c r="Z313" s="2" t="inlineStr"/>
@@ -40246,7 +40339,7 @@
       </c>
       <c r="Y315" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_regime_gate.py | 83% of 248 lines in 1 key file(s) run by: test_w39_delivery, test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_technicals (+4 more)</t>
+          <t>tests/test_w39_regime_gate.py | 83% of 248 lines in 1 key file(s) run by: test_w39_delivery, test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_technicals (+6 more)</t>
         </is>
       </c>
       <c r="Z315" s="2" t="inlineStr"/>
@@ -40362,7 +40455,7 @@
       </c>
       <c r="Y316" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_track_record.py | 84% of 522 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+6 more)</t>
+          <t>tests/test_w39_track_record.py | 85% of 587 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+9 more)</t>
         </is>
       </c>
       <c r="Z316" s="2" t="inlineStr"/>
@@ -40478,7 +40571,7 @@
       </c>
       <c r="Y317" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_weekly.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
+          <t>tests/test_w39_weekly.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+7 more)</t>
         </is>
       </c>
       <c r="Z317" s="2" t="inlineStr"/>
@@ -40594,7 +40687,7 @@
       </c>
       <c r="Y318" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_patterns.py; tests/test_w39b_patterns_more.py | 93% of 491 lines in 2 key file(s) run by: test_auto_recover, test_w39_delivery, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
+          <t>tests/test_w39_patterns.py; tests/test_w39b_patterns_more.py | 93% of 626 lines in 2 key file(s) run by: test_auto_recover, test_w39_delivery, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+7 more)</t>
         </is>
       </c>
       <c r="Z318" s="2" t="inlineStr"/>
@@ -40710,7 +40803,7 @@
       </c>
       <c r="Y319" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_rs_line.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
+          <t>tests/test_w39_rs_line.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+7 more)</t>
         </is>
       </c>
       <c r="Z319" s="2" t="inlineStr"/>
@@ -40826,7 +40919,7 @@
       </c>
       <c r="Y320" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_delivery.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
+          <t>tests/test_w39_delivery.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+7 more)</t>
         </is>
       </c>
       <c r="Z320" s="2" t="inlineStr"/>
@@ -41174,7 +41267,7 @@
       </c>
       <c r="Y323" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_intraday.py | 88% of 225 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly, test_w39b_tf75</t>
+          <t>tests/test_w39_intraday.py | 88% of 225 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly, test_w39b_tf75 (+2 more)</t>
         </is>
       </c>
       <c r="Z323" s="2" t="inlineStr"/>
@@ -41591,7 +41684,7 @@
       <c r="M327" s="2" t="inlineStr"/>
       <c r="N327" s="2" t="inlineStr">
         <is>
-          <t>tools/atip_mcp.py</t>
+          <t>tools/atip_mcp.py; W40: 20 tools -- adds dvm, earnings_surprise, mf_search / mf_analytics / mf_sip / mf_compare, backtest_validation (stored CPCV / PBO) and chart_marks, each checked under query_only</t>
         </is>
       </c>
       <c r="O327" s="2" t="inlineStr">
@@ -41638,7 +41731,7 @@
       </c>
       <c r="Y327" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_mcp.py | 83% of 184 lines in 1 key file(s) run by: test_w39_mcp</t>
+          <t>tests/test_w39_mcp.py | 91% of 331 lines in 1 key file(s) run by: test_w39_mcp</t>
         </is>
       </c>
       <c r="Z327" s="2" t="inlineStr"/>
@@ -41828,7 +41921,7 @@
       </c>
       <c r="O329" s="2" t="inlineStr">
         <is>
-          <t>Independent QA; no live intraday refresh (once a day, as of the close); /signals has no 75-minute column</t>
+          <t>Independent QA. W40: a 75m column on /signals and GET /api/stock/{symbol}/rating-75 (on demand from the stored 15-minute bars, completed bars only); the /signals column is still the 20:30 snapshot</t>
         </is>
       </c>
       <c r="P329" s="2" t="inlineStr">
@@ -41838,7 +41931,7 @@
       </c>
       <c r="Q329" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_tf75.py</t>
+          <t>tests/test_w39b_tf75.py; tests/test_w39b_tf75_signals.py</t>
         </is>
       </c>
       <c r="R329" s="2" t="inlineStr">
@@ -41870,7 +41963,7 @@
       </c>
       <c r="Y329" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_tf75.py | 88% of 1266 lines in 3 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+10 more)</t>
+          <t>tests/test_w39b_tf75.py; tests/test_w39b_tf75_signals.py | 89% of 1331 lines in 3 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+13 more)</t>
         </is>
       </c>
       <c r="Z329" s="2" t="inlineStr"/>
@@ -41986,7 +42079,7 @@
       </c>
       <c r="Y330" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_dvm.py | 86% of 1041 lines in 3 key file(s) run by: test_auto_recover, test_w39_depth20, test_w39_event_calendar, test_w39_global_sync, test_w39_intraday, test_w39_market_pulse, test_w39_mcp, test_w39_options (+12 more)</t>
+          <t>tests/test_w39b_dvm.py | 86% of 1044 lines in 3 key file(s) run by: test_auto_recover, test_w39_depth20, test_w39_event_calendar, test_w39_global_sync, test_w39_intraday, test_w39_market_pulse, test_w39_mcp, test_w39_options (+14 more)</t>
         </is>
       </c>
       <c r="Z330" s="2" t="inlineStr"/>
@@ -42102,7 +42195,7 @@
       </c>
       <c r="Y331" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_earnings_surprise.py | 85% of 905 lines in 2 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+6 more)</t>
+          <t>tests/test_w39b_earnings_surprise.py | 86% of 970 lines in 2 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+9 more)</t>
         </is>
       </c>
       <c r="Z331" s="2" t="inlineStr">
@@ -42175,12 +42268,12 @@
       <c r="M332" s="2" t="inlineStr"/>
       <c r="N332" s="2" t="inlineStr">
         <is>
-          <t>data/mf_analytics.py: point-to-point and CAGR returns, 1Y / 3Y rolling returns with hurdle stats, volatility / Sharpe / Sortino, drawdown with dates, beta / alpha / tracking error vs a price index, SIP and lump-sum XIRR, category rank among stored schemes, side-by-side compare; 3 read-only GET routes; scheme detail card on /data-platform</t>
+          <t>data/mf_analytics.py: point-to-point and CAGR returns, 1Y / 3Y rolling returns with hurdle stats, volatility / Sharpe / Sortino, drawdown with dates, beta / alpha / tracking error vs a price index, SIP and lump-sum XIRR, category rank among stored schemes, side-by-side compare; 3 read-only GET routes; scheme detail card on /data-platform. W40: step-up SIP, stamp duty (0.005 %) and units rounded down to 3 decimals by default, optional flat exit load per instalment; volatility annualised by the NAVs actually observed a year (not a fixed 252)</t>
         </is>
       </c>
       <c r="O332" s="2" t="inlineStr">
         <is>
-          <t>Independent QA. Holding MFs in the wealth ledger stays out of scope (owner Scope Exclusions); benchmark is a price index, not total return; peers limited to stored schemes</t>
+          <t>Independent QA. Holding MFs in the wealth ledger stays out of scope (owner Scope Exclusions); benchmark is a price index (the W40 Nifty 50 TR is not wired here yet); peers limited to stored schemes; tiered exit loads not modelled</t>
         </is>
       </c>
       <c r="P332" s="2" t="inlineStr">
@@ -42222,13 +42315,245 @@
       </c>
       <c r="Y332" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_mf_analytics.py | 86% of 626 lines in 3 key file(s) run by: test_auto_recover, test_w39_ml_regime_lineage_surface, test_w39_perf_budget, test_w39_ui_smoke, test_w39b_mf_analytics</t>
+          <t>tests/test_w39b_mf_analytics.py | 87% of 688 lines in 3 key file(s) run by: test_auto_recover, test_w39_mcp, test_w39_ml_regime_lineage_surface, test_w39_perf_budget, test_w39_ui_smoke, test_w39b_mf_analytics</t>
         </is>
       </c>
       <c r="Z332" s="2" t="inlineStr"/>
     </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>W40-RISKMODEL</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>Risk &amp; Portfolio</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>Fundamental factor risk model (Barra-style)</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>Factor exposures, factor returns, covariance, specific risk and portfolio risk decomposition</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>W40 (PR #9): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4 items 5 and 9; tracker next actions</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J333" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K333" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr"/>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>quant/risk_model.py: 8 styles (size, beta, momentum, residual volatility, book-to-price, earnings yield, ROE, liquidity) point in time, winsorised and cap-standardised, NSE industries (small ones pooled); daily sqrt(cap)-weighted regression with the industry constraint and robust t statistics; EWMA / Newey-West factor covariance; shrunk EWMA specific risk; decomposition of the PAPER / LIVE book (factor vs specific, per factor, marginal per stock, beta, active risk vs a cap-weighted Nifty 50 proxy); bias statistic on standard portfolios; nightly 21:45, incremental; /trading and /quant cards</t>
+        </is>
+      </c>
+      <c r="O333" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA on the real database; needs filed share counts for 30+ stocks; universe and industries are today's (survivorship); no free-float data</t>
+        </is>
+      </c>
+      <c r="P333" s="2" t="inlineStr">
+        <is>
+          <t>quant/risk_model.py; portfolio/risk.py; dashboard/risk_model_routes.py</t>
+        </is>
+      </c>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w40_risk_model.py</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S333" s="2" t="inlineStr"/>
+      <c r="T333" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U333" s="2" t="inlineStr"/>
+      <c r="V333" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W333" s="2" t="inlineStr">
+        <is>
+          <t>W40 developed 2026-10-09 on branch claude/wizardly-curie-fbjeoa (PR #9); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X333" s="2" t="inlineStr">
+        <is>
+          <t>W40 (PR #9)</t>
+        </is>
+      </c>
+      <c r="Y333" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w40_risk_model.py | 76% of 1466 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_w40_risk_model, test_w40_total_return</t>
+        </is>
+      </c>
+      <c r="Z333" s="2" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>W40-META</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Meta-labelling of the technical signals (AFML ch. 3-4, 7, 10)</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>A second model deciding which primary signals to take, with bet sizes</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>W40 (PR #9): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4 items 5 and 9; tracker next actions</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J334" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K334" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L334" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="inlineStr"/>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>ml/meta_label.py: triple-barrier labels from the signal engine's own outcome rule; 37 features known at the signal's close; sample weights by average uniqueness; purged k-fold with embargo; GBM / logistic / RF; out-of-fold precision / recall / AUC and the kept signals' expectancy vs all; AFML bet sizing (reported only); ADOPTABLE only with 200+ signals and t &gt;= 2, and the registry refuses activating anything else; Saturday retrain and 20:45 scoring, both off unless meta_label.enabled; /signals column when adopted</t>
+        </is>
+      </c>
+      <c r="O334" s="2" t="inlineStr">
+        <is>
+          <t>Owner: switch on after a few hundred closed signals exist and a version is ADOPTABLE; independent QA</t>
+        </is>
+      </c>
+      <c r="P334" s="2" t="inlineStr">
+        <is>
+          <t>ml/meta_label.py; ml/validation.py; dashboard/w40_routes.py</t>
+        </is>
+      </c>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w40_meta_label.py</t>
+        </is>
+      </c>
+      <c r="R334" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S334" s="2" t="inlineStr"/>
+      <c r="T334" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U334" s="2" t="inlineStr"/>
+      <c r="V334" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W334" s="2" t="inlineStr">
+        <is>
+          <t>W40 developed 2026-10-09 on branch claude/wizardly-curie-fbjeoa (PR #9); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X334" s="2" t="inlineStr">
+        <is>
+          <t>W40 (PR #9)</t>
+        </is>
+      </c>
+      <c r="Y334" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w40_meta_label.py | 90% of 861 lines in 3 key file(s) run by: test_auto_recover, test_w39_qa_suite, test_w39_regime_gate, test_w39_technicals, test_w40_meta_label</t>
+        </is>
+      </c>
+      <c r="Z334" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z332"/>
+  <autoFilter ref="A1:Z334"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42239,7 +42564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z55"/>
+  <dimension ref="A1:Z57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42513,7 +42838,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 77% of 317 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance (+1 more)</t>
+          <t>test_paper_partial_fills_reach_the_ledger; test_entry_order_is_portable_and_numbered; test_migration_0006_numbers_old_rows_and_the_ledger_stays_append_only; test_cash_rows_and_fee_breakdown_are_validated; test_voided_transactions_are_ignored_but_kept | 77% of 317 lines in 3 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_ops_tests, test_w39_perf_budget, test_w39_performance_detail, test_w40_total_return, test_wealth_api_security (+2 more)</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -42629,7 +42954,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>test_model_return_is_reproducible_and_matches_a_hand_calculation; test_model_and_executable_are_reported_separately | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_model_return_is_reproducible_and_matches_a_hand_calculation; test_model_and_executable_are_reported_separately | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr"/>
@@ -42745,7 +43070,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap; test_impact_slippage_uses_the_square_root_estimate_known_at_the_signal | 83% of 331 lines in 2 key file(s) run by: test_w39_backtest_partial, test_w39_contract_note_fees, test_w39_performance_detail, test_w39_untested_modules, test_wealth_performance</t>
+          <t>test_executable_applies_slippage_costs_and_the_liquidity_cap; test_impact_slippage_uses_the_square_root_estimate_known_at_the_signal | 83% of 331 lines in 2 key file(s) run by: test_w39_backtest_partial, test_w39_contract_note_fees, test_w39_performance_detail, test_w39_untested_modules, test_w40_futures_backtest, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
@@ -42861,7 +43186,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>test_period_scope_is_separate_from_lifetime; test_xirr_and_pme_match_hand_computed_flows; test_average_cost_realized_pnl_and_fees | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_period_scope_is_separate_from_lifetime; test_xirr_and_pme_match_hand_computed_flows; test_average_cost_realized_pnl_and_fees | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr"/>
@@ -42930,22 +43255,22 @@
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>any prices_daily symbol (NIFTY50, NIFTYBANK, midcap, smallcap, sector indices); price return over the same sessions + PME of the investor's flows; W39: days invested shown and exported</t>
+          <t>any prices_daily symbol (NIFTY50, NIFTYBANK, midcap, smallcap, sector indices); price return over the same sessions + PME of the investor's flows; W39: days invested shown and exported. W40: benchmark "nifty50tr" -- the Nifty 50 with dividends reinvested (data/total_return.py: NSE's TRI method, the price index exact, its dividend points estimated from the top 50 stored stocks by cap, picked monthly and weighted daily; nightly 21:10; GET /api/data/total-return), part of the report's audited inputs</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Total-return index (dividends) not available from the data source</t>
+          <t>Independent QA; the dividend part is an estimate (no free-float or constituent data) -- compare once with NSE's published TRI</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>wealth/perf/data.py; wealth/perf/report.py</t>
+          <t>wealth/perf/data.py; wealth/perf/report.py; data/total_return.py</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>test_benchmark_return_is_the_price_return_over_the_sessions</t>
+          <t>test_benchmark_return_is_the_price_return_over_the_sessions; tests/test_w40_total_return.py</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -42977,7 +43302,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>test_benchmark_return_is_the_price_return_over_the_sessions | 93% of 299 lines in 2 key file(s) run by: test_w39_performance_detail, test_w39b_mf_analytics, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_benchmark_return_is_the_price_return_over_the_sessions; tests/test_w40_total_return.py | 91% of 502 lines in 3 key file(s) run by: test_w39_mcp, test_w39_performance_detail, test_w39b_mf_analytics, test_w40_total_return, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr"/>
@@ -43093,7 +43418,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades; tests/test_w39_contract_note_fees.py | 89% of 587 lines in 2 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_costs_reconcile_with_dividend_tax_fee_rows_and_a_capped_sell; test_statutory_estimate_itemises_paper_brokerage_only_trades; tests/test_w39_contract_note_fees.py | 89% of 587 lines in 2 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr"/>
@@ -43209,7 +43534,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win; test_position_attribution_identity | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win; test_position_attribution_identity | 88% of 230 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr"/>
@@ -43325,7 +43650,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 96% of 216 lines in 2 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_cpcv_pbo, test_w39b_mf_analytics, test_wealth_math (+1 more)</t>
+          <t>test_risk_metrics_match_independent_formulas; test_cagr_annualises_a_full_year; test_xirr_one_year_ten_percent; test_trade_stats | 96% of 217 lines in 2 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39_mcp, test_w39_performance_detail, test_w39_qa_suite, test_w39_untested_modules, test_w39b_bayes_optimize, test_w39b_cpcv_dominance (+7 more)</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr"/>
@@ -43441,7 +43766,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win | 92% of 461 lines in 2 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_sizing_effect_completes_the_decomposition_and_exact_links_win | 92% of 461 lines in 2 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr"/>
@@ -43557,7 +43882,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>test_risk_contribution_reconciles_and_groups_sum_to_the_total; test_contributions_reconcile_to_the_total | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_wealth_performance</t>
+          <t>test_risk_contribution_reconciles_and_groups_sum_to_the_total; test_contributions_reconcile_to_the_total | 94% of 371 lines in 1 key file(s) run by: test_w39_contract_note_fees, test_w39_performance_detail, test_w40_total_return, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr"/>
@@ -43789,7 +44114,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>test_verify_reproduces_and_detects_changed_inputs | 95% of 231 lines in 1 key file(s) run by: test_w39_performance_detail, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_verify_reproduces_and_detects_changed_inputs | 96% of 231 lines in 1 key file(s) run by: test_w39_performance_detail, test_w40_total_return, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr"/>
@@ -43905,7 +44230,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio; test_printable_html_has_the_csv_sections_and_numbers_and_escapes_text | 87% of 594 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_performance_detail, test_w39_ui_smoke, test_wealth_api_security, test_wealth_performance</t>
+          <t>test_export_carries_every_section_with_the_reports_numbers; test_strategy_filter_limits_the_actual_portfolio; test_printable_html_has_the_csv_sections_and_numbers_and_escapes_text | 87% of 594 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_performance_detail, test_w39_ui_smoke, test_w40_total_return, test_wealth_api_security, test_wealth_performance</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr"/>
@@ -44021,7 +44346,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 89% of 1179 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_notify_transactions, test_w39_performance_detail, test_w39b_mf_analytics, test_wealth_api_security, test_wealth_math, test_wealth_performance (+1 more)</t>
+          <t>test_a_trade_on_a_market_holiday_counts_on_the_next_session; test_missing_bars_are_reported_not_hidden; test_a_bonus_issue_keeps_value_and_cost; test_an_opening_position_is_measured_from_that_days_close; test_split_between_buy_and_today_moves_neither_value_nor_return | 90% of 1207 lines in 6 key file(s) run by: test_w37_brokers_multi_asset, test_w39_contract_note_fees, test_w39_mcp, test_w39_notify_transactions, test_w39_performance_detail, test_w39b_mf_analytics, test_w40_total_return, test_wealth_api_security (+3 more)</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr"/>
@@ -44253,7 +44578,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_history.py; tests/test_w39b_merge.py | 51% of 1001 lines in 3 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests (+3 more)</t>
+          <t>tests/test_w39_history.py; tests/test_w39b_merge.py | 50% of 1001 lines in 3 key file(s) run by: test_corporate_actions, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w39_history, test_w39_notify_transactions, test_w39_ops_tests (+3 more)</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr"/>
@@ -44322,7 +44647,7 @@
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>W26 stock panel + W39: 3Y / 5Y / All, daily / weekly / monthly bars, SMA 20/50/200, EMA 21, Bollinger, log scale, multi-year returns; checked in headless Chromium</t>
+          <t>W26 stock panel + W39: 3Y / 5Y / All, daily / weekly / monthly bars, SMA 20/50/200, EMA 21, Bollinger, log scale, multi-year returns; checked in headless Chromium. W39b: signal / pattern marks. W40: RSI 14 and MACD 12-26-9 panels (the server's definitions), an intraday chart (1D / 5D on 15-minute bars, session VWAP, previous close, intraday scan marks; GET /api/stock/{symbol}/intraday) and the on-demand 75-minute rating</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -44337,7 +44662,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>test_stock_history_reports_multi_year_returns</t>
+          <t>test_stock_history_reports_multi_year_returns; tests/test_w40_stock_chart.py</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -44369,7 +44694,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>test_stock_history_reports_multi_year_returns | 84% of 113 lines in 1 key file(s) run by: test_auto_recover, test_w39_owner_notes, test_w39_perf_budget, test_w39b_patterns_more</t>
+          <t>test_stock_history_reports_multi_year_returns; tests/test_w40_stock_chart.py | 88% of 248 lines in 1 key file(s) run by: test_auto_recover, test_w39_mcp, test_w39_owner_notes, test_w39_perf_budget, test_w39b_patterns_more, test_w39b_tf75_signals, test_w40_stock_chart</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr"/>
@@ -44485,7 +44810,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_risk_gateway.py | 51% of 1617 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+10 more)</t>
+          <t>tests/test_w39_risk_gateway.py | 51% of 1622 lines in 3 key file(s) run by: test_auto_recover, test_corporate_actions, test_job_monitoring, test_regressions, test_risk_controls, test_signal_pipeline, test_strategy_live, test_w38_platform_compliance (+15 more)</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr"/>
@@ -44601,7 +44926,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_quant_portfolio.py | 61% of 266 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio</t>
+          <t>tests/test_w39_quant_portfolio.py | 68% of 269 lines in 1 key file(s) run by: test_auto_recover, test_w36_ml_strategy_tooling, test_w39_api_contract, test_w39_quant_portfolio, test_w40_risk_model</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr"/>
@@ -44949,7 +45274,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_ml_regime_lineage_surface.py | 86% of 140 lines in 1 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_ml_regime_lineage_surface, test_w39_options</t>
+          <t>tests/test_w39_ml_regime_lineage_surface.py | 86% of 140 lines in 1 key file(s) run by: test_w36_ml_strategy_tooling, test_w39_ml_regime_lineage_surface, test_w39_options, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr"/>
@@ -45065,7 +45390,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_ml_regime_lineage_surface.py | 87% of 341 lines in 2 key file(s) run by: test_w39_ml_regime_lineage_surface</t>
+          <t>tests/test_w39_ml_regime_lineage_surface.py | 87% of 341 lines in 2 key file(s) run by: test_w39_ml_regime_lineage_surface, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr"/>
@@ -45181,7 +45506,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_ml_regime_lineage_surface.py | 73% of 148 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite</t>
+          <t>tests/test_w39_ml_regime_lineage_surface.py | 88% of 154 lines in 1 key file(s) run by: test_auto_recover, test_w39_api_contract, test_w39_ml_regime_lineage_surface, test_w39_qa_suite, test_w40_meta_label</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
@@ -45297,7 +45622,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_backtest.py | 82% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39b_cpcv_pbo</t>
+          <t>tests/test_w39_backtest.py | 83% of 126 lines in 1 key file(s) run by: test_w39_backtest, test_w39_backtest_partial, test_w39b_bayes_optimize, test_w39b_cpcv_dominance, test_w39b_cpcv_pbo, test_w39b_event_driven_skips, test_w40_futures_backtest</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr"/>
@@ -46337,7 +46662,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_options.py | 88% of 209 lines in 1 key file(s) run by: test_w39_options</t>
+          <t>tests/test_w39_options.py | 88% of 209 lines in 1 key file(s) run by: test_signal_pipeline, test_w39_options, test_w40_option_intents</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr"/>
@@ -46453,7 +46778,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_technicals.py | 88% of 820 lines in 2 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+9 more)</t>
+          <t>tests/test_w39_technicals.py | 89% of 885 lines in 2 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+12 more)</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr"/>
@@ -46685,7 +47010,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_regime_gate.py | 83% of 248 lines in 1 key file(s) run by: test_w39_delivery, test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_technicals (+4 more)</t>
+          <t>tests/test_w39_regime_gate.py | 83% of 248 lines in 1 key file(s) run by: test_w39_delivery, test_w39_event_calendar, test_w39_market_pulse, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_technicals (+6 more)</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr"/>
@@ -46801,7 +47126,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_track_record.py | 84% of 522 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+6 more)</t>
+          <t>tests/test_w39_track_record.py | 85% of 587 lines in 1 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+9 more)</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr"/>
@@ -46917,7 +47242,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_weekly.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
+          <t>tests/test_w39_weekly.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+7 more)</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr"/>
@@ -47033,7 +47358,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_patterns.py; tests/test_w39b_patterns_more.py | 93% of 491 lines in 2 key file(s) run by: test_auto_recover, test_w39_delivery, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
+          <t>tests/test_w39_patterns.py; tests/test_w39b_patterns_more.py | 93% of 626 lines in 2 key file(s) run by: test_auto_recover, test_w39_delivery, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+7 more)</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr"/>
@@ -47149,7 +47474,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_rs_line.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
+          <t>tests/test_w39_rs_line.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+7 more)</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr"/>
@@ -47265,7 +47590,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_delivery.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals (+4 more)</t>
+          <t>tests/test_w39_delivery.py | 95% of 298 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+7 more)</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr"/>
@@ -47613,7 +47938,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_intraday.py | 88% of 225 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly, test_w39b_tf75</t>
+          <t>tests/test_w39_intraday.py | 88% of 225 lines in 1 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_regime_gate, test_w39_rs_line, test_w39_technicals, test_w39_weekly, test_w39b_tf75 (+2 more)</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr"/>
@@ -48030,7 +48355,7 @@
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>tools/atip_mcp.py</t>
+          <t>tools/atip_mcp.py; W40: 20 tools -- adds dvm, earnings_surprise, mf_search / mf_analytics / mf_sip / mf_compare, backtest_validation (stored CPCV / PBO) and chart_marks, each checked under query_only</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -48077,7 +48402,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39_mcp.py | 83% of 184 lines in 1 key file(s) run by: test_w39_mcp</t>
+          <t>tests/test_w39_mcp.py | 91% of 331 lines in 1 key file(s) run by: test_w39_mcp</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr"/>
@@ -48267,7 +48592,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Independent QA; no live intraday refresh (once a day, as of the close); /signals has no 75-minute column</t>
+          <t>Independent QA. W40: a 75m column on /signals and GET /api/stock/{symbol}/rating-75 (on demand from the stored 15-minute bars, completed bars only); the /signals column is still the 20:30 snapshot</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -48277,7 +48602,7 @@
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_tf75.py</t>
+          <t>tests/test_w39b_tf75.py; tests/test_w39b_tf75_signals.py</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
@@ -48309,7 +48634,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_tf75.py | 88% of 1266 lines in 3 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+10 more)</t>
+          <t>tests/test_w39b_tf75.py; tests/test_w39b_tf75_signals.py | 89% of 1331 lines in 3 key file(s) run by: test_w39_delivery, test_w39_intraday, test_w39_mcp, test_w39_owner_notes, test_w39_patterns, test_w39_perf_budget, test_w39_regime_gate, test_w39_rs_line (+13 more)</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr"/>
@@ -48425,7 +48750,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_dvm.py | 86% of 1041 lines in 3 key file(s) run by: test_auto_recover, test_w39_depth20, test_w39_event_calendar, test_w39_global_sync, test_w39_intraday, test_w39_market_pulse, test_w39_mcp, test_w39_options (+12 more)</t>
+          <t>tests/test_w39b_dvm.py | 86% of 1044 lines in 3 key file(s) run by: test_auto_recover, test_w39_depth20, test_w39_event_calendar, test_w39_global_sync, test_w39_intraday, test_w39_market_pulse, test_w39_mcp, test_w39_options (+14 more)</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr"/>
@@ -48541,7 +48866,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_earnings_surprise.py | 85% of 905 lines in 2 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+6 more)</t>
+          <t>tests/test_w39b_earnings_surprise.py | 86% of 970 lines in 2 key file(s) run by: test_w39_delivery, test_w39_mcp, test_w39_patterns, test_w39_regime_gate, test_w39_rs_line, test_w39_scorecard, test_w39_screener, test_w39_technicals (+9 more)</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -48614,12 +48939,12 @@
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>data/mf_analytics.py: point-to-point and CAGR returns, 1Y / 3Y rolling returns with hurdle stats, volatility / Sharpe / Sortino, drawdown with dates, beta / alpha / tracking error vs a price index, SIP and lump-sum XIRR, category rank among stored schemes, side-by-side compare; 3 read-only GET routes; scheme detail card on /data-platform</t>
+          <t>data/mf_analytics.py: point-to-point and CAGR returns, 1Y / 3Y rolling returns with hurdle stats, volatility / Sharpe / Sortino, drawdown with dates, beta / alpha / tracking error vs a price index, SIP and lump-sum XIRR, category rank among stored schemes, side-by-side compare; 3 read-only GET routes; scheme detail card on /data-platform. W40: step-up SIP, stamp duty (0.005 %) and units rounded down to 3 decimals by default, optional flat exit load per instalment; volatility annualised by the NAVs actually observed a year (not a fixed 252)</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Independent QA. Holding MFs in the wealth ledger stays out of scope (owner Scope Exclusions); benchmark is a price index, not total return; peers limited to stored schemes</t>
+          <t>Independent QA. Holding MFs in the wealth ledger stays out of scope (owner Scope Exclusions); benchmark is a price index (the W40 Nifty 50 TR is not wired here yet); peers limited to stored schemes; tiered exit loads not modelled</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -48661,13 +48986,245 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>tests/test_w39b_mf_analytics.py | 86% of 626 lines in 3 key file(s) run by: test_auto_recover, test_w39_ml_regime_lineage_surface, test_w39_perf_budget, test_w39_ui_smoke, test_w39b_mf_analytics</t>
+          <t>tests/test_w39b_mf_analytics.py | 87% of 688 lines in 3 key file(s) run by: test_auto_recover, test_w39_mcp, test_w39_ml_regime_lineage_surface, test_w39_perf_budget, test_w39_ui_smoke, test_w39b_mf_analytics</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>W40-RISKMODEL</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Risk &amp; Portfolio</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Fundamental factor risk model (Barra-style)</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Factor exposures, factor returns, covariance, specific risk and portfolio risk decomposition</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>W40 (PR #9): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4 items 5 and 9; tracker next actions</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J56" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K56" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>quant/risk_model.py: 8 styles (size, beta, momentum, residual volatility, book-to-price, earnings yield, ROE, liquidity) point in time, winsorised and cap-standardised, NSE industries (small ones pooled); daily sqrt(cap)-weighted regression with the industry constraint and robust t statistics; EWMA / Newey-West factor covariance; shrunk EWMA specific risk; decomposition of the PAPER / LIVE book (factor vs specific, per factor, marginal per stock, beta, active risk vs a cap-weighted Nifty 50 proxy); bias statistic on standard portfolios; nightly 21:45, incremental; /trading and /quant cards</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Independent QA on the real database; needs filed share counts for 30+ stocks; universe and industries are today's (survivorship); no free-float data</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>quant/risk_model.py; portfolio/risk.py; dashboard/risk_model_routes.py</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w40_risk_model.py</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>W40 developed 2026-10-09 on branch claude/wizardly-curie-fbjeoa (PR #9); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>W40 (PR #9)</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w40_risk_model.py | 76% of 1466 lines in 3 key file(s) run by: test_auto_recover, test_w39_perf_budget, test_w39_qa_suite, test_w39_quant_portfolio, test_w39_ui_smoke, test_w40_risk_model, test_w40_total_return</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>W39 reconciliation (owner tracker 2026-10-07)</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>W40-META</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Meta-labelling of the technical signals (AFML ch. 3-4, 7, 10)</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>A second model deciding which primary signals to take, with bet sizes</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>W40 (PR #9): docs/ATIP_GAP_ANALYSIS_2026-10.md section 4 items 5 and 9; tracker next actions</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J57" s="18" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED BUT NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="K57" s="14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>ml/meta_label.py: triple-barrier labels from the signal engine's own outcome rule; 37 features known at the signal's close; sample weights by average uniqueness; purged k-fold with embargo; GBM / logistic / RF; out-of-fold precision / recall / AUC and the kept signals' expectancy vs all; AFML bet sizing (reported only); ADOPTABLE only with 200+ signals and t &gt;= 2, and the registry refuses activating anything else; Saturday retrain and 20:45 scoring, both off unless meta_label.enabled; /signals column when adopted</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>Owner: switch on after a few hundred closed signals exist and a version is ADOPTABLE; independent QA</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>ml/meta_label.py; ml/validation.py; dashboard/w40_routes.py</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w40_meta_label.py</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Claude (development)</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>W40 developed 2026-10-09 on branch claude/wizardly-curie-fbjeoa (PR #9); independent validation PENDING</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>W40 (PR #9)</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_w40_meta_label.py | 90% of 861 lines in 3 key file(s) run by: test_auto_recover, test_w39_qa_suite, test_w39_regime_gate, test_w39_technicals, test_w40_meta_label</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z55"/>
+  <autoFilter ref="A1:Z57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49352,7 +49909,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 49/49 features developed (14 COMPLETED, 35 awaiting independent QA); automated tests: 35 covered, 14 partly, 0 none</t>
+          <t>[2026-10-07] 49/49 features developed (14 COMPLETED, 35 awaiting independent QA); automated tests: 36 covered, 13 partly, 0 none</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -49392,7 +49949,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 18/19 features developed (16 COMPLETED, 2 awaiting independent QA); automated tests: 9 covered, 9 partly, 0 none; BLOCKED: SE-05</t>
+          <t>[2026-10-07] 18/19 features developed (16 COMPLETED, 2 awaiting independent QA); automated tests: 11 covered, 7 partly, 0 none; BLOCKED: SE-05</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -49432,7 +49989,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>[2026-10-07] 32/32 features developed (15 COMPLETED, 17 awaiting independent QA); automated tests: 19 covered, 13 partly, 0 none</t>
+          <t>[2026-10-07] 32/32 features developed (15 COMPLETED, 17 awaiting independent QA); automated tests: 22 covered, 10 partly, 0 none</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -50160,7 +50717,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[2026-10-07] 10/10 features developed (0 COMPLETED, 10 awaiting independent QA); automated tests: 5 covered, 5 partly, 0 none</t>
+          <t>[2026-10-07] 10/10 features developed (0 COMPLETED, 10 awaiting independent QA); automated tests: 6 covered, 4 partly, 0 none</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -50454,7 +51011,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 1 covered, 5 partly, 0 none</t>
+          <t>[2026-10-07] 6/6 features developed (0 COMPLETED, 6 awaiting independent QA); automated tests: 3 covered, 3 partly, 0 none</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -50832,7 +51389,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[2026-10-07] 57/59 features developed (1 COMPLETED, 56 awaiting independent QA); automated tests: 58 covered, 0 partly, 0 none; BLOCKED: EX-19; open: QA-001</t>
+          <t>[2026-10-07] 59/61 features developed (1 COMPLETED, 58 awaiting independent QA); automated tests: 60 covered, 0 partly, 0 none; BLOCKED: EX-19; open: QA-001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -50990,7 +51547,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>79.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="G4" t="n">
         <v>41</v>
@@ -51022,7 +51579,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>85.5</v>
       </c>
       <c r="G5" t="n">
         <v>19</v>
@@ -52203,17 +52760,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>any prices_daily symbol (NIFTY50, NIFTYBANK, midcap, smallcap, sector indices); price return over the same sessions + PME of the investor's flows; W39: days invested shown and exported</t>
+          <t>any prices_daily symbol (NIFTY50, NIFTYBANK, midcap, smallcap, sector indices); price return over the same sessions + PME of the investor's flows; W39: days invested shown and exported. W40: benchmark "nifty50tr" -- the Nifty 50 with dividends reinvested (data/total_return.py: NSE's TRI method, the price index exact, its dividend points estimated from the top 50 stored stocks by cap, picked monthly and weighted daily; nightly 21:10; GET /api/data/total-return), part of the report's audited inputs</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>test_benchmark_return_is_the_price_return_over_the_sessions</t>
+          <t>test_benchmark_return_is_the_price_return_over_the_sessions; tests/test_w40_total_return.py</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Total-return index (dividends) not available from the data source</t>
+          <t>Independent QA; the dividend part is an estimate (no free-float or constituent data) -- compare once with NSE's published TRI</t>
         </is>
       </c>
     </row>
